--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -652,6 +652,11 @@
 </t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>done 2026-05-31 16:19</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -658,6 +658,33 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่นกรึบ หวานน้อย สูตรน้ำตาลต่ำ (Dried Coconut) ราคา 189.00 บาท</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3qKMKSQPB2</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mg3ydny6nkzwa4.webp</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>done 2026-06-05 11:44</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -672,16 +672,41 @@
           <t>https://s.shopee.co.th/3qKMKSQPB2</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mg3ydny6nkzwa4.webp</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>done 2026-06-05 11:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>เก๊กฮวยผงสำเร็จรูป HighlandHerb ขนาด 600 กรัม ราคา 249.00 บาท</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3VhVvoUPHl</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98v-lp4vdgeuw77id2.webp</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>done 2026-06-05 11:57</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -697,16 +697,41 @@
           <t>https://s.shopee.co.th/3VhVvoUPHl</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98v-lp4vdgeuw77id2.webp</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>done 2026-06-05 11:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>❤️ส่งด่วน1วัน รีวิวเยอะสุด 🙏เกรดพรีเมี่ยม ทุเรียนหมอนทองจันทบุรี แกะเนื้อล้วน พร้อมทาน 🚚ส่งรถเย็น ราคา 469.00 บาท</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1gFrkSHnnm</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0o-mcoacmrgvbz293.webp</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>done 2026-06-05 22:49</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -722,16 +722,41 @@
           <t>https://s.shopee.co.th/1gFrkSHnnm</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0o-mcoacmrgvbz293.webp</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>done 2026-06-05 22:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ชาเขียว 100% เพียวมัทฉะ ชาเขียว พรีเมี่ยม matcha powder from japan 0 สารเติมแต่ง 1 กระป๋อง 300g ราคา 374.00 บาท</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1qZHwlPy1j</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mhivoyzzzqird0.webp</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>done 2026-06-06 09:30</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -747,16 +747,141 @@
           <t>https://s.shopee.co.th/1qZHwlPy1j</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mhivoyzzzqird0.webp</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>done 2026-06-06 09:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>19</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ไส้อั่วโฮมเมดสูตรเชียงใหม่ หอมสมุนไพร เครื่องแกงเราทำเอง ชุด2แพ็ค รวมน้ำหนัก 1กิโลกรัม ราคา 337.00 บาท</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2qS1GCKbXS</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/0b788de026956cdf22390697e7a0306c.webp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>done 2026-06-08 05:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ทุเรียนจันทบุรีเนื้อพรีเมียม ยอดขายเยอะที่สุดทุเรียนหมอนทอง คัดเนื้อเทพไม่เน้นทรง เนื้อเหลือง เนื้อตลาดที่คนไทยกิน ราคา 621.00 บาท</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5fmCd5ZUob</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rask-mabmx8hshx6278.webp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>done 2026-06-08 05:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย เนื้อแน่น หนังกรอบ กรอบนอกนุ่มใน พร้อมน้ำจิ้ม ขนาด 500ก./ 1,000ก. ราคา 290.00 บาท</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7pqf9H2jLU</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rask-m76elywra3an63.webp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>done 2026-06-08 05:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>กุ้งจ่อมโคราชแท้ 100% ขนาด 500 กรัม (ส่งตรงจากบ้านปลาจ่อม อำเภอปักธงชัย จังหวัดนครราชสีมา) ราคา 90.00 บาท</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6VLJcuyatD</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/0952cbb174eccbe472d21bbfd74f6b1e.webp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>done 2026-06-08 05:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>[แพ็คเกจลุ้นรางวัล][แพ็ค 6] Tulip Cocoa Powder Dark Brown Colour 440 g. ทิวลิปผงโกโก้สีเข้ม 440 กรัม ราคา 1335.00 บาท</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/BRG53bISA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-823pw-mowwmk8cx5vmdc.webp</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>done 2026-06-08 05:46</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -872,16 +872,141 @@
           <t>https://s.shopee.co.th/BRG53bISA</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/sg-11134201-823pw-mowwmk8cx5vmdc.webp</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>done 2026-06-08 05:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>17</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ไร้เม็ด ผลไม้อบแห้งเกรดส่งออก สูตรน้ำตาลต่ำ (Dried Orange Low Sugar) ราคา 95.00 บาท</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6fehl9kz4K</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m6tjad8k1fxc38.webp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>done 2026-06-08 07:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ขนมเปี๊ยะลาวาไส้ฝอยทองนูเทลล่า (350g) Noeyleeshop ราคา 94.00 บาท</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8fPoCgrCHw</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasb-mb1xybwmbxc1d2.webp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>done 2026-06-08 07:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>หมูหวานซีอิ๊วงา ทอดไท (นุ่ม-ไม่แข็ง 150 ก) 👉 ไม่ใส่พริกไทย เด็กทานได้ ราคา 114.00 บาท</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/110N4eA1qB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98y-lr10flflzagt5a.webp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>done 2026-06-08 07:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>18</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>นมกล่อง (ยกลัง) นมยูเอชที นมไฮคิวสูตร3 1พลัส ซูเปอร์โกลด์ รสจืด180 มล (27 กล่อง) นม UHT HiQ Super Gold UHT ราคา 669.00 บาท</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2qS1FunWwa</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasg-m7hrtewsksjj0d.webp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>done 2026-06-08 07:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>12</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>น้ำมันปาล์ม ตรา หยก ขนาด1ลิตร แพ็ค 3 ขวด ราคา 210.00 บาท</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/70HaDgeSt4</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-823rr-mp0ouarhqkn61b.webp</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>done 2026-06-08 07:41</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -997,16 +997,141 @@
           <t>https://s.shopee.co.th/70HaDgeSt4</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/sg-11134201-823rr-mp0ouarhqkn61b.webp</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>done 2026-06-08 07:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>10</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ขนมอัลมอนด์ดาร์กช็อค ไม่ใส่เนย ไม่ใส่แป้ง Ketoทานได้ สูตรคลีนเพื่อสุขภาพ Almond DarkChoc Kanomdeedee (ขนมดีดี) ราคา 193.00 บาท</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8pjEP3FPCX</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztc-mjlfxs2zdmva1c.webp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>done 2026-06-09 06:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>[ของแท้ ต้นตำรับ] หยิบเป็นชิ้นทานง่าย หมี่กรอบเตาถ่าน กรอบนุ่มไม่แข็ง หอมผิวส้มซ่า (1กล่อง 60 ชิ้น) ราคา 251.00 บาท</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4qD5devtq4</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztn-mlth9szef6df1f.webp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>done 2026-06-09 06:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>น้ำพริกกากหมู ขนาด 150 กรัม แบบกระปุก แซ่บปะล้ำปะเหลือ ราคา 158.00 บาท</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/17psx9vPd</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7qul6-lig9ntju66lk6e.webp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>done 2026-06-09 06:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ค่าส่งถูกที่สุดร้านช่วยจ่าย ยอดขายเยอะที่สุดทุเรียนหมอนทอง คัดเนื้อเทพไม่เน้นทรง เนื้อเหลือง เนื้อตลาดที่คนไทยกิน ราคา 621.00 บาท</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4ftfRK3fOI</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r992-lx9x2ueokgxcc9.webp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>done 2026-06-09 06:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>น้ำพริกกากหมู ยาหยี (200 ก) 🌶 อร่อย 🔥มีเนื้อ - มีหนัง ราคา 99.00 บาท</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4ftfRbjCEv</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98q-lr8le588wcsd92.webp</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>done 2026-06-09 06:04</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1122,16 +1122,141 @@
           <t>https://s.shopee.co.th/4ftfRbjCEv</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98q-lr8le588wcsd92.webp</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>done 2026-06-09 06:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>13</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>เมล็ดกาแฟคั่ว เขาทะลุ ชุมพร💥คัดเกรดขนาด 500 กรัม กาแฟโรบัสต้า จากขุนเขาชุมพร สู่กาแฟพรีเมียมไทย | Khao Thalu Coffee ราคา 180.00 บาท</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6VLJciC5w7</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztn-mjh2qiig3y83e1.webp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>done 2026-06-10 06:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>19</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ปลาหมึกไข่แดดเดียวทอดพร้อมทาน -(ไข่ทุกตัว) ไซร์ 5-9 ตัวต่อแพค น้ำหนักก่อนทอด300กรัมและ 500 กรัม ราคา 325.00 บาท</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6fehlA2J9M</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/23e49a44f577b0531100e55e0851f11f.webp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>done 2026-06-10 06:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>20</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>[โปร 3 กระปุก] น้ำพริกแจ่วบอง ไร่จิตภักดี แบบผัดสุก รสชาติเผ็ดนัวแซ่บถึงใจ ขนาด150กรัม ราคา 219.00 บาท</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/LkgHbeZU4</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasc-m8x35mczvx0ude.webp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>done 2026-06-10 06:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>16</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>น้ำพริกปลาแซลมอน น้ำพริกรสแซ่บ น้ำพริกแห้ง ขนาด 80 กรัม แม่ทองคำรสแซ่บ แซลมอน Salmon Chilli Paste ราคา 55.00 บาท</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9AM4ncO9EF</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98p-lrzz1m8bd41pfb.webp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>done 2026-06-10 06:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>13</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ปังเปี๊ยะโมจินมสดฮอกไกโด250g แถมดริปนูเทลล่า 40g ราคา 79.00 บาท</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9UyvCR64vP</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0g-mcltjs8w1rlsba.webp</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>done 2026-06-10 06:05</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1247,16 +1247,141 @@
           <t>https://s.shopee.co.th/9UyvCR64vP</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0g-mcltjs8w1rlsba.webp</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>done 2026-06-10 06:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>12</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Chocolate Brownie Bite ช็อกโกแลตบราวนี่ไบท์ บราวนี่หน้าฟิล์ม ราคา 119.00 บาท</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4AxMmYCMnR</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-23030-bggj3q1eovovda.webp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>done 2026-06-10 11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>8</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ตากสดใหม่ รับประกันความอร่อย ราคา 129.00 บาท</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6pyA1F9Gqv</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-22110-pkze82odovjv1f.webp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>done 2026-06-10 11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Cheesy Jujube - พุทรานมชีส 250 กรัม ขนม อร่อย โฮมเมด นูกัตตี๋เล็ก พุทรา นม ชีส ของฝาก ขนมทานเล่น by teeleknougat ราคา 189.00 บาท</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8fPoCsmUHB</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zte-mgdl0qn5u70q1e.webp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>done 2026-06-10 11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>KETO ไส้อั่วหมูสมุนไพรคีโต ย่างหอมๆจากเมืองเหนือ คีโต-โลว์คาร์บทานได้ ราคา 109.00 บาท</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/17psy0rKS</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98r-ltgbf2j90fi721.webp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>done 2026-06-10 11:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>12</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>(แบบไม่มีน้ำจิ้ม) หมูกรอบ อบ ไม่มีไขมันทรานส์ เนื้อนุ่ม หนังกรอบ by หมูกรอบ SNOOK ราคา 172.00 บาท</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/W46TxsKWN</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/cc8c958732c4728a5538bdd8ae6475f8.webp</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>done 2026-06-10 11:16</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1372,16 +1372,141 @@
           <t>https://s.shopee.co.th/W46TxsKWN</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/cc8c958732c4728a5538bdd8ae6475f8.webp</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>done 2026-06-10 11:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>7</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ไร้แมลง เนื้อนุ่ม ฉ่ำ ทอดง่าย ราคา 149.00 บาท</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/30lRSKFxR4</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mm8rnpzzshs429.webp</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>done 2026-06-11 06:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>9</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ผงชาเขียวอาโอโมริ"AOMORI Matcha"ผงชาเขียวมัทฉะ 100% สูตรพรีเมี่ยม 100g. ราคา 119.00 บาท</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1LdDTGYsoS</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasj-m5sqf6g4v4c668.webp</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>done 2026-06-11 06:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>7</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>น้ำพริกหนังไก่ ยาหยี (100/150/200 ก) 🌶 เผ็ด จัดจ้าน ราคา 75.00 บาท</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/50WTm4WhFs</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r991-lr10flflv2rh60.webp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>done 2026-06-11 06:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>16</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>เบนิฟิตต์ ไฮโปรตีน ขนาด350 มล.( หมดอายุ เดือน 9-10/2026)จัดส่งภายใน2-3วัน(สั่ง1ลังต่อคำสั่งซื้อ) ราคา 399.00 บาท</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3LOHr6tssA</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztj-mlh91o6kf95bed.webp</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>done 2026-06-11 06:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>6</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>เม็ดมะม่วงหิมพานต์อบ 500 กรัม เกรด A เต็มเม็ด หอม กรอบ ไม่ทอด | Khunja Shop ราคา 155.00 บาท</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9AM4nb7QzA</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zti-miibfjkeai2q55.webp</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>done 2026-06-11 06:15</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -7,6 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -472,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1497,16 +1498,141 @@
           <t>https://s.shopee.co.th/9AM4nb7QzA</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81zti-miibfjkeai2q55.webp</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>done 2026-06-11 06:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>20</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ตราฉัตร 5 กิโล ข้าวหอมมะลิใหม่ ข้าวหอมมะลิแท้ ตราฉัตร 5kg. (หอม นุ่ม ตลอดปี) ข้าวหอมผสม ข้าวขาว หุงอร่อย หุงขึ้นหม้อ ราคา 134.00 บาท</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2qRzC7LIj7</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-8260m-mkdsz738rxtu0a.webp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>done 2026-06-12 06:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>20</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ผลไม้ดอง 1kg บรรจุขวดโหล ชั่งเฉพาะเนื้อ แถมฟรีพริกเกลือรสเด็ด ราคา 100.00 บาท</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7fXH0vfIv3</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98x-ll6odn47bqr032.webp</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>done 2026-06-12 06:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>3</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นใหญ่ เต็มคำ แซ่บ เปรี้ยวเผ็ดสะใจ มี2ขนาด 100g./400g. ราคา 177.00 บาท</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8pjCL6ho1X</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mnmij2prwhl2a7.webp</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>done 2026-06-12 06:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>10</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ผงมัทฉะ ออร์แกนิค 100% กลิ่นหอมละมุน ชงง่ายในทุกเมนู - RAIWAN ขนาด 100 กรัม ราคา 340.00 บาท</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/30lPOOyjCD</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0s-md4csnzellfp52.webp</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>done 2026-06-12 06:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>16</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>น้ำพริกปูม้า แบรนด์ บังฟิส มันปู/ไข่ปู/เนื้อปู ราคา 169.00 บาท</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4AxOqi9zhi</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98v-lzsvhmsql75t87.webp</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>done 2026-06-12 06:11</t>
         </is>
       </c>
     </row>
@@ -1521,4 +1647,25 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>{"last_personas": ["G", "G", "C", "D", "H"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ..."], "last_styles": ["ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก"]}</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1623,16 +1623,141 @@
           <t>https://s.shopee.co.th/4AxOqi9zhi</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98v-lzsvhmsql75t87.webp</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>done 2026-06-12 06:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>8</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ปุยแสบปาก พริกผัดน้ำมันมะกอก Vegen ราคา 263.00 บาท</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/AKY2C1mROs</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mnu2gil3c16u83.webp</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>done 2026-06-13 06:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>11</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ส่งด่วนกรุงเทพ/ตจว.❤️ทุเรียนหมอนทองระยอง-จัน แท้💯พรีเมี่ยม แกะเนื้อ รับประกันไม่ตรงปกเปลี่ยนใหม่ให้100%💋 ส่งทุกวัน ราคา 415.00 บาท</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9fILOaKtZ4</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-mkjkqzprk3ye45.webp</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>done 2026-06-13 06:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>[เซ็ตคู่] น้ำพริกไข่ปูม้า + น้ำพริกเนื้อปูม้า น้ำพริก ปูม้ามีเลขฮาลาลทุกสูตร . ราคา 304.00 บาท</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5Apw2WWZJu</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasi-m5phpwu6gkvqac.webp</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>done 2026-06-13 06:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>[Official] 🔥 [KETO] Wholesweet น้ำเชื่อมหญ้าหวาน ไซรัปหญ้าหวาน สูตรคีโต 320 มล. ราคา 151.00 บาท</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1BJnH6JRHT</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/a59d309f9d3e34b88669ec977426484d.webp</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>done 2026-06-13 06:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>11</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>หมูแดดเดียว หมูเบทาโกรเกรดA ไม่ใส่สารกันบูด ไม่เหนียว ไม่แข็ง สีธรรมชาติ วัตถุดิบเครื่องปรุงคุณภาพสูง อร่อย สะอาด มี อย. ราคา 92.00 บาท</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5Apw2XRyH1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98x-lxflamy6285r9b.webp</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>done 2026-06-13 06:04</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1786,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["G", "G", "C", "D", "H"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ..."], "last_styles": ["ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก"]}</t>
+          <t>{"last_personas": ["G", "G", "C", "D", "H", "E", "G", "B", "H", "F"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ"], "last_styles": ["ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "คำถาม"], "last_roles": ["R7", "R3", "R7", "R5", "R5"], "recent_captions": ["มีใครเป็นเหมือนผมไหม นมโปรตีนตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปุยแสบปาก พริกผัดน้ำมันมะกอก Vegen ราคา ราคาแค่ 263 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น กรุงเทพ/ตจว.❤️ทุเรียนหมอนทองระยอง-จัน แท้💯พรี ราคาแค่ 415 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เซ็ตคู่ น้ำพริกไข่ปูม้า + น้ำพริกเนื้อปูม้า ราคาแค่ 304 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Official 🔥 KETO Wholesweet ราคาแค่ 151 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูแดดเดียว หมูเบทาโกรเกรดA ไม่ใส่สารกันบูด ไ ราคาแค่ 92 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1748,16 +1748,141 @@
           <t>https://s.shopee.co.th/5Apw2XRyH1</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98x-lxflamy6285r9b.webp</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>done 2026-06-13 06:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>4</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>(แพ็ค 24 ซอง) Muek Groob หมึกกรุบ เส้นบุกปรุงรสหม่าล่า (เลือกรสชาติได้) ราคา 532.00 บาท</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1gG3rjy0Kb</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mp4md3z4eyvi66.webp</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>done 2026-06-14 05:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>4</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ขายดีมาก ปลาสลิดไข่ 4-5 ตัว 500 กรัม📌(ซื้อ2แพคคุ้มกว่าจ้า) เค็มน้อย อร่อยมาก มีไข่จุกๆทุกตัว ราคา 200.00 บาท</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7pqhDM2ExP</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-mg3tpwy77v2m4b.webp</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>done 2026-06-14 05:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Llamito ผงมัทฉะ ออร์แกนิค (Matcha Powder) ขนาด 250g ราคา 449.00 บาท</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/qgwsYVoHw</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mih9x5ddqn0n95.webp</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>done 2026-06-14 05:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>อุดมสุข น้ำพริกอกไก่คลีน น้ำพริกอกไก่ น้ำพริกคลีน น้ำพริกคีโต อาหารเพื่อสุขภาพ อาหารคลีน อาหารคีโต ราคา 109.00 บาท</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5VSmQmR3XO</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mgdp5aurnthl96.webp</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>done 2026-06-14 05:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>4</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>เต้าหู้เฮียแว่น เต้าหู้เนื้อครีมคัสตาร์ด กรอบนอก ครีมฉ่ำ นิ่มละมุน | แพ็ค 5 ชิ้น 1 กิโล | โปรตีน 55 กรัม | แช่เย็น 7 วัน ราคา 175.00 บาท</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1BJnGwvqq6</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-ml3bpvzk2l8ic2.webp</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>done 2026-06-14 05:46</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1911,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["G", "G", "C", "D", "H", "E", "G", "B", "H", "F"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ"], "last_styles": ["ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "คำถาม"], "last_roles": ["R7", "R3", "R7", "R5", "R5"], "recent_captions": ["มีใครเป็นเหมือนผมไหม นมโปรตีนตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปุยแสบปาก พริกผัดน้ำมันมะกอก Vegen ราคา ราคาแค่ 263 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น กรุงเทพ/ตจว.❤️ทุเรียนหมอนทองระยอง-จัน แท้💯พรี ราคาแค่ 415 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เซ็ตคู่ น้ำพริกไข่ปูม้า + น้ำพริกเนื้อปูม้า ราคาแค่ 304 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Official 🔥 KETO Wholesweet ราคาแค่ 151 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูแดดเดียว หมูเบทาโกรเกรดA ไม่ใส่สารกันบูด ไ ราคาแค่ 92 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇"]}</t>
+          <t>{"last_personas": ["G", "G", "C", "D", "H", "E", "G", "B", "H", "F", "A", "D", "A", "C", "H"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ..."], "last_styles": ["ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว"], "last_roles": ["R7", "R3", "R7", "R5", "R5", "R6", "R8", "R8", "R2", "R4"], "recent_captions": ["มีใครเป็นเหมือนผมไหม นมโปรตีนตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปุยแสบปาก พริกผัดน้ำมันมะกอก Vegen ราคา ราคาแค่ 263 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น กรุงเทพ/ตจว.❤️ทุเรียนหมอนทองระยอง-จัน แท้💯พรี ราคาแค่ 415 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เซ็ตคู่ น้ำพริกไข่ปูม้า + น้ำพริกเนื้อปูม้า ราคาแค่ 304 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Official 🔥 KETO Wholesweet ราคาแค่ 151 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูแดดเดียว หมูเบทาโกรเกรดA ไม่ใส่สารกันบูด ไ ราคาแค่ 92 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 532 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดีมาก ปลาสลิดไข่ - กรัม📌ซื้อ2แพคคุ้มกว่าจ้ ราคาแค่ 200 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Llamito ผงมัทฉะ ออร์แกนิค Matcha ราคาแค่ 449 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อุดมสุข น้ำพริกอกไก่คลีน น้ำพริกอกไก่ น้ำพริก ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ แว่นตากันแดด ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เต้าหู้เฮียแว่น เต้าหู้เนื้อครีมคัสตาร์ด กรอบ ราคาแค่ 175 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1873,16 +1873,141 @@
           <t>https://s.shopee.co.th/1BJnGwvqq6</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-ml3bpvzk2l8ic2.webp</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>done 2026-06-14 05:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>19</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>(6.6) koreadong โคเรียดอง 4 กระปุก แซลมอน 2 กุ้ง 2 ฟรี!! น้ำจิ้ม 2 สูตร ราคา 1089.00 บาท</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6VLJcekMgd</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztn-mp3lp4rqcflt1c.webp</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>done 2026-06-15 05:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>15</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี 1 กระปุก ขนาด 500 กรัม ราคา 283.00 บาท</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/30lRSHhZGU</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98o-lvaiypl9rum22b.webp</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>done 2026-06-15 05:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>11</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>PRO2 *แซลมอนชาคริต* 20 ชิ้น ส่งแช่แข็งฟรี -เนื้อแซลมอน นอร์เวย์ ไร้ก้าง ทานดิบได้- ร้านของคริต ชาคริต แย้มนาม ร้านชาคริต ราคา 3099.00 บาท</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5q5cpPcaAJ</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztj-ml5rl1atqqyq13.webp</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>done 2026-06-15 05:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>10</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>(แพ็ก 12) Muek Groob หมึกกรุบ เส้นบุกปรุงรสหม่าล่า สูตรดั้งเดิม หมึกกรุบซันซุ sunsu ราคา 270.00 บาท</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7fXH0qnVjj</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-823qs-mp3qgnwmeept30.webp</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>done 2026-06-15 05:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>14</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>หมูสามชั้นแดดเดียวไร้หนัง สะอาด ปลอดภัย ไม่ใส่สารกันเสีย ไม่ใส่สีผสมอาหาร ทำสดใหม่ทุกวัน ราคา 152.00 บาท</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1qZU4Lgl3I</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mhshbqn5vy848f.webp</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>done 2026-06-15 05:51</t>
         </is>
       </c>
     </row>
@@ -1911,7 +2036,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["G", "G", "C", "D", "H", "E", "G", "B", "H", "F", "A", "D", "A", "C", "H"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ..."], "last_styles": ["ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว"], "last_roles": ["R7", "R3", "R7", "R5", "R5", "R6", "R8", "R8", "R2", "R4"], "recent_captions": ["มีใครเป็นเหมือนผมไหม นมโปรตีนตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปุยแสบปาก พริกผัดน้ำมันมะกอก Vegen ราคา ราคาแค่ 263 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น กรุงเทพ/ตจว.❤️ทุเรียนหมอนทองระยอง-จัน แท้💯พรี ราคาแค่ 415 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เซ็ตคู่ น้ำพริกไข่ปูม้า + น้ำพริกเนื้อปูม้า ราคาแค่ 304 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Official 🔥 KETO Wholesweet ราคาแค่ 151 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูแดดเดียว หมูเบทาโกรเกรดA ไม่ใส่สารกันบูด ไ ราคาแค่ 92 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 532 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดีมาก ปลาสลิดไข่ - กรัม📌ซื้อ2แพคคุ้มกว่าจ้ ราคาแค่ 200 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Llamito ผงมัทฉะ ออร์แกนิค Matcha ราคาแค่ 449 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อุดมสุข น้ำพริกอกไก่คลีน น้ำพริกอกไก่ น้ำพริก ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ แว่นตากันแดด ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เต้าหู้เฮียแว่น เต้าหู้เนื้อครีมคัสตาร์ด กรอบ ราคาแค่ 175 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇"]}</t>
+          <t>{"last_personas": ["G", "G", "C", "D", "H", "E", "G", "B", "H", "F", "A", "D", "A", "C", "H", "A", "H", "G", "E", "H"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ"], "last_styles": ["ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ"], "last_roles": ["R7", "R3", "R7", "R5", "R5", "R6", "R8", "R8", "R2", "R4", "R6", "R2", "R4", "R1", "R1"], "recent_captions": ["มีใครเป็นเหมือนผมไหม นมโปรตีนตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปุยแสบปาก พริกผัดน้ำมันมะกอก Vegen ราคา ราคาแค่ 263 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น กรุงเทพ/ตจว.❤️ทุเรียนหมอนทองระยอง-จัน แท้💯พรี ราคาแค่ 415 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เซ็ตคู่ น้ำพริกไข่ปูม้า + น้ำพริกเนื้อปูม้า ราคาแค่ 304 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Official 🔥 KETO Wholesweet ราคาแค่ 151 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูแดดเดียว หมูเบทาโกรเกรดA ไม่ใส่สารกันบูด ไ ราคาแค่ 92 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 532 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดีมาก ปลาสลิดไข่ - กรัม📌ซื้อ2แพคคุ้มกว่าจ้ ราคาแค่ 200 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Llamito ผงมัทฉะ ออร์แกนิค Matcha ราคาแค่ 449 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อุดมสุข น้ำพริกอกไก่คลีน น้ำพริกอกไก่ น้ำพริก ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ แว่นตากันแดด ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เต้าหู้เฮียแว่น เต้าหู้เนื้อครีมคัสตาร์ด กรอบ ราคาแค่ 175 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง กระปุก แซลมอน ราคาแค่ 1089 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 283 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น *แซลมอนชาคริต* ชิ้น ส่งแช่แข็งฟรี -เนื้อแซลมอ ราคาแค่ 3099 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ก Muek Groob หมึกกรุบ ราคาแค่ 270 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูสามชั้นแดดเดียวไร้หนัง สะอาด ปลอดภัย ไม่ใส ราคาแค่ 152 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1998,16 +1998,141 @@
           <t>https://s.shopee.co.th/1qZU4Lgl3I</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mhshbqn5vy848f.webp</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
           <t>done 2026-06-15 05:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>16</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>ชุด 4 ขวด นมแดรี่โฮมไฮโปรตีน สูตรแลคโตสฟรี ขนาด 300 มล. **จัดส่งเฉพาะในกรุงเทพ** (ไม่มีแถมลังโฟม) ราคา 300.00 บาท</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8Kmxo93MVt</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztn-mogz3i52c64t0b.webp</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>done 2026-06-16 06:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>13</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>มันหนึบญี่ปุ่น เบนิฮารุกะ หวานธรรมชาติ ไม่ใส่น้ำตาล ร้านมาซาริ ราคา 272.00 บาท</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8fPoCyWB2R</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ras9-m70vmyupwyzzda.webp</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>done 2026-06-16 06:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>3</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>🦐 กุ้งแม่น้ำไซส์จัมโป้ 4-7ตัวโล กุ้งตัวใหญ่ๆ 1แพ็คมี3-5ตัว น้ำหนัก1กิโลกรัมน้ำหนักอาจหายนะครับกุ้งสดๆและนำไปแช็ง ราคา 280.00 บาท</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5Apw2WO73q</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztj-mlpbfq1962o574.webp</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>done 2026-06-16 06:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>10</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>เมล็ดเจีย Organic มี อย.คัดพิเศษ เกรดพรีเมี่ยม แบรนด์ไร่พระจันทร์ chia seed 200 400กรัม ราคา 130.00 บาท</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/20suGeAdc0</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztn-mkv374joghds15.webp</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>done 2026-06-16 06:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>8</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ถูกที่สุด Bertolli Extra Virgin Olive Oil เบอร์ทอลลีน้ำมันมะกอกเอ็กซ์ตร้าเวอร์จิ้น ราคา 442.00 บาท</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7fXH0u6NAg</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-7rbn7-m5xznx46gpavb2.webp</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>done 2026-06-16 06:24</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2161,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["G", "G", "C", "D", "H", "E", "G", "B", "H", "F", "A", "D", "A", "C", "H", "A", "H", "G", "E", "H"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ"], "last_styles": ["ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ"], "last_roles": ["R7", "R3", "R7", "R5", "R5", "R6", "R8", "R8", "R2", "R4", "R6", "R2", "R4", "R1", "R1"], "recent_captions": ["มีใครเป็นเหมือนผมไหม นมโปรตีนตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปุยแสบปาก พริกผัดน้ำมันมะกอก Vegen ราคา ราคาแค่ 263 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น กรุงเทพ/ตจว.❤️ทุเรียนหมอนทองระยอง-จัน แท้💯พรี ราคาแค่ 415 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เซ็ตคู่ น้ำพริกไข่ปูม้า + น้ำพริกเนื้อปูม้า ราคาแค่ 304 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Official 🔥 KETO Wholesweet ราคาแค่ 151 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูแดดเดียว หมูเบทาโกรเกรดA ไม่ใส่สารกันบูด ไ ราคาแค่ 92 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 532 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดีมาก ปลาสลิดไข่ - กรัม📌ซื้อ2แพคคุ้มกว่าจ้ ราคาแค่ 200 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Llamito ผงมัทฉะ ออร์แกนิค Matcha ราคาแค่ 449 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อุดมสุข น้ำพริกอกไก่คลีน น้ำพริกอกไก่ น้ำพริก ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ แว่นตากันแดด ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เต้าหู้เฮียแว่น เต้าหู้เนื้อครีมคัสตาร์ด กรอบ ราคาแค่ 175 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง กระปุก แซลมอน ราคาแค่ 1089 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 283 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น *แซลมอนชาคริต* ชิ้น ส่งแช่แข็งฟรี -เนื้อแซลมอ ราคาแค่ 3099 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ก Muek Groob หมึกกรุบ ราคาแค่ 270 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูสามชั้นแดดเดียวไร้หนัง สะอาด ปลอดภัย ไม่ใส ราคาแค่ 152 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇"]}</t>
+          <t>{"last_personas": ["G", "G", "C", "D", "H", "E", "G", "B", "H", "F", "A", "D", "A", "C", "H", "A", "H", "G", "E", "H", "D", "A", "D", "B", "H"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ..."], "last_styles": ["ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ"], "last_roles": ["R7", "R3", "R7", "R5", "R5", "R6", "R8", "R8", "R2", "R4", "R6", "R2", "R4", "R1", "R1", "R3", "R3", "R6", "R5", "R4"], "recent_captions": ["มีใครเป็นเหมือนผมไหม นมโปรตีนตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปุยแสบปาก พริกผัดน้ำมันมะกอก Vegen ราคา ราคาแค่ 263 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น กรุงเทพ/ตจว.❤️ทุเรียนหมอนทองระยอง-จัน แท้💯พรี ราคาแค่ 415 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เซ็ตคู่ น้ำพริกไข่ปูม้า + น้ำพริกเนื้อปูม้า ราคาแค่ 304 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Official 🔥 KETO Wholesweet ราคาแค่ 151 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูแดดเดียว หมูเบทาโกรเกรดA ไม่ใส่สารกันบูด ไ ราคาแค่ 92 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 532 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดีมาก ปลาสลิดไข่ - กรัม📌ซื้อ2แพคคุ้มกว่าจ้ ราคาแค่ 200 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Llamito ผงมัทฉะ ออร์แกนิค Matcha ราคาแค่ 449 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อุดมสุข น้ำพริกอกไก่คลีน น้ำพริกอกไก่ น้ำพริก ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ แว่นตากันแดด ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เต้าหู้เฮียแว่น เต้าหู้เนื้อครีมคัสตาร์ด กรอบ ราคาแค่ 175 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง กระปุก แซลมอน ราคาแค่ 1089 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 283 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น *แซลมอนชาคริต* ชิ้น ส่งแช่แข็งฟรี -เนื้อแซลมอ ราคาแค่ 3099 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ก Muek Groob หมึกกรุบ ราคาแค่ 270 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูสามชั้นแดดเดียวไร้หนัง สะอาด ปลอดภัย ไม่ใส ราคาแค่ 152 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วยลดยากินน้ำหวานจุกจิกได้เยอะ แคลคุมง่ายอิ่มท้องนาน แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชุด ขวด นมแดรี่โฮมไฮโปรตีน สูตรแลคโตสฟรี ราคาแค่ 300 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มันหนึบญี่ปุ่น เบนิฮารุกะ หวานธรรมชาติ ไม่ใส่ ราคาแค่ 272 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น 🦐 กุ้งแม่น้ำไซส์จัมโป้ -7ตัวโล กุ้งตัวใหญ่ๆ ราคาแค่ 280 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เมล็ดเจีย Organic มี อย.คัดพิเศษ ราคาแค่ 130 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ถูกที่สุด Bertolli Extra Virgin ราคาแค่ 442 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2123,16 +2123,141 @@
           <t>https://s.shopee.co.th/7fXH0u6NAg</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/sg-11134201-7rbn7-m5xznx46gpavb2.webp</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
           <t>done 2026-06-16 06:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>13</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>(แพ็ค 24 ซอง) Muek Groob หมึกกรุบ เส้นบุกปรุงรสหม่าล่า (เลือกรสชาติได้) ราคา 529.00 บาท</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/20ssCZUVx7</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mp4md3z4eyvi66.webp</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>done 2026-06-17 06:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>18</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ขนมเปี๊ยะไส้ทะลัก ไข่แดงเค็ม 3 ใบ มีให้เลือก 4 รสชาติ ขนาด 450 กรัม WANWANACH ราคา 139.00 บาท</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8V6O0gAxW4</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mmprjgiy639d92.webp</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>done 2026-06-17 06:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>15</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>(6.6) koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี 4 กระปุก สุดฮิต แถมฟรีน้ำจิ้ม ราคา 1112.00 บาท</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9AM4nY110F</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zte-mp3lys3nslqk0b.webp</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>done 2026-06-17 06:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>1</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Teelek Nougat -นูกัตถุงใหญ่ 18 ชิ้น ราคา 250.00 บาท</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4ftfRb84dJ</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0i-mbrwl55927v730.webp</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>done 2026-06-17 06:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>4</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Country Sourdough Bread ขนมปังซาวโดว์โฮมเมด 100% | SOURDOUGH BREAD | ราคา 182.00 บาท</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9AM2jit34K</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0h-mcpd1y74lysm7e.webp</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>done 2026-06-17 06:10</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2286,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["G", "G", "C", "D", "H", "E", "G", "B", "H", "F", "A", "D", "A", "C", "H", "A", "H", "G", "E", "H", "D", "A", "D", "B", "H"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ..."], "last_styles": ["ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ"], "last_roles": ["R7", "R3", "R7", "R5", "R5", "R6", "R8", "R8", "R2", "R4", "R6", "R2", "R4", "R1", "R1", "R3", "R3", "R6", "R5", "R4"], "recent_captions": ["มีใครเป็นเหมือนผมไหม นมโปรตีนตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปุยแสบปาก พริกผัดน้ำมันมะกอก Vegen ราคา ราคาแค่ 263 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น กรุงเทพ/ตจว.❤️ทุเรียนหมอนทองระยอง-จัน แท้💯พรี ราคาแค่ 415 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เซ็ตคู่ น้ำพริกไข่ปูม้า + น้ำพริกเนื้อปูม้า ราคาแค่ 304 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Official 🔥 KETO Wholesweet ราคาแค่ 151 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูแดดเดียว หมูเบทาโกรเกรดA ไม่ใส่สารกันบูด ไ ราคาแค่ 92 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 532 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดีมาก ปลาสลิดไข่ - กรัม📌ซื้อ2แพคคุ้มกว่าจ้ ราคาแค่ 200 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Llamito ผงมัทฉะ ออร์แกนิค Matcha ราคาแค่ 449 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อุดมสุข น้ำพริกอกไก่คลีน น้ำพริกอกไก่ น้ำพริก ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ แว่นตากันแดด ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เต้าหู้เฮียแว่น เต้าหู้เนื้อครีมคัสตาร์ด กรอบ ราคาแค่ 175 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง กระปุก แซลมอน ราคาแค่ 1089 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 283 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น *แซลมอนชาคริต* ชิ้น ส่งแช่แข็งฟรี -เนื้อแซลมอ ราคาแค่ 3099 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ก Muek Groob หมึกกรุบ ราคาแค่ 270 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูสามชั้นแดดเดียวไร้หนัง สะอาด ปลอดภัย ไม่ใส ราคาแค่ 152 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วยลดยากินน้ำหวานจุกจิกได้เยอะ แคลคุมง่ายอิ่มท้องนาน แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชุด ขวด นมแดรี่โฮมไฮโปรตีน สูตรแลคโตสฟรี ราคาแค่ 300 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มันหนึบญี่ปุ่น เบนิฮารุกะ หวานธรรมชาติ ไม่ใส่ ราคาแค่ 272 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น 🦐 กุ้งแม่น้ำไซส์จัมโป้ -7ตัวโล กุ้งตัวใหญ่ๆ ราคาแค่ 280 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เมล็ดเจีย Organic มี อย.คัดพิเศษ ราคาแค่ 130 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ถูกที่สุด Bertolli Extra Virgin ราคาแค่ 442 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇"]}</t>
+          <t>{"last_personas": ["G", "G", "C", "D", "H", "E", "G", "B", "H", "F", "A", "D", "A", "C", "H", "A", "H", "G", "E", "H", "D", "A", "D", "B", "H", "G", "H", "E", "A", "D"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ"], "last_styles": ["ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ"], "last_roles": ["R7", "R3", "R7", "R5", "R5", "R6", "R8", "R8", "R2", "R4", "R6", "R2", "R4", "R1", "R1", "R3", "R3", "R6", "R5", "R4", "R2", "R4", "R5", "R6", "R5"], "recent_captions": ["มีใครเป็นเหมือนผมไหม นมโปรตีนตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปุยแสบปาก พริกผัดน้ำมันมะกอก Vegen ราคา ราคาแค่ 263 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น กรุงเทพ/ตจว.❤️ทุเรียนหมอนทองระยอง-จัน แท้💯พรี ราคาแค่ 415 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เซ็ตคู่ น้ำพริกไข่ปูม้า + น้ำพริกเนื้อปูม้า ราคาแค่ 304 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Official 🔥 KETO Wholesweet ราคาแค่ 151 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูแดดเดียว หมูเบทาโกรเกรดA ไม่ใส่สารกันบูด ไ ราคาแค่ 92 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 532 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดีมาก ปลาสลิดไข่ - กรัม📌ซื้อ2แพคคุ้มกว่าจ้ ราคาแค่ 200 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Llamito ผงมัทฉะ ออร์แกนิค Matcha ราคาแค่ 449 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อุดมสุข น้ำพริกอกไก่คลีน น้ำพริกอกไก่ น้ำพริก ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ แว่นตากันแดด ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เต้าหู้เฮียแว่น เต้าหู้เนื้อครีมคัสตาร์ด กรอบ ราคาแค่ 175 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง กระปุก แซลมอน ราคาแค่ 1089 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 283 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น *แซลมอนชาคริต* ชิ้น ส่งแช่แข็งฟรี -เนื้อแซลมอ ราคาแค่ 3099 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ก Muek Groob หมึกกรุบ ราคาแค่ 270 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูสามชั้นแดดเดียวไร้หนัง สะอาด ปลอดภัย ไม่ใส ราคาแค่ 152 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วยลดยากินน้ำหวานจุกจิกได้เยอะ แคลคุมง่ายอิ่มท้องนาน แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชุด ขวด นมแดรี่โฮมไฮโปรตีน สูตรแลคโตสฟรี ราคาแค่ 300 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มันหนึบญี่ปุ่น เบนิฮารุกะ หวานธรรมชาติ ไม่ใส่ ราคาแค่ 272 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น 🦐 กุ้งแม่น้ำไซส์จัมโป้ -7ตัวโล กุ้งตัวใหญ่ๆ ราคาแค่ 280 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เมล็ดเจีย Organic มี อย.คัดพิเศษ ราคาแค่ 130 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ถูกที่สุด Bertolli Extra Virgin ราคาแค่ 442 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 529 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ขนมเปี๊ยะไส้ทะลัก ไข่แดงเค็ม ใบ มีให้เลือก ราคาแค่ 139 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 1112 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Teelek Nougat -นูกัตถุงใหญ่ ชิ้น ราคาแค่ 250 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Country Sourdough Bread ขนมปังซาวโดว์โฮมเมด ราคาแค่ 182 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2248,16 +2248,141 @@
           <t>https://s.shopee.co.th/9AM2jit34K</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0h-mcpd1y74lysm7e.webp</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
           <t>done 2026-06-17 06:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>2</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>(มาใหม่)ดูไบคิมบับ ดูไบคุกกี้ชิววี่ เวฟไฟอ่อน10-15วิ ก่อนทาน เพิ่มความฉ่ำ ความยืด ยิ่งอร่อยยิ่งฟิน ตุ๊กกี้ตัวแสบ ราคา 129.00 บาท</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/W46TihThK</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mm00dhdvnqbpce.webp</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>done 2026-06-19 06:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>10</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>นมแพะ Smart Goat 3 ลัง - นมเเพะ ขับถ่ายดี สารอาหารสูง สูตร มัลติวิตามิน &amp; Omega ราคา 2180.00 บาท</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8ATXc38AC9</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasl-maayycy88cayfa.webp</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>done 2026-06-19 06:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>7</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>สลิดติดปาก ปลาสลิดแดดเดียว 5-6 ตัว/โล | ปลาสลิดไข่บางบ่อ ตัวโต สด สะอาด เนื้อแน่นหอมมัน ราคา 469.00 บาท</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4ftfRc0nMj</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mgvmi6civ40e0a.webp</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>done 2026-06-19 06:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>9</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>(ซื้อ 1 แถม 2)Matcha Japan ผงมัทฉะ ออร์แกนิค (Organic Matcha Powder) ขนาด 300g ขนาด ไม่ผสมแป้ง ไม่ผสมน้ำตาล ทานง่ายไม่ขม ราคา 351.00 บาท</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1BJnGu1X1D</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-7ren5-mdu2gpkdaiop19.webp</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>done 2026-06-19 06:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>5</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>น้ำพริกปูม้า(เจ๊เล็กน้ำพริกปูม้า),ฮาลาลฟู๊ด,มี6สูตร มันปูม้า/ไข่ปูม้า/เนื้อปูม้า/สไปซี่/ไข่เผ็ดน้อย ราคา 147.00 บาท</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/80A7PfAPBU</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasl-m5phtrsv3qy25c.webp</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>done 2026-06-19 06:24</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2411,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["G", "G", "C", "D", "H", "E", "G", "B", "H", "F", "A", "D", "A", "C", "H", "A", "H", "G", "E", "H", "D", "A", "D", "B", "H", "G", "H", "E", "A", "D"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ"], "last_styles": ["ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ"], "last_roles": ["R7", "R3", "R7", "R5", "R5", "R6", "R8", "R8", "R2", "R4", "R6", "R2", "R4", "R1", "R1", "R3", "R3", "R6", "R5", "R4", "R2", "R4", "R5", "R6", "R5"], "recent_captions": ["มีใครเป็นเหมือนผมไหม นมโปรตีนตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปุยแสบปาก พริกผัดน้ำมันมะกอก Vegen ราคา ราคาแค่ 263 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น กรุงเทพ/ตจว.❤️ทุเรียนหมอนทองระยอง-จัน แท้💯พรี ราคาแค่ 415 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เซ็ตคู่ น้ำพริกไข่ปูม้า + น้ำพริกเนื้อปูม้า ราคาแค่ 304 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Official 🔥 KETO Wholesweet ราคาแค่ 151 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูแดดเดียว หมูเบทาโกรเกรดA ไม่ใส่สารกันบูด ไ ราคาแค่ 92 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 532 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดีมาก ปลาสลิดไข่ - กรัม📌ซื้อ2แพคคุ้มกว่าจ้ ราคาแค่ 200 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Llamito ผงมัทฉะ ออร์แกนิค Matcha ราคาแค่ 449 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อุดมสุข น้ำพริกอกไก่คลีน น้ำพริกอกไก่ น้ำพริก ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ แว่นตากันแดด ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เต้าหู้เฮียแว่น เต้าหู้เนื้อครีมคัสตาร์ด กรอบ ราคาแค่ 175 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง กระปุก แซลมอน ราคาแค่ 1089 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 283 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น *แซลมอนชาคริต* ชิ้น ส่งแช่แข็งฟรี -เนื้อแซลมอ ราคาแค่ 3099 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ก Muek Groob หมึกกรุบ ราคาแค่ 270 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูสามชั้นแดดเดียวไร้หนัง สะอาด ปลอดภัย ไม่ใส ราคาแค่ 152 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วยลดยากินน้ำหวานจุกจิกได้เยอะ แคลคุมง่ายอิ่มท้องนาน แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชุด ขวด นมแดรี่โฮมไฮโปรตีน สูตรแลคโตสฟรี ราคาแค่ 300 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มันหนึบญี่ปุ่น เบนิฮารุกะ หวานธรรมชาติ ไม่ใส่ ราคาแค่ 272 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น 🦐 กุ้งแม่น้ำไซส์จัมโป้ -7ตัวโล กุ้งตัวใหญ่ๆ ราคาแค่ 280 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เมล็ดเจีย Organic มี อย.คัดพิเศษ ราคาแค่ 130 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ถูกที่สุด Bertolli Extra Virgin ราคาแค่ 442 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 529 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ขนมเปี๊ยะไส้ทะลัก ไข่แดงเค็ม ใบ มีให้เลือก ราคาแค่ 139 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 1112 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Teelek Nougat -นูกัตถุงใหญ่ ชิ้น ราคาแค่ 250 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Country Sourdough Bread ขนมปังซาวโดว์โฮมเมด ราคาแค่ 182 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇"]}</t>
+          <t>{"last_personas": ["G", "G", "C", "D", "H", "E", "G", "B", "H", "F", "A", "D", "A", "C", "H", "A", "H", "G", "E", "H", "D", "A", "D", "B", "H", "G", "H", "E", "A", "D", "F", "E", "A", "D", "E"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ..."], "last_styles": ["ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)"], "last_roles": ["R7", "R3", "R7", "R5", "R5", "R6", "R8", "R8", "R2", "R4", "R6", "R2", "R4", "R1", "R1", "R3", "R3", "R6", "R5", "R4", "R2", "R4", "R5", "R6", "R5", "R4", "R4", "R7", "R6", "R2"], "recent_captions": ["มีใครเป็นเหมือนผมไหม นมโปรตีนตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปุยแสบปาก พริกผัดน้ำมันมะกอก Vegen ราคา ราคาแค่ 263 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น กรุงเทพ/ตจว.❤️ทุเรียนหมอนทองระยอง-จัน แท้💯พรี ราคาแค่ 415 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เซ็ตคู่ น้ำพริกไข่ปูม้า + น้ำพริกเนื้อปูม้า ราคาแค่ 304 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Official 🔥 KETO Wholesweet ราคาแค่ 151 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูแดดเดียว หมูเบทาโกรเกรดA ไม่ใส่สารกันบูด ไ ราคาแค่ 92 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 532 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดีมาก ปลาสลิดไข่ - กรัม📌ซื้อ2แพคคุ้มกว่าจ้ ราคาแค่ 200 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Llamito ผงมัทฉะ ออร์แกนิค Matcha ราคาแค่ 449 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อุดมสุข น้ำพริกอกไก่คลีน น้ำพริกอกไก่ น้ำพริก ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ แว่นตากันแดด ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เต้าหู้เฮียแว่น เต้าหู้เนื้อครีมคัสตาร์ด กรอบ ราคาแค่ 175 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง กระปุก แซลมอน ราคาแค่ 1089 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 283 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น *แซลมอนชาคริต* ชิ้น ส่งแช่แข็งฟรี -เนื้อแซลมอ ราคาแค่ 3099 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ก Muek Groob หมึกกรุบ ราคาแค่ 270 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูสามชั้นแดดเดียวไร้หนัง สะอาด ปลอดภัย ไม่ใส ราคาแค่ 152 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วยลดยากินน้ำหวานจุกจิกได้เยอะ แคลคุมง่ายอิ่มท้องนาน แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชุด ขวด นมแดรี่โฮมไฮโปรตีน สูตรแลคโตสฟรี ราคาแค่ 300 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มันหนึบญี่ปุ่น เบนิฮารุกะ หวานธรรมชาติ ไม่ใส่ ราคาแค่ 272 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น 🦐 กุ้งแม่น้ำไซส์จัมโป้ -7ตัวโล กุ้งตัวใหญ่ๆ ราคาแค่ 280 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เมล็ดเจีย Organic มี อย.คัดพิเศษ ราคาแค่ 130 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ถูกที่สุด Bertolli Extra Virgin ราคาแค่ 442 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 529 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ขนมเปี๊ยะไส้ทะลัก ไข่แดงเค็ม ใบ มีให้เลือก ราคาแค่ 139 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 1112 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Teelek Nougat -นูกัตถุงใหญ่ ชิ้น ราคาแค่ 250 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Country Sourdough Bread ขนมปังซาวโดว์โฮมเมด ราคาแค่ 182 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มาใหม่ดูไบคิมบับ ดูไบคุกกี้ชิววี่ เวฟไฟอ่อน10 ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง นมแพะ Smart Goat ลัง ราคาแค่ 2180 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สลิดติดปาก ปลาสลิดแดดเดียว -/โล | ราคาแค่ 469 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซื้อ แถม Matcha Japan ราคาแค่ 351 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกปูม้าเจ๊เล็กน้ำพริกปูม้า,ฮาลาลฟู๊ด,มี6 ราคาแค่ 147 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2373,16 +2373,141 @@
           <t>https://s.shopee.co.th/80A7PfAPBU</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasl-m5phtrsv3qy25c.webp</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
           <t>done 2026-06-19 06:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>19</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>ICHITAN อิชิตัน น้ำด่าง ผสมวิตามินบีรวม ขนาดใหญ่ 550 ml. 1 ลัง (24 ขวด) รวมจัดส่ง ราคา 480.00 บาท</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9AM4ngSAXx</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ras9-m3byqpp14oa0c1.webp</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>done 2026-06-20 05:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>13</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>พร้อมส่งในไทย Marukyu​ Koyamaen​ ผงมัทฉะ​ มารุคิวของแท้จากญี่ปุ่น​ Matcha​ มัทฉะยี่ห้อดังจากอูจิ ราคา 760.00 บาท</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6VLJclpvLq</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mn5j25gwgmx2ed.webp</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>done 2026-06-20 05:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>1</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Kanbayashi Shunsho.มัทฉะ Matcha ZUIHO/ชาเขียว/ชาเขียวมัทฉะ/ผงมัทฉะ/ลูกร่อนผงมัทฉะ/มัทฉะโทนถั่ว ราคา 1048.00 บาท</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4qD5dYKnKI</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasi-m76lcjji3bcfb4.webp</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>done 2026-06-20 05:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>19</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>หมูเเดดเดียว 500 กรัม เจ๊ติ๋ม ตลาด อ.ต.ก.เจ้าเก่า (30ปี) "สูตรอร่อยไม่มีใครเหมือน" ราคา 194.00 บาท</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8fPoCzE2Lb</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/3f7c3f4a61b0bef5b99b1041e212dfe4.webp</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>done 2026-06-20 05:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>12</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>ตราฉัตร 5 กิโล ข้าวหอมมะลิใหม่ ข้าวหอมมะลิแท้ ตราฉัตร 5kg. (หอม นุ่ม ตลอดปี) ข้าวหอมผสม ข้าวขาว หุงอร่อย หุงขึ้นหม้อ ราคา 145.00 บาท</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4AxOqdHAb1</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-8260m-mkdsz738rxtu0a.webp</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>done 2026-06-20 05:38</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2536,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["G", "G", "C", "D", "H", "E", "G", "B", "H", "F", "A", "D", "A", "C", "H", "A", "H", "G", "E", "H", "D", "A", "D", "B", "H", "G", "H", "E", "A", "D", "F", "E", "A", "D", "E"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ..."], "last_styles": ["ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)"], "last_roles": ["R7", "R3", "R7", "R5", "R5", "R6", "R8", "R8", "R2", "R4", "R6", "R2", "R4", "R1", "R1", "R3", "R3", "R6", "R5", "R4", "R2", "R4", "R5", "R6", "R5", "R4", "R4", "R7", "R6", "R2"], "recent_captions": ["มีใครเป็นเหมือนผมไหม นมโปรตีนตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปุยแสบปาก พริกผัดน้ำมันมะกอก Vegen ราคา ราคาแค่ 263 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น กรุงเทพ/ตจว.❤️ทุเรียนหมอนทองระยอง-จัน แท้💯พรี ราคาแค่ 415 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เซ็ตคู่ น้ำพริกไข่ปูม้า + น้ำพริกเนื้อปูม้า ราคาแค่ 304 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Official 🔥 KETO Wholesweet ราคาแค่ 151 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูแดดเดียว หมูเบทาโกรเกรดA ไม่ใส่สารกันบูด ไ ราคาแค่ 92 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 532 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดีมาก ปลาสลิดไข่ - กรัม📌ซื้อ2แพคคุ้มกว่าจ้ ราคาแค่ 200 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Llamito ผงมัทฉะ ออร์แกนิค Matcha ราคาแค่ 449 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อุดมสุข น้ำพริกอกไก่คลีน น้ำพริกอกไก่ น้ำพริก ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ แว่นตากันแดด ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เต้าหู้เฮียแว่น เต้าหู้เนื้อครีมคัสตาร์ด กรอบ ราคาแค่ 175 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง กระปุก แซลมอน ราคาแค่ 1089 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 283 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น *แซลมอนชาคริต* ชิ้น ส่งแช่แข็งฟรี -เนื้อแซลมอ ราคาแค่ 3099 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ก Muek Groob หมึกกรุบ ราคาแค่ 270 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูสามชั้นแดดเดียวไร้หนัง สะอาด ปลอดภัย ไม่ใส ราคาแค่ 152 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วยลดยากินน้ำหวานจุกจิกได้เยอะ แคลคุมง่ายอิ่มท้องนาน แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชุด ขวด นมแดรี่โฮมไฮโปรตีน สูตรแลคโตสฟรี ราคาแค่ 300 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มันหนึบญี่ปุ่น เบนิฮารุกะ หวานธรรมชาติ ไม่ใส่ ราคาแค่ 272 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น 🦐 กุ้งแม่น้ำไซส์จัมโป้ -7ตัวโล กุ้งตัวใหญ่ๆ ราคาแค่ 280 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เมล็ดเจีย Organic มี อย.คัดพิเศษ ราคาแค่ 130 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ถูกที่สุด Bertolli Extra Virgin ราคาแค่ 442 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 529 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ขนมเปี๊ยะไส้ทะลัก ไข่แดงเค็ม ใบ มีให้เลือก ราคาแค่ 139 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 1112 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Teelek Nougat -นูกัตถุงใหญ่ ชิ้น ราคาแค่ 250 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Country Sourdough Bread ขนมปังซาวโดว์โฮมเมด ราคาแค่ 182 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มาใหม่ดูไบคิมบับ ดูไบคุกกี้ชิววี่ เวฟไฟอ่อน10 ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง นมแพะ Smart Goat ลัง ราคาแค่ 2180 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สลิดติดปาก ปลาสลิดแดดเดียว -/โล | ราคาแค่ 469 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซื้อ แถม Matcha Japan ราคาแค่ 351 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกปูม้าเจ๊เล็กน้ำพริกปูม้า,ฮาลาลฟู๊ด,มี6 ราคาแค่ 147 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇"]}</t>
+          <t>{"last_personas": ["G", "G", "C", "D", "H", "E", "G", "B", "H", "F", "A", "D", "A", "C", "H", "A", "H", "G", "E", "H", "D", "A", "D", "B", "H", "G", "H", "E", "A", "D", "F", "E", "A", "D", "E", "A", "C", "E", "F", "E"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ"], "last_styles": ["ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม"], "last_roles": ["R7", "R3", "R7", "R5", "R5", "R6", "R8", "R8", "R2", "R4", "R6", "R2", "R4", "R1", "R1", "R3", "R3", "R6", "R5", "R4", "R2", "R4", "R5", "R6", "R5", "R4", "R4", "R7", "R6", "R2", "R5", "R8", "R8", "R7", "R4"], "recent_captions": ["มีใครเป็นเหมือนผมไหม นมโปรตีนตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปุยแสบปาก พริกผัดน้ำมันมะกอก Vegen ราคา ราคาแค่ 263 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น กรุงเทพ/ตจว.❤️ทุเรียนหมอนทองระยอง-จัน แท้💯พรี ราคาแค่ 415 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เซ็ตคู่ น้ำพริกไข่ปูม้า + น้ำพริกเนื้อปูม้า ราคาแค่ 304 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Official 🔥 KETO Wholesweet ราคาแค่ 151 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูแดดเดียว หมูเบทาโกรเกรดA ไม่ใส่สารกันบูด ไ ราคาแค่ 92 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 532 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดีมาก ปลาสลิดไข่ - กรัม📌ซื้อ2แพคคุ้มกว่าจ้ ราคาแค่ 200 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Llamito ผงมัทฉะ ออร์แกนิค Matcha ราคาแค่ 449 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อุดมสุข น้ำพริกอกไก่คลีน น้ำพริกอกไก่ น้ำพริก ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ แว่นตากันแดด ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เต้าหู้เฮียแว่น เต้าหู้เนื้อครีมคัสตาร์ด กรอบ ราคาแค่ 175 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง กระปุก แซลมอน ราคาแค่ 1089 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 283 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น *แซลมอนชาคริต* ชิ้น ส่งแช่แข็งฟรี -เนื้อแซลมอ ราคาแค่ 3099 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ก Muek Groob หมึกกรุบ ราคาแค่ 270 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูสามชั้นแดดเดียวไร้หนัง สะอาด ปลอดภัย ไม่ใส ราคาแค่ 152 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วยลดยากินน้ำหวานจุกจิกได้เยอะ แคลคุมง่ายอิ่มท้องนาน แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชุด ขวด นมแดรี่โฮมไฮโปรตีน สูตรแลคโตสฟรี ราคาแค่ 300 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มันหนึบญี่ปุ่น เบนิฮารุกะ หวานธรรมชาติ ไม่ใส่ ราคาแค่ 272 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น 🦐 กุ้งแม่น้ำไซส์จัมโป้ -7ตัวโล กุ้งตัวใหญ่ๆ ราคาแค่ 280 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เมล็ดเจีย Organic มี อย.คัดพิเศษ ราคาแค่ 130 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ถูกที่สุด Bertolli Extra Virgin ราคาแค่ 442 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 529 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ขนมเปี๊ยะไส้ทะลัก ไข่แดงเค็ม ใบ มีให้เลือก ราคาแค่ 139 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 1112 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Teelek Nougat -นูกัตถุงใหญ่ ชิ้น ราคาแค่ 250 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Country Sourdough Bread ขนมปังซาวโดว์โฮมเมด ราคาแค่ 182 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มาใหม่ดูไบคิมบับ ดูไบคุกกี้ชิววี่ เวฟไฟอ่อน10 ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง นมแพะ Smart Goat ลัง ราคาแค่ 2180 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สลิดติดปาก ปลาสลิดแดดเดียว -/โล | ราคาแค่ 469 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซื้อ แถม Matcha Japan ราคาแค่ 351 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกปูม้าเจ๊เล็กน้ำพริกปูม้า,ฮาลาลฟู๊ด,มี6 ราคาแค่ 147 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ICHITAN อิชิตัน น้ำด่าง ผสมวิตามินบีรวม ราคาแค่ 480 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ในไทย Marukyu​ Koyamaen​ ผงมัทฉะ​ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ Kanbayashi Shunsho.มัทฉะ Matcha ZUIHO/ชาเขียว ราคาแค่ 1048 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูเเดดเดียว กรัม เจ๊ติ๋ม ตลาด ราคาแค่ 194 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ตราฉัตร กิโล ข้าวหอมมะลิใหม่ ข้าวหอมมะลิแท้ ราคาแค่ 145 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2498,16 +2498,141 @@
           <t>https://s.shopee.co.th/4AxOqdHAb1</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/sg-11134201-8260m-mkdsz738rxtu0a.webp</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
           <t>done 2026-06-20 05:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>9</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1แถม1ขนมโมจิมีนม่วงญี่ปุ่น หอม หวาน มัน ราคา 98.00 บาท</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7KuQcRjWpZ</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mfun2mvlmk25c6.webp</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>done 2026-06-21 05:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>5</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Nao Matcha นาโอะ มัทฉะแท้ 100% เกรดพรีเมียมจากนิชิโอะ ญี่ปุ่น หอมนัว Nutty ไม่ขม ไม่ฝาด ขนาด 40g ราคา 290.00 บาท</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5VSmQuoqES</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztj-mn9qqsw8mtqab0.webp</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>done 2026-06-21 05:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>20</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Esan phasuab น้ำปลาร้าอีสานพาสวบ 3ขวด (ขวดละ350มล) หอมกลิ่นปลาร้าแท้ สูตรแซบนัว สำหรับส้มตำและอาหาร ราคา 180.00 บาท</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3g18FWNAGN</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7qukz-lhj88jai5qmrb3.webp</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>done 2026-06-21 05:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>14</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>นมเปรี้ยว ดัชมิลล์ ขนาด 180 ml เซต 5 แพ็ค มี 5 รสชาติ คละรสให้อย่างละ 1แพ็ค (4 กล่อง/แพ็ค) ราคา 250.00 บาท</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/902ebaZJA4</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasj-m0hc9m3k5g3e37.webp</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>done 2026-06-21 05:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>18</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>แคบหมูไร้มัน แคปหมูไร้มัน 1kg. 500g. ราคา 219.00 บาท</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/30lRSLg5c1</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-macyz9o9j8fof8.webp</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>done 2026-06-21 05:49</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2661,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["G", "G", "C", "D", "H", "E", "G", "B", "H", "F", "A", "D", "A", "C", "H", "A", "H", "G", "E", "H", "D", "A", "D", "B", "H", "G", "H", "E", "A", "D", "F", "E", "A", "D", "E", "A", "C", "E", "F", "E"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ"], "last_styles": ["ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม"], "last_roles": ["R7", "R3", "R7", "R5", "R5", "R6", "R8", "R8", "R2", "R4", "R6", "R2", "R4", "R1", "R1", "R3", "R3", "R6", "R5", "R4", "R2", "R4", "R5", "R6", "R5", "R4", "R4", "R7", "R6", "R2", "R5", "R8", "R8", "R7", "R4"], "recent_captions": ["มีใครเป็นเหมือนผมไหม นมโปรตีนตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปุยแสบปาก พริกผัดน้ำมันมะกอก Vegen ราคา ราคาแค่ 263 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น กรุงเทพ/ตจว.❤️ทุเรียนหมอนทองระยอง-จัน แท้💯พรี ราคาแค่ 415 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เซ็ตคู่ น้ำพริกไข่ปูม้า + น้ำพริกเนื้อปูม้า ราคาแค่ 304 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Official 🔥 KETO Wholesweet ราคาแค่ 151 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูแดดเดียว หมูเบทาโกรเกรดA ไม่ใส่สารกันบูด ไ ราคาแค่ 92 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 532 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดีมาก ปลาสลิดไข่ - กรัม📌ซื้อ2แพคคุ้มกว่าจ้ ราคาแค่ 200 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Llamito ผงมัทฉะ ออร์แกนิค Matcha ราคาแค่ 449 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อุดมสุข น้ำพริกอกไก่คลีน น้ำพริกอกไก่ น้ำพริก ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ แว่นตากันแดด ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เต้าหู้เฮียแว่น เต้าหู้เนื้อครีมคัสตาร์ด กรอบ ราคาแค่ 175 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง กระปุก แซลมอน ราคาแค่ 1089 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 283 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น *แซลมอนชาคริต* ชิ้น ส่งแช่แข็งฟรี -เนื้อแซลมอ ราคาแค่ 3099 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ก Muek Groob หมึกกรุบ ราคาแค่ 270 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูสามชั้นแดดเดียวไร้หนัง สะอาด ปลอดภัย ไม่ใส ราคาแค่ 152 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วยลดยากินน้ำหวานจุกจิกได้เยอะ แคลคุมง่ายอิ่มท้องนาน แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชุด ขวด นมแดรี่โฮมไฮโปรตีน สูตรแลคโตสฟรี ราคาแค่ 300 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มันหนึบญี่ปุ่น เบนิฮารุกะ หวานธรรมชาติ ไม่ใส่ ราคาแค่ 272 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น 🦐 กุ้งแม่น้ำไซส์จัมโป้ -7ตัวโล กุ้งตัวใหญ่ๆ ราคาแค่ 280 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เมล็ดเจีย Organic มี อย.คัดพิเศษ ราคาแค่ 130 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ถูกที่สุด Bertolli Extra Virgin ราคาแค่ 442 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 529 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ขนมเปี๊ยะไส้ทะลัก ไข่แดงเค็ม ใบ มีให้เลือก ราคาแค่ 139 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 1112 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Teelek Nougat -นูกัตถุงใหญ่ ชิ้น ราคาแค่ 250 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Country Sourdough Bread ขนมปังซาวโดว์โฮมเมด ราคาแค่ 182 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มาใหม่ดูไบคิมบับ ดูไบคุกกี้ชิววี่ เวฟไฟอ่อน10 ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง นมแพะ Smart Goat ลัง ราคาแค่ 2180 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สลิดติดปาก ปลาสลิดแดดเดียว -/โล | ราคาแค่ 469 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซื้อ แถม Matcha Japan ราคาแค่ 351 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกปูม้าเจ๊เล็กน้ำพริกปูม้า,ฮาลาลฟู๊ด,มี6 ราคาแค่ 147 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ICHITAN อิชิตัน น้ำด่าง ผสมวิตามินบีรวม ราคาแค่ 480 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ในไทย Marukyu​ Koyamaen​ ผงมัทฉะ​ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ Kanbayashi Shunsho.มัทฉะ Matcha ZUIHO/ชาเขียว ราคาแค่ 1048 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูเเดดเดียว กรัม เจ๊ติ๋ม ตลาด ราคาแค่ 194 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ตราฉัตร กิโล ข้าวหอมมะลิใหม่ ข้าวหอมมะลิแท้ ราคาแค่ 145 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇"]}</t>
+          <t>{"last_personas": ["G", "G", "C", "D", "H", "E", "G", "B", "H", "F", "A", "D", "A", "C", "H", "A", "H", "G", "E", "H", "D", "A", "D", "B", "H", "G", "H", "E", "A", "D", "F", "E", "A", "D", "E", "A", "C", "E", "F", "E", "A", "A", "E", "A", "B"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ..."], "last_styles": ["ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ"], "last_roles": ["R7", "R3", "R7", "R5", "R5", "R6", "R8", "R8", "R2", "R4", "R6", "R2", "R4", "R1", "R1", "R3", "R3", "R6", "R5", "R4", "R2", "R4", "R5", "R6", "R5", "R4", "R4", "R7", "R6", "R2", "R5", "R8", "R8", "R7", "R4", "R6", "R5", "R7", "R6", "R2"], "recent_captions": ["มีใครเป็นเหมือนผมไหม นมโปรตีนตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปุยแสบปาก พริกผัดน้ำมันมะกอก Vegen ราคา ราคาแค่ 263 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น กรุงเทพ/ตจว.❤️ทุเรียนหมอนทองระยอง-จัน แท้💯พรี ราคาแค่ 415 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เซ็ตคู่ น้ำพริกไข่ปูม้า + น้ำพริกเนื้อปูม้า ราคาแค่ 304 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Official 🔥 KETO Wholesweet ราคาแค่ 151 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูแดดเดียว หมูเบทาโกรเกรดA ไม่ใส่สารกันบูด ไ ราคาแค่ 92 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 532 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดีมาก ปลาสลิดไข่ - กรัม📌ซื้อ2แพคคุ้มกว่าจ้ ราคาแค่ 200 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Llamito ผงมัทฉะ ออร์แกนิค Matcha ราคาแค่ 449 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อุดมสุข น้ำพริกอกไก่คลีน น้ำพริกอกไก่ น้ำพริก ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ แว่นตากันแดด ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เต้าหู้เฮียแว่น เต้าหู้เนื้อครีมคัสตาร์ด กรอบ ราคาแค่ 175 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง กระปุก แซลมอน ราคาแค่ 1089 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 283 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น *แซลมอนชาคริต* ชิ้น ส่งแช่แข็งฟรี -เนื้อแซลมอ ราคาแค่ 3099 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ก Muek Groob หมึกกรุบ ราคาแค่ 270 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูสามชั้นแดดเดียวไร้หนัง สะอาด ปลอดภัย ไม่ใส ราคาแค่ 152 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วยลดยากินน้ำหวานจุกจิกได้เยอะ แคลคุมง่ายอิ่มท้องนาน แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชุด ขวด นมแดรี่โฮมไฮโปรตีน สูตรแลคโตสฟรี ราคาแค่ 300 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มันหนึบญี่ปุ่น เบนิฮารุกะ หวานธรรมชาติ ไม่ใส่ ราคาแค่ 272 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น 🦐 กุ้งแม่น้ำไซส์จัมโป้ -7ตัวโล กุ้งตัวใหญ่ๆ ราคาแค่ 280 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เมล็ดเจีย Organic มี อย.คัดพิเศษ ราคาแค่ 130 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ถูกที่สุด Bertolli Extra Virgin ราคาแค่ 442 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 529 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ขนมเปี๊ยะไส้ทะลัก ไข่แดงเค็ม ใบ มีให้เลือก ราคาแค่ 139 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 1112 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Teelek Nougat -นูกัตถุงใหญ่ ชิ้น ราคาแค่ 250 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Country Sourdough Bread ขนมปังซาวโดว์โฮมเมด ราคาแค่ 182 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มาใหม่ดูไบคิมบับ ดูไบคุกกี้ชิววี่ เวฟไฟอ่อน10 ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง นมแพะ Smart Goat ลัง ราคาแค่ 2180 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สลิดติดปาก ปลาสลิดแดดเดียว -/โล | ราคาแค่ 469 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซื้อ แถม Matcha Japan ราคาแค่ 351 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกปูม้าเจ๊เล็กน้ำพริกปูม้า,ฮาลาลฟู๊ด,มี6 ราคาแค่ 147 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ICHITAN อิชิตัน น้ำด่าง ผสมวิตามินบีรวม ราคาแค่ 480 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ในไทย Marukyu​ Koyamaen​ ผงมัทฉะ​ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ Kanbayashi Shunsho.มัทฉะ Matcha ZUIHO/ชาเขียว ราคาแค่ 1048 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูเเดดเดียว กรัม เจ๊ติ๋ม ตลาด ราคาแค่ 194 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ตราฉัตร กิโล ข้าวหอมมะลิใหม่ ข้าวหอมมะลิแท้ ราคาแค่ 145 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถม1ขนมโมจิมีนม่วงญี่ปุ่น หอม หวาน มัน ราคาแค่ 98 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Nao Matcha นาโอะ มัทฉะแท้ ราคาแค่ 290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ของกินตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Esan phasuab น้ำปลาร้าอีสานพาสวบ 3ขวด ราคาแค่ 180 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังออกกำลังกายเสร็จเหนื่อยๆ บางวันเคี้ยวอกไก่ไม่ไหวจริงๆ ได้ตัวนี้ดื่มแทนง่ายมาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น นมเปรี้ยว ดัชมิลล์ ขนาด เซต ราคาแค่ 250 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แคบหมูไร้มัน แคปหมูไร้มัน . . ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2623,16 +2623,141 @@
           <t>https://s.shopee.co.th/30lRSLg5c1</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-macyz9o9j8fof8.webp</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
           <t>done 2026-06-21 05:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>6</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>กาแฟดำเพื่อสุขภาพ ไม่มีน้ำตาล คั่วสด บดละเอียด ผงสกัดกาแฟละลายน้ำร้อนทันที พร้อมดื่ม Healthy Black Coffee | ร้านกาแฟ 89 ราคา 99.00 บาท</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6VLHYpGKZE</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98r-ly99vph2c04pdc.webp</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>done 2026-06-22 05:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>9</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>ทุเรียนจันทบุรีเนื้อพรีเมียม ยอดขายเยอะที่สุดทุเรียนหมอนทอง คัดเนื้อเทพไม่เน้นทรง เนื้อเหลือง เนื้อตลาดที่คนไทยกิน ราคา 621.00 บาท</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2LVibAwjEv</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rask-mabmx8hshx6278.webp</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>done 2026-06-22 05:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>14</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>พริกกากหมู เคี้ยวเพลินๆ(รสต้มยำ) ราคา 150.00 บาท</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5Apw2C68Zb</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mgl58k2i07ii90.webp</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>done 2026-06-22 05:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>19</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ 3.5 กก. ราคา 3700.00 บาท</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8pjEP0uUQS</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/f8fb32659a3650ce0dcc468f645e65be.webp</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>done 2026-06-22 05:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>16</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>[✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม] น้ำปลาร้าปรุงสุก ตราไมค์ 6 ขวด ขนาด 350 ml. (แซ่บไมค์) น้ำปลาร้า ปรุงสุก สูตรแซ่บทุกเมนู ราคา 245.00 บาท</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/60P31jKZ0f</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasj-mab0imamdy4f32.webp</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>done 2026-06-22 05:49</t>
         </is>
       </c>
     </row>
@@ -2661,7 +2786,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["G", "G", "C", "D", "H", "E", "G", "B", "H", "F", "A", "D", "A", "C", "H", "A", "H", "G", "E", "H", "D", "A", "D", "B", "H", "G", "H", "E", "A", "D", "F", "E", "A", "D", "E", "A", "C", "E", "F", "E", "A", "A", "E", "A", "B"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ..."], "last_styles": ["ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ"], "last_roles": ["R7", "R3", "R7", "R5", "R5", "R6", "R8", "R8", "R2", "R4", "R6", "R2", "R4", "R1", "R1", "R3", "R3", "R6", "R5", "R4", "R2", "R4", "R5", "R6", "R5", "R4", "R4", "R7", "R6", "R2", "R5", "R8", "R8", "R7", "R4", "R6", "R5", "R7", "R6", "R2"], "recent_captions": ["มีใครเป็นเหมือนผมไหม นมโปรตีนตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปุยแสบปาก พริกผัดน้ำมันมะกอก Vegen ราคา ราคาแค่ 263 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น กรุงเทพ/ตจว.❤️ทุเรียนหมอนทองระยอง-จัน แท้💯พรี ราคาแค่ 415 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เซ็ตคู่ น้ำพริกไข่ปูม้า + น้ำพริกเนื้อปูม้า ราคาแค่ 304 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Official 🔥 KETO Wholesweet ราคาแค่ 151 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูแดดเดียว หมูเบทาโกรเกรดA ไม่ใส่สารกันบูด ไ ราคาแค่ 92 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 532 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดีมาก ปลาสลิดไข่ - กรัม📌ซื้อ2แพคคุ้มกว่าจ้ ราคาแค่ 200 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Llamito ผงมัทฉะ ออร์แกนิค Matcha ราคาแค่ 449 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อุดมสุข น้ำพริกอกไก่คลีน น้ำพริกอกไก่ น้ำพริก ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ แว่นตากันแดด ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เต้าหู้เฮียแว่น เต้าหู้เนื้อครีมคัสตาร์ด กรอบ ราคาแค่ 175 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง กระปุก แซลมอน ราคาแค่ 1089 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 283 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น *แซลมอนชาคริต* ชิ้น ส่งแช่แข็งฟรี -เนื้อแซลมอ ราคาแค่ 3099 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ก Muek Groob หมึกกรุบ ราคาแค่ 270 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูสามชั้นแดดเดียวไร้หนัง สะอาด ปลอดภัย ไม่ใส ราคาแค่ 152 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วยลดยากินน้ำหวานจุกจิกได้เยอะ แคลคุมง่ายอิ่มท้องนาน แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชุด ขวด นมแดรี่โฮมไฮโปรตีน สูตรแลคโตสฟรี ราคาแค่ 300 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มันหนึบญี่ปุ่น เบนิฮารุกะ หวานธรรมชาติ ไม่ใส่ ราคาแค่ 272 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น 🦐 กุ้งแม่น้ำไซส์จัมโป้ -7ตัวโล กุ้งตัวใหญ่ๆ ราคาแค่ 280 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เมล็ดเจีย Organic มี อย.คัดพิเศษ ราคาแค่ 130 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ถูกที่สุด Bertolli Extra Virgin ราคาแค่ 442 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 529 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ขนมเปี๊ยะไส้ทะลัก ไข่แดงเค็ม ใบ มีให้เลือก ราคาแค่ 139 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 1112 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Teelek Nougat -นูกัตถุงใหญ่ ชิ้น ราคาแค่ 250 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Country Sourdough Bread ขนมปังซาวโดว์โฮมเมด ราคาแค่ 182 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มาใหม่ดูไบคิมบับ ดูไบคุกกี้ชิววี่ เวฟไฟอ่อน10 ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง นมแพะ Smart Goat ลัง ราคาแค่ 2180 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สลิดติดปาก ปลาสลิดแดดเดียว -/โล | ราคาแค่ 469 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซื้อ แถม Matcha Japan ราคาแค่ 351 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกปูม้าเจ๊เล็กน้ำพริกปูม้า,ฮาลาลฟู๊ด,มี6 ราคาแค่ 147 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ICHITAN อิชิตัน น้ำด่าง ผสมวิตามินบีรวม ราคาแค่ 480 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ในไทย Marukyu​ Koyamaen​ ผงมัทฉะ​ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ Kanbayashi Shunsho.มัทฉะ Matcha ZUIHO/ชาเขียว ราคาแค่ 1048 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูเเดดเดียว กรัม เจ๊ติ๋ม ตลาด ราคาแค่ 194 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ตราฉัตร กิโล ข้าวหอมมะลิใหม่ ข้าวหอมมะลิแท้ ราคาแค่ 145 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถม1ขนมโมจิมีนม่วงญี่ปุ่น หอม หวาน มัน ราคาแค่ 98 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Nao Matcha นาโอะ มัทฉะแท้ ราคาแค่ 290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ของกินตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Esan phasuab น้ำปลาร้าอีสานพาสวบ 3ขวด ราคาแค่ 180 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังออกกำลังกายเสร็จเหนื่อยๆ บางวันเคี้ยวอกไก่ไม่ไหวจริงๆ ได้ตัวนี้ดื่มแทนง่ายมาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น นมเปรี้ยว ดัชมิลล์ ขนาด เซต ราคาแค่ 250 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แคบหมูไร้มัน แคปหมูไร้มัน . . ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇"]}</t>
+          <t>{"last_personas": ["G", "G", "C", "D", "H", "E", "G", "B", "H", "F", "A", "D", "A", "C", "H", "A", "H", "G", "E", "H", "D", "A", "D", "B", "H", "G", "H", "E", "A", "D", "F", "E", "A", "D", "E", "A", "C", "E", "F", "E", "A", "A", "E", "A", "B", "H", "B", "H", "F", "E"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ"], "last_styles": ["ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ"], "last_roles": ["R7", "R3", "R7", "R5", "R5", "R6", "R8", "R8", "R2", "R4", "R6", "R2", "R4", "R1", "R1", "R3", "R3", "R6", "R5", "R4", "R2", "R4", "R5", "R6", "R5", "R4", "R4", "R7", "R6", "R2", "R5", "R8", "R8", "R7", "R4", "R6", "R5", "R7", "R6", "R2", "R8", "R1", "R6", "R8", "R3"], "recent_captions": ["มีใครเป็นเหมือนผมไหม นมโปรตีนตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปุยแสบปาก พริกผัดน้ำมันมะกอก Vegen ราคา ราคาแค่ 263 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น กรุงเทพ/ตจว.❤️ทุเรียนหมอนทองระยอง-จัน แท้💯พรี ราคาแค่ 415 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เซ็ตคู่ น้ำพริกไข่ปูม้า + น้ำพริกเนื้อปูม้า ราคาแค่ 304 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Official 🔥 KETO Wholesweet ราคาแค่ 151 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูแดดเดียว หมูเบทาโกรเกรดA ไม่ใส่สารกันบูด ไ ราคาแค่ 92 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 532 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดีมาก ปลาสลิดไข่ - กรัม📌ซื้อ2แพคคุ้มกว่าจ้ ราคาแค่ 200 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Llamito ผงมัทฉะ ออร์แกนิค Matcha ราคาแค่ 449 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อุดมสุข น้ำพริกอกไก่คลีน น้ำพริกอกไก่ น้ำพริก ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ แว่นตากันแดด ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เต้าหู้เฮียแว่น เต้าหู้เนื้อครีมคัสตาร์ด กรอบ ราคาแค่ 175 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง กระปุก แซลมอน ราคาแค่ 1089 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 283 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น *แซลมอนชาคริต* ชิ้น ส่งแช่แข็งฟรี -เนื้อแซลมอ ราคาแค่ 3099 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ก Muek Groob หมึกกรุบ ราคาแค่ 270 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูสามชั้นแดดเดียวไร้หนัง สะอาด ปลอดภัย ไม่ใส ราคาแค่ 152 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วยลดยากินน้ำหวานจุกจิกได้เยอะ แคลคุมง่ายอิ่มท้องนาน แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชุด ขวด นมแดรี่โฮมไฮโปรตีน สูตรแลคโตสฟรี ราคาแค่ 300 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มันหนึบญี่ปุ่น เบนิฮารุกะ หวานธรรมชาติ ไม่ใส่ ราคาแค่ 272 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น 🦐 กุ้งแม่น้ำไซส์จัมโป้ -7ตัวโล กุ้งตัวใหญ่ๆ ราคาแค่ 280 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เมล็ดเจีย Organic มี อย.คัดพิเศษ ราคาแค่ 130 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ถูกที่สุด Bertolli Extra Virgin ราคาแค่ 442 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 529 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ขนมเปี๊ยะไส้ทะลัก ไข่แดงเค็ม ใบ มีให้เลือก ราคาแค่ 139 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 1112 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Teelek Nougat -นูกัตถุงใหญ่ ชิ้น ราคาแค่ 250 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Country Sourdough Bread ขนมปังซาวโดว์โฮมเมด ราคาแค่ 182 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มาใหม่ดูไบคิมบับ ดูไบคุกกี้ชิววี่ เวฟไฟอ่อน10 ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง นมแพะ Smart Goat ลัง ราคาแค่ 2180 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สลิดติดปาก ปลาสลิดแดดเดียว -/โล | ราคาแค่ 469 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซื้อ แถม Matcha Japan ราคาแค่ 351 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกปูม้าเจ๊เล็กน้ำพริกปูม้า,ฮาลาลฟู๊ด,มี6 ราคาแค่ 147 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ICHITAN อิชิตัน น้ำด่าง ผสมวิตามินบีรวม ราคาแค่ 480 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ในไทย Marukyu​ Koyamaen​ ผงมัทฉะ​ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ Kanbayashi Shunsho.มัทฉะ Matcha ZUIHO/ชาเขียว ราคาแค่ 1048 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูเเดดเดียว กรัม เจ๊ติ๋ม ตลาด ราคาแค่ 194 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ตราฉัตร กิโล ข้าวหอมมะลิใหม่ ข้าวหอมมะลิแท้ ราคาแค่ 145 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถม1ขนมโมจิมีนม่วงญี่ปุ่น หอม หวาน มัน ราคาแค่ 98 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Nao Matcha นาโอะ มัทฉะแท้ ราคาแค่ 290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ของกินตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Esan phasuab น้ำปลาร้าอีสานพาสวบ 3ขวด ราคาแค่ 180 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังออกกำลังกายเสร็จเหนื่อยๆ บางวันเคี้ยวอกไก่ไม่ไหวจริงๆ ได้ตัวนี้ดื่มแทนง่ายมาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น นมเปรี้ยว ดัชมิลล์ ขนาด เซต ราคาแค่ 250 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แคบหมูไร้มัน แคปหมูไร้มัน . . ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กาแฟดำเพื่อสุขภาพ ไม่มีน้ำตาล คั่วสด บดละเอีย ราคาแค่ 99 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ทุเรียนจันทบุรีเนื้อพรีเมียม ยอดขายเยอะที่สุด ราคาแค่ 621 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู เคี้ยวเพลินๆรสต้มยำ ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ . ราคาแค่ 3700 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม น้ำปลาร้าปรุงสุก ตราไม ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2748,16 +2748,141 @@
           <t>https://s.shopee.co.th/60P31jKZ0f</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasj-mab0imamdy4f32.webp</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
           <t>done 2026-06-22 05:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>14</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>แอปเปิ้ลแช่แข็งแห้งกรอบพรีเมี่ยมชิ้นไม่มีสารเติมแต่งขนมขบเคี้ยวผลไม้แห้งสําหรับผู้ใหญ่ของว่างเพื่อสุขภาพแบบสบาย ๆ ราคา 112.00 บาท</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6AiTE9uySD</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/cn-11134207-820l4-mn06agdyktfl55.webp</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>done 2026-06-23 06:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>8</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุนไพร รสน้ำพริกนรก แบบซอง ขนาด 100 กรัม 3 รสชาติ 1 ซอง Zalidpordeekum ราคา 155.00 บาท</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7VDqoXVW0v</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m863k6w28arga0.webp</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>done 2026-06-23 06:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>15</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวมากที่สุด ทุเรียนหมอนทองจันทบุรีแกะเนื้อ ราคา 542.00 บาท</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9fILOohMBk</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/4fb7d47caa67d61241a2af680a4ad3a6.webp</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>done 2026-06-23 06:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>1</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา 173.00 บาท</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6VLJckD4gB</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztk-mjrwzih0tts540.webp</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>done 2026-06-23 06:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>18</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>เนยถั่วรวม Chocolate Nuts Butter รสช็อคโกแลต ขนาด 220 g. | Paweenee’s ราคา 175.00 บาท</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/20suGfEdLr</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0j-mdoxiej3ykficb.webp</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>done 2026-06-23 06:06</t>
         </is>
       </c>
     </row>
@@ -2786,7 +2911,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["G", "G", "C", "D", "H", "E", "G", "B", "H", "F", "A", "D", "A", "C", "H", "A", "H", "G", "E", "H", "D", "A", "D", "B", "H", "G", "H", "E", "A", "D", "F", "E", "A", "D", "E", "A", "C", "E", "F", "E", "A", "A", "E", "A", "B", "H", "B", "H", "F", "E"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ"], "last_styles": ["ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ"], "last_roles": ["R7", "R3", "R7", "R5", "R5", "R6", "R8", "R8", "R2", "R4", "R6", "R2", "R4", "R1", "R1", "R3", "R3", "R6", "R5", "R4", "R2", "R4", "R5", "R6", "R5", "R4", "R4", "R7", "R6", "R2", "R5", "R8", "R8", "R7", "R4", "R6", "R5", "R7", "R6", "R2", "R8", "R1", "R6", "R8", "R3"], "recent_captions": ["มีใครเป็นเหมือนผมไหม นมโปรตีนตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปุยแสบปาก พริกผัดน้ำมันมะกอก Vegen ราคา ราคาแค่ 263 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น กรุงเทพ/ตจว.❤️ทุเรียนหมอนทองระยอง-จัน แท้💯พรี ราคาแค่ 415 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เซ็ตคู่ น้ำพริกไข่ปูม้า + น้ำพริกเนื้อปูม้า ราคาแค่ 304 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Official 🔥 KETO Wholesweet ราคาแค่ 151 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูแดดเดียว หมูเบทาโกรเกรดA ไม่ใส่สารกันบูด ไ ราคาแค่ 92 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 532 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดีมาก ปลาสลิดไข่ - กรัม📌ซื้อ2แพคคุ้มกว่าจ้ ราคาแค่ 200 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Llamito ผงมัทฉะ ออร์แกนิค Matcha ราคาแค่ 449 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อุดมสุข น้ำพริกอกไก่คลีน น้ำพริกอกไก่ น้ำพริก ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ แว่นตากันแดด ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เต้าหู้เฮียแว่น เต้าหู้เนื้อครีมคัสตาร์ด กรอบ ราคาแค่ 175 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง กระปุก แซลมอน ราคาแค่ 1089 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 283 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น *แซลมอนชาคริต* ชิ้น ส่งแช่แข็งฟรี -เนื้อแซลมอ ราคาแค่ 3099 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ก Muek Groob หมึกกรุบ ราคาแค่ 270 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูสามชั้นแดดเดียวไร้หนัง สะอาด ปลอดภัย ไม่ใส ราคาแค่ 152 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วยลดยากินน้ำหวานจุกจิกได้เยอะ แคลคุมง่ายอิ่มท้องนาน แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชุด ขวด นมแดรี่โฮมไฮโปรตีน สูตรแลคโตสฟรี ราคาแค่ 300 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มันหนึบญี่ปุ่น เบนิฮารุกะ หวานธรรมชาติ ไม่ใส่ ราคาแค่ 272 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น 🦐 กุ้งแม่น้ำไซส์จัมโป้ -7ตัวโล กุ้งตัวใหญ่ๆ ราคาแค่ 280 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เมล็ดเจีย Organic มี อย.คัดพิเศษ ราคาแค่ 130 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ถูกที่สุด Bertolli Extra Virgin ราคาแค่ 442 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 529 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ขนมเปี๊ยะไส้ทะลัก ไข่แดงเค็ม ใบ มีให้เลือก ราคาแค่ 139 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 1112 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Teelek Nougat -นูกัตถุงใหญ่ ชิ้น ราคาแค่ 250 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Country Sourdough Bread ขนมปังซาวโดว์โฮมเมด ราคาแค่ 182 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มาใหม่ดูไบคิมบับ ดูไบคุกกี้ชิววี่ เวฟไฟอ่อน10 ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง นมแพะ Smart Goat ลัง ราคาแค่ 2180 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สลิดติดปาก ปลาสลิดแดดเดียว -/โล | ราคาแค่ 469 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซื้อ แถม Matcha Japan ราคาแค่ 351 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกปูม้าเจ๊เล็กน้ำพริกปูม้า,ฮาลาลฟู๊ด,มี6 ราคาแค่ 147 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ICHITAN อิชิตัน น้ำด่าง ผสมวิตามินบีรวม ราคาแค่ 480 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ในไทย Marukyu​ Koyamaen​ ผงมัทฉะ​ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ Kanbayashi Shunsho.มัทฉะ Matcha ZUIHO/ชาเขียว ราคาแค่ 1048 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูเเดดเดียว กรัม เจ๊ติ๋ม ตลาด ราคาแค่ 194 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ตราฉัตร กิโล ข้าวหอมมะลิใหม่ ข้าวหอมมะลิแท้ ราคาแค่ 145 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถม1ขนมโมจิมีนม่วงญี่ปุ่น หอม หวาน มัน ราคาแค่ 98 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Nao Matcha นาโอะ มัทฉะแท้ ราคาแค่ 290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ของกินตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Esan phasuab น้ำปลาร้าอีสานพาสวบ 3ขวด ราคาแค่ 180 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังออกกำลังกายเสร็จเหนื่อยๆ บางวันเคี้ยวอกไก่ไม่ไหวจริงๆ ได้ตัวนี้ดื่มแทนง่ายมาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น นมเปรี้ยว ดัชมิลล์ ขนาด เซต ราคาแค่ 250 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แคบหมูไร้มัน แคปหมูไร้มัน . . ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กาแฟดำเพื่อสุขภาพ ไม่มีน้ำตาล คั่วสด บดละเอีย ราคาแค่ 99 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ทุเรียนจันทบุรีเนื้อพรีเมียม ยอดขายเยอะที่สุด ราคาแค่ 621 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู เคี้ยวเพลินๆรสต้มยำ ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ . ราคาแค่ 3700 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม น้ำปลาร้าปรุงสุก ตราไม ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇"]}</t>
+          <t>{"last_personas": ["E", "G", "B", "H", "F", "A", "D", "A", "C", "H", "A", "H", "G", "E", "H", "D", "A", "D", "B", "H", "G", "H", "E", "A", "D", "F", "E", "A", "D", "E", "A", "C", "E", "F", "E", "A", "A", "E", "A", "B", "H", "B", "H", "F", "E", "D", "B", "F", "F", "E"], "last_hooks": ["มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ..."], "last_styles": ["มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)"], "last_roles": ["R7", "R3", "R7", "R5", "R5", "R6", "R8", "R8", "R2", "R4", "R6", "R2", "R4", "R1", "R1", "R3", "R3", "R6", "R5", "R4", "R2", "R4", "R5", "R6", "R5", "R4", "R4", "R7", "R6", "R2", "R5", "R8", "R8", "R7", "R4", "R6", "R5", "R7", "R6", "R2", "R8", "R1", "R6", "R8", "R3", "R4", "R2", "R7", "R6", "R7"], "recent_captions": ["มีใครเป็นเหมือนผมไหม นมโปรตีนตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปุยแสบปาก พริกผัดน้ำมันมะกอก Vegen ราคา ราคาแค่ 263 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น กรุงเทพ/ตจว.❤️ทุเรียนหมอนทองระยอง-จัน แท้💯พรี ราคาแค่ 415 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เซ็ตคู่ น้ำพริกไข่ปูม้า + น้ำพริกเนื้อปูม้า ราคาแค่ 304 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Official 🔥 KETO Wholesweet ราคาแค่ 151 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูแดดเดียว หมูเบทาโกรเกรดA ไม่ใส่สารกันบูด ไ ราคาแค่ 92 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 532 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดีมาก ปลาสลิดไข่ - กรัม📌ซื้อ2แพคคุ้มกว่าจ้ ราคาแค่ 200 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Llamito ผงมัทฉะ ออร์แกนิค Matcha ราคาแค่ 449 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อุดมสุข น้ำพริกอกไก่คลีน น้ำพริกอกไก่ น้ำพริก ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ แว่นตากันแดด ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เต้าหู้เฮียแว่น เต้าหู้เนื้อครีมคัสตาร์ด กรอบ ราคาแค่ 175 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง กระปุก แซลมอน ราคาแค่ 1089 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 283 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น *แซลมอนชาคริต* ชิ้น ส่งแช่แข็งฟรี -เนื้อแซลมอ ราคาแค่ 3099 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ก Muek Groob หมึกกรุบ ราคาแค่ 270 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูสามชั้นแดดเดียวไร้หนัง สะอาด ปลอดภัย ไม่ใส ราคาแค่ 152 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วยลดยากินน้ำหวานจุกจิกได้เยอะ แคลคุมง่ายอิ่มท้องนาน แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชุด ขวด นมแดรี่โฮมไฮโปรตีน สูตรแลคโตสฟรี ราคาแค่ 300 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มันหนึบญี่ปุ่น เบนิฮารุกะ หวานธรรมชาติ ไม่ใส่ ราคาแค่ 272 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น 🦐 กุ้งแม่น้ำไซส์จัมโป้ -7ตัวโล กุ้งตัวใหญ่ๆ ราคาแค่ 280 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เมล็ดเจีย Organic มี อย.คัดพิเศษ ราคาแค่ 130 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ถูกที่สุด Bertolli Extra Virgin ราคาแค่ 442 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 529 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ขนมเปี๊ยะไส้ทะลัก ไข่แดงเค็ม ใบ มีให้เลือก ราคาแค่ 139 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 1112 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Teelek Nougat -นูกัตถุงใหญ่ ชิ้น ราคาแค่ 250 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Country Sourdough Bread ขนมปังซาวโดว์โฮมเมด ราคาแค่ 182 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มาใหม่ดูไบคิมบับ ดูไบคุกกี้ชิววี่ เวฟไฟอ่อน10 ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง นมแพะ Smart Goat ลัง ราคาแค่ 2180 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สลิดติดปาก ปลาสลิดแดดเดียว -/โล | ราคาแค่ 469 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซื้อ แถม Matcha Japan ราคาแค่ 351 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกปูม้าเจ๊เล็กน้ำพริกปูม้า,ฮาลาลฟู๊ด,มี6 ราคาแค่ 147 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ICHITAN อิชิตัน น้ำด่าง ผสมวิตามินบีรวม ราคาแค่ 480 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ในไทย Marukyu​ Koyamaen​ ผงมัทฉะ​ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ Kanbayashi Shunsho.มัทฉะ Matcha ZUIHO/ชาเขียว ราคาแค่ 1048 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูเเดดเดียว กรัม เจ๊ติ๋ม ตลาด ราคาแค่ 194 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ตราฉัตร กิโล ข้าวหอมมะลิใหม่ ข้าวหอมมะลิแท้ ราคาแค่ 145 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถม1ขนมโมจิมีนม่วงญี่ปุ่น หอม หวาน มัน ราคาแค่ 98 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Nao Matcha นาโอะ มัทฉะแท้ ราคาแค่ 290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ของกินตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Esan phasuab น้ำปลาร้าอีสานพาสวบ 3ขวด ราคาแค่ 180 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังออกกำลังกายเสร็จเหนื่อยๆ บางวันเคี้ยวอกไก่ไม่ไหวจริงๆ ได้ตัวนี้ดื่มแทนง่ายมาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น นมเปรี้ยว ดัชมิลล์ ขนาด เซต ราคาแค่ 250 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แคบหมูไร้มัน แคปหมูไร้มัน . . ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กาแฟดำเพื่อสุขภาพ ไม่มีน้ำตาล คั่วสด บดละเอีย ราคาแค่ 99 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ทุเรียนจันทบุรีเนื้อพรีเมียม ยอดขายเยอะที่สุด ราคาแค่ 621 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู เคี้ยวเพลินๆรสต้มยำ ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ . ราคาแค่ 3700 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม น้ำปลาร้าปรุงสุก ตราไม ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ แอปเปิ้ลแช่แข็งแห้งกรอบพรีเมี่ยมชิ้นไม่มีสารเ ราคาแค่ 112 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุน ราคาแค่ 155 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2873,16 +2873,141 @@
           <t>https://s.shopee.co.th/20suGfEdLr</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0j-mdoxiej3ykficb.webp</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
           <t>done 2026-06-23 06:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>7</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไข่ฝนแรกล็อตสุดท้ายของปีนี้ ราคา 850.00 บาท</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1VwdfVn8Ft</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rash-m8x3w0uh4ci73e.webp</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>done 2026-06-24 05:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>14</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ไร้แมลง เนื้อนุ่ม ฉ่ำ ทอดง่าย ราคา 149.00 บาท</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2g8YznZTBU</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mm8rnpzzshs429.webp</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>done 2026-06-24 05:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>6</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ พร้อมส่ง📌 ราคา 80.00 บาท</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9zvBnPVuA0</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rash-m3hccjp1scl7d9.webp</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>done 2026-06-24 05:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>17</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>[พร้อมส่งในไทย]Marukyu Koyamaen Matcha มัทฉะมารุคิวโคยามะเอ็น สาหร่ายผู้ดี อูมามิ เกรดพิธีการญี่ปุ่น ราคา 1118.00 บาท</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/902ebFHsE7</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasj-m91el64l52bt32.webp</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>done 2026-06-24 05:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>10</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นใหญ่ เต็มคำ แซ่บ เปรี้ยวเผ็ดสะใจ มี2ขนาด 100g./400g. ราคา 365.00 บาท</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/20suGMieQS</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mnmij2prwhl2a7.webp</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>done 2026-06-24 05:52</t>
         </is>
       </c>
     </row>
@@ -2911,7 +3036,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["E", "G", "B", "H", "F", "A", "D", "A", "C", "H", "A", "H", "G", "E", "H", "D", "A", "D", "B", "H", "G", "H", "E", "A", "D", "F", "E", "A", "D", "E", "A", "C", "E", "F", "E", "A", "A", "E", "A", "B", "H", "B", "H", "F", "E", "D", "B", "F", "F", "E"], "last_hooks": ["มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ..."], "last_styles": ["มุกตลก", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)"], "last_roles": ["R7", "R3", "R7", "R5", "R5", "R6", "R8", "R8", "R2", "R4", "R6", "R2", "R4", "R1", "R1", "R3", "R3", "R6", "R5", "R4", "R2", "R4", "R5", "R6", "R5", "R4", "R4", "R7", "R6", "R2", "R5", "R8", "R8", "R7", "R4", "R6", "R5", "R7", "R6", "R2", "R8", "R1", "R6", "R8", "R3", "R4", "R2", "R7", "R6", "R7"], "recent_captions": ["มีใครเป็นเหมือนผมไหม นมโปรตีนตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปุยแสบปาก พริกผัดน้ำมันมะกอก Vegen ราคา ราคาแค่ 263 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น กรุงเทพ/ตจว.❤️ทุเรียนหมอนทองระยอง-จัน แท้💯พรี ราคาแค่ 415 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เซ็ตคู่ น้ำพริกไข่ปูม้า + น้ำพริกเนื้อปูม้า ราคาแค่ 304 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Official 🔥 KETO Wholesweet ราคาแค่ 151 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูแดดเดียว หมูเบทาโกรเกรดA ไม่ใส่สารกันบูด ไ ราคาแค่ 92 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 532 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดีมาก ปลาสลิดไข่ - กรัม📌ซื้อ2แพคคุ้มกว่าจ้ ราคาแค่ 200 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Llamito ผงมัทฉะ ออร์แกนิค Matcha ราคาแค่ 449 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อุดมสุข น้ำพริกอกไก่คลีน น้ำพริกอกไก่ น้ำพริก ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ แว่นตากันแดด ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เต้าหู้เฮียแว่น เต้าหู้เนื้อครีมคัสตาร์ด กรอบ ราคาแค่ 175 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง กระปุก แซลมอน ราคาแค่ 1089 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 283 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น *แซลมอนชาคริต* ชิ้น ส่งแช่แข็งฟรี -เนื้อแซลมอ ราคาแค่ 3099 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ก Muek Groob หมึกกรุบ ราคาแค่ 270 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูสามชั้นแดดเดียวไร้หนัง สะอาด ปลอดภัย ไม่ใส ราคาแค่ 152 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วยลดยากินน้ำหวานจุกจิกได้เยอะ แคลคุมง่ายอิ่มท้องนาน แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชุด ขวด นมแดรี่โฮมไฮโปรตีน สูตรแลคโตสฟรี ราคาแค่ 300 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มันหนึบญี่ปุ่น เบนิฮารุกะ หวานธรรมชาติ ไม่ใส่ ราคาแค่ 272 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น 🦐 กุ้งแม่น้ำไซส์จัมโป้ -7ตัวโล กุ้งตัวใหญ่ๆ ราคาแค่ 280 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เมล็ดเจีย Organic มี อย.คัดพิเศษ ราคาแค่ 130 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ถูกที่สุด Bertolli Extra Virgin ราคาแค่ 442 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 529 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ขนมเปี๊ยะไส้ทะลัก ไข่แดงเค็ม ใบ มีให้เลือก ราคาแค่ 139 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 1112 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Teelek Nougat -นูกัตถุงใหญ่ ชิ้น ราคาแค่ 250 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Country Sourdough Bread ขนมปังซาวโดว์โฮมเมด ราคาแค่ 182 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มาใหม่ดูไบคิมบับ ดูไบคุกกี้ชิววี่ เวฟไฟอ่อน10 ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง นมแพะ Smart Goat ลัง ราคาแค่ 2180 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สลิดติดปาก ปลาสลิดแดดเดียว -/โล | ราคาแค่ 469 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซื้อ แถม Matcha Japan ราคาแค่ 351 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกปูม้าเจ๊เล็กน้ำพริกปูม้า,ฮาลาลฟู๊ด,มี6 ราคาแค่ 147 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ICHITAN อิชิตัน น้ำด่าง ผสมวิตามินบีรวม ราคาแค่ 480 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ในไทย Marukyu​ Koyamaen​ ผงมัทฉะ​ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ Kanbayashi Shunsho.มัทฉะ Matcha ZUIHO/ชาเขียว ราคาแค่ 1048 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูเเดดเดียว กรัม เจ๊ติ๋ม ตลาด ราคาแค่ 194 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ตราฉัตร กิโล ข้าวหอมมะลิใหม่ ข้าวหอมมะลิแท้ ราคาแค่ 145 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถม1ขนมโมจิมีนม่วงญี่ปุ่น หอม หวาน มัน ราคาแค่ 98 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Nao Matcha นาโอะ มัทฉะแท้ ราคาแค่ 290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ของกินตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Esan phasuab น้ำปลาร้าอีสานพาสวบ 3ขวด ราคาแค่ 180 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังออกกำลังกายเสร็จเหนื่อยๆ บางวันเคี้ยวอกไก่ไม่ไหวจริงๆ ได้ตัวนี้ดื่มแทนง่ายมาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น นมเปรี้ยว ดัชมิลล์ ขนาด เซต ราคาแค่ 250 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แคบหมูไร้มัน แคปหมูไร้มัน . . ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กาแฟดำเพื่อสุขภาพ ไม่มีน้ำตาล คั่วสด บดละเอีย ราคาแค่ 99 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ทุเรียนจันทบุรีเนื้อพรีเมียม ยอดขายเยอะที่สุด ราคาแค่ 621 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู เคี้ยวเพลินๆรสต้มยำ ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ . ราคาแค่ 3700 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม น้ำปลาร้าปรุงสุก ตราไม ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ แอปเปิ้ลแช่แข็งแห้งกรอบพรีเมี่ยมชิ้นไม่มีสารเ ราคาแค่ 112 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุน ราคาแค่ 155 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇"]}</t>
+          <t>{"last_personas": ["A", "D", "A", "C", "H", "A", "H", "G", "E", "H", "D", "A", "D", "B", "H", "G", "H", "E", "A", "D", "F", "E", "A", "D", "E", "A", "C", "E", "F", "E", "A", "A", "E", "A", "B", "H", "B", "H", "F", "E", "D", "B", "F", "F", "E", "E", "B", "F", "H", "A"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ"], "last_styles": ["การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก"], "last_roles": ["R6", "R8", "R8", "R2", "R4", "R6", "R2", "R4", "R1", "R1", "R3", "R3", "R6", "R5", "R4", "R2", "R4", "R5", "R6", "R5", "R4", "R4", "R7", "R6", "R2", "R5", "R8", "R8", "R7", "R4", "R6", "R5", "R7", "R6", "R2", "R8", "R1", "R6", "R8", "R3", "R4", "R2", "R7", "R6", "R7", "R4", "R4", "R6", "R7", "R3"], "recent_captions": ["แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 532 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดีมาก ปลาสลิดไข่ - กรัม📌ซื้อ2แพคคุ้มกว่าจ้ ราคาแค่ 200 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Llamito ผงมัทฉะ ออร์แกนิค Matcha ราคาแค่ 449 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อุดมสุข น้ำพริกอกไก่คลีน น้ำพริกอกไก่ น้ำพริก ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ แว่นตากันแดด ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เต้าหู้เฮียแว่น เต้าหู้เนื้อครีมคัสตาร์ด กรอบ ราคาแค่ 175 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง กระปุก แซลมอน ราคาแค่ 1089 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 283 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น *แซลมอนชาคริต* ชิ้น ส่งแช่แข็งฟรี -เนื้อแซลมอ ราคาแค่ 3099 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ก Muek Groob หมึกกรุบ ราคาแค่ 270 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูสามชั้นแดดเดียวไร้หนัง สะอาด ปลอดภัย ไม่ใส ราคาแค่ 152 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วยลดยากินน้ำหวานจุกจิกได้เยอะ แคลคุมง่ายอิ่มท้องนาน แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชุด ขวด นมแดรี่โฮมไฮโปรตีน สูตรแลคโตสฟรี ราคาแค่ 300 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มันหนึบญี่ปุ่น เบนิฮารุกะ หวานธรรมชาติ ไม่ใส่ ราคาแค่ 272 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น 🦐 กุ้งแม่น้ำไซส์จัมโป้ -7ตัวโล กุ้งตัวใหญ่ๆ ราคาแค่ 280 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เมล็ดเจีย Organic มี อย.คัดพิเศษ ราคาแค่ 130 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ถูกที่สุด Bertolli Extra Virgin ราคาแค่ 442 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 529 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ขนมเปี๊ยะไส้ทะลัก ไข่แดงเค็ม ใบ มีให้เลือก ราคาแค่ 139 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 1112 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Teelek Nougat -นูกัตถุงใหญ่ ชิ้น ราคาแค่ 250 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Country Sourdough Bread ขนมปังซาวโดว์โฮมเมด ราคาแค่ 182 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มาใหม่ดูไบคิมบับ ดูไบคุกกี้ชิววี่ เวฟไฟอ่อน10 ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง นมแพะ Smart Goat ลัง ราคาแค่ 2180 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สลิดติดปาก ปลาสลิดแดดเดียว -/โล | ราคาแค่ 469 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซื้อ แถม Matcha Japan ราคาแค่ 351 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกปูม้าเจ๊เล็กน้ำพริกปูม้า,ฮาลาลฟู๊ด,มี6 ราคาแค่ 147 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ICHITAN อิชิตัน น้ำด่าง ผสมวิตามินบีรวม ราคาแค่ 480 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ในไทย Marukyu​ Koyamaen​ ผงมัทฉะ​ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ Kanbayashi Shunsho.มัทฉะ Matcha ZUIHO/ชาเขียว ราคาแค่ 1048 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูเเดดเดียว กรัม เจ๊ติ๋ม ตลาด ราคาแค่ 194 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ตราฉัตร กิโล ข้าวหอมมะลิใหม่ ข้าวหอมมะลิแท้ ราคาแค่ 145 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถม1ขนมโมจิมีนม่วงญี่ปุ่น หอม หวาน มัน ราคาแค่ 98 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Nao Matcha นาโอะ มัทฉะแท้ ราคาแค่ 290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ของกินตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Esan phasuab น้ำปลาร้าอีสานพาสวบ 3ขวด ราคาแค่ 180 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังออกกำลังกายเสร็จเหนื่อยๆ บางวันเคี้ยวอกไก่ไม่ไหวจริงๆ ได้ตัวนี้ดื่มแทนง่ายมาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น นมเปรี้ยว ดัชมิลล์ ขนาด เซต ราคาแค่ 250 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แคบหมูไร้มัน แคปหมูไร้มัน . . ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กาแฟดำเพื่อสุขภาพ ไม่มีน้ำตาล คั่วสด บดละเอีย ราคาแค่ 99 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ทุเรียนจันทบุรีเนื้อพรีเมียม ยอดขายเยอะที่สุด ราคาแค่ 621 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู เคี้ยวเพลินๆรสต้มยำ ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ . ราคาแค่ 3700 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม น้ำปลาร้าปรุงสุก ตราไม ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ แอปเปิ้ลแช่แข็งแห้งกรอบพรีเมี่ยมชิ้นไม่มีสารเ ราคาแค่ 112 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุน ราคาแค่ 155 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2998,16 +2998,141 @@
           <t>https://s.shopee.co.th/20suGMieQS</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mnmij2prwhl2a7.webp</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
           <t>done 2026-06-24 05:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>12</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี** กระทะร้อน อร่อยมาก ถึงเครื่อง เข้มข้น ครบรส ราคา 89.00 บาท</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9fILOSX406</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mp66zmbl7xtt82.webp</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>done 2026-06-25 05:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>4</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>น้ำมันปาล์ม เกสร ราคาพิเศษ 3 ขวด ราคา 220.00 บาท</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3LOHqsGZzL</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztc-mmtjwuvjtxxf59.webp</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>done 2026-06-25 05:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>9</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>คุกกี้ไส้ทะลัก แบบ 6 ชิ้น 10 ชิ้น กระปุกเดี่ยว (เลือกได้ 3 ไส้ ช็อกโกแลต, ไวท์ช็อก, มัทฉะ) ราคา 120.00 บาท</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/60P324DO3F</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztk-mf0sw2zx81sdb8.webp</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>done 2026-06-25 05:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>1</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่นกรึบ หวานน้อย สูตรน้ำตาลต่ำ (Dried Coconut) ราคา 195.00 บาท</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8fPm8nVF0k</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mg3ydny6nkzwa4.webp</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>done 2026-06-25 05:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>7</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>น้ำมันมรกต 1 ลิตร ยกลัง 12 ขวด สินค้าส่งตรงจากโรงงาน (1 คำสั่งซื้อ 1 ลัง) ต้องการมากกว่า 1 ให้แยกคำสั่งซื้อ ราคา 822.00 บาท</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/AKY2BxEinW</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98u-lnfj2bxeyxioc3.webp</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>done 2026-06-25 05:52</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3161,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["A", "D", "A", "C", "H", "A", "H", "G", "E", "H", "D", "A", "D", "B", "H", "G", "H", "E", "A", "D", "F", "E", "A", "D", "E", "A", "C", "E", "F", "E", "A", "A", "E", "A", "B", "H", "B", "H", "F", "E", "D", "B", "F", "F", "E", "E", "B", "F", "H", "A"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ"], "last_styles": ["การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก"], "last_roles": ["R6", "R8", "R8", "R2", "R4", "R6", "R2", "R4", "R1", "R1", "R3", "R3", "R6", "R5", "R4", "R2", "R4", "R5", "R6", "R5", "R4", "R4", "R7", "R6", "R2", "R5", "R8", "R8", "R7", "R4", "R6", "R5", "R7", "R6", "R2", "R8", "R1", "R6", "R8", "R3", "R4", "R2", "R7", "R6", "R7", "R4", "R4", "R6", "R7", "R3"], "recent_captions": ["แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 532 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดีมาก ปลาสลิดไข่ - กรัม📌ซื้อ2แพคคุ้มกว่าจ้ ราคาแค่ 200 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Llamito ผงมัทฉะ ออร์แกนิค Matcha ราคาแค่ 449 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อุดมสุข น้ำพริกอกไก่คลีน น้ำพริกอกไก่ น้ำพริก ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ แว่นตากันแดด ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เต้าหู้เฮียแว่น เต้าหู้เนื้อครีมคัสตาร์ด กรอบ ราคาแค่ 175 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง กระปุก แซลมอน ราคาแค่ 1089 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 283 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น *แซลมอนชาคริต* ชิ้น ส่งแช่แข็งฟรี -เนื้อแซลมอ ราคาแค่ 3099 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ก Muek Groob หมึกกรุบ ราคาแค่ 270 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูสามชั้นแดดเดียวไร้หนัง สะอาด ปลอดภัย ไม่ใส ราคาแค่ 152 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วยลดยากินน้ำหวานจุกจิกได้เยอะ แคลคุมง่ายอิ่มท้องนาน แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชุด ขวด นมแดรี่โฮมไฮโปรตีน สูตรแลคโตสฟรี ราคาแค่ 300 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มันหนึบญี่ปุ่น เบนิฮารุกะ หวานธรรมชาติ ไม่ใส่ ราคาแค่ 272 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น 🦐 กุ้งแม่น้ำไซส์จัมโป้ -7ตัวโล กุ้งตัวใหญ่ๆ ราคาแค่ 280 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เมล็ดเจีย Organic มี อย.คัดพิเศษ ราคาแค่ 130 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ถูกที่สุด Bertolli Extra Virgin ราคาแค่ 442 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 529 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ขนมเปี๊ยะไส้ทะลัก ไข่แดงเค็ม ใบ มีให้เลือก ราคาแค่ 139 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 1112 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Teelek Nougat -นูกัตถุงใหญ่ ชิ้น ราคาแค่ 250 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Country Sourdough Bread ขนมปังซาวโดว์โฮมเมด ราคาแค่ 182 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มาใหม่ดูไบคิมบับ ดูไบคุกกี้ชิววี่ เวฟไฟอ่อน10 ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง นมแพะ Smart Goat ลัง ราคาแค่ 2180 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สลิดติดปาก ปลาสลิดแดดเดียว -/โล | ราคาแค่ 469 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซื้อ แถม Matcha Japan ราคาแค่ 351 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกปูม้าเจ๊เล็กน้ำพริกปูม้า,ฮาลาลฟู๊ด,มี6 ราคาแค่ 147 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ICHITAN อิชิตัน น้ำด่าง ผสมวิตามินบีรวม ราคาแค่ 480 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ในไทย Marukyu​ Koyamaen​ ผงมัทฉะ​ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ Kanbayashi Shunsho.มัทฉะ Matcha ZUIHO/ชาเขียว ราคาแค่ 1048 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูเเดดเดียว กรัม เจ๊ติ๋ม ตลาด ราคาแค่ 194 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ตราฉัตร กิโล ข้าวหอมมะลิใหม่ ข้าวหอมมะลิแท้ ราคาแค่ 145 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถม1ขนมโมจิมีนม่วงญี่ปุ่น หอม หวาน มัน ราคาแค่ 98 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Nao Matcha นาโอะ มัทฉะแท้ ราคาแค่ 290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ของกินตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Esan phasuab น้ำปลาร้าอีสานพาสวบ 3ขวด ราคาแค่ 180 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังออกกำลังกายเสร็จเหนื่อยๆ บางวันเคี้ยวอกไก่ไม่ไหวจริงๆ ได้ตัวนี้ดื่มแทนง่ายมาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น นมเปรี้ยว ดัชมิลล์ ขนาด เซต ราคาแค่ 250 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แคบหมูไร้มัน แคปหมูไร้มัน . . ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กาแฟดำเพื่อสุขภาพ ไม่มีน้ำตาล คั่วสด บดละเอีย ราคาแค่ 99 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ทุเรียนจันทบุรีเนื้อพรีเมียม ยอดขายเยอะที่สุด ราคาแค่ 621 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู เคี้ยวเพลินๆรสต้มยำ ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ . ราคาแค่ 3700 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม น้ำปลาร้าปรุงสุก ตราไม ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ แอปเปิ้ลแช่แข็งแห้งกรอบพรีเมี่ยมชิ้นไม่มีสารเ ราคาแค่ 112 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุน ราคาแค่ 155 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇"]}</t>
+          <t>{"last_personas": ["A", "H", "G", "E", "H", "D", "A", "D", "B", "H", "G", "H", "E", "A", "D", "F", "E", "A", "D", "E", "A", "C", "E", "F", "E", "A", "A", "E", "A", "B", "H", "B", "H", "F", "E", "D", "B", "F", "F", "E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B"], "last_hooks": ["มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ..."], "last_styles": ["การบอกต่อเฉยๆ", "การเปรียบเทียบ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)"], "last_roles": ["R6", "R2", "R4", "R1", "R1", "R3", "R3", "R6", "R5", "R4", "R2", "R4", "R5", "R6", "R5", "R4", "R4", "R7", "R6", "R2", "R5", "R8", "R8", "R7", "R4", "R6", "R5", "R7", "R6", "R2", "R8", "R1", "R6", "R8", "R3", "R4", "R2", "R7", "R6", "R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4"], "recent_captions": ["มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง กระปุก แซลมอน ราคาแค่ 1089 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 283 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น *แซลมอนชาคริต* ชิ้น ส่งแช่แข็งฟรี -เนื้อแซลมอ ราคาแค่ 3099 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ก Muek Groob หมึกกรุบ ราคาแค่ 270 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูสามชั้นแดดเดียวไร้หนัง สะอาด ปลอดภัย ไม่ใส ราคาแค่ 152 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วยลดยากินน้ำหวานจุกจิกได้เยอะ แคลคุมง่ายอิ่มท้องนาน แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชุด ขวด นมแดรี่โฮมไฮโปรตีน สูตรแลคโตสฟรี ราคาแค่ 300 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มันหนึบญี่ปุ่น เบนิฮารุกะ หวานธรรมชาติ ไม่ใส่ ราคาแค่ 272 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น 🦐 กุ้งแม่น้ำไซส์จัมโป้ -7ตัวโล กุ้งตัวใหญ่ๆ ราคาแค่ 280 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เมล็ดเจีย Organic มี อย.คัดพิเศษ ราคาแค่ 130 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ถูกที่สุด Bertolli Extra Virgin ราคาแค่ 442 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 529 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ขนมเปี๊ยะไส้ทะลัก ไข่แดงเค็ม ใบ มีให้เลือก ราคาแค่ 139 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 1112 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Teelek Nougat -นูกัตถุงใหญ่ ชิ้น ราคาแค่ 250 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Country Sourdough Bread ขนมปังซาวโดว์โฮมเมด ราคาแค่ 182 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มาใหม่ดูไบคิมบับ ดูไบคุกกี้ชิววี่ เวฟไฟอ่อน10 ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง นมแพะ Smart Goat ลัง ราคาแค่ 2180 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สลิดติดปาก ปลาสลิดแดดเดียว -/โล | ราคาแค่ 469 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซื้อ แถม Matcha Japan ราคาแค่ 351 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกปูม้าเจ๊เล็กน้ำพริกปูม้า,ฮาลาลฟู๊ด,มี6 ราคาแค่ 147 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ICHITAN อิชิตัน น้ำด่าง ผสมวิตามินบีรวม ราคาแค่ 480 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ในไทย Marukyu​ Koyamaen​ ผงมัทฉะ​ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ Kanbayashi Shunsho.มัทฉะ Matcha ZUIHO/ชาเขียว ราคาแค่ 1048 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูเเดดเดียว กรัม เจ๊ติ๋ม ตลาด ราคาแค่ 194 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ตราฉัตร กิโล ข้าวหอมมะลิใหม่ ข้าวหอมมะลิแท้ ราคาแค่ 145 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถม1ขนมโมจิมีนม่วงญี่ปุ่น หอม หวาน มัน ราคาแค่ 98 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Nao Matcha นาโอะ มัทฉะแท้ ราคาแค่ 290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ของกินตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Esan phasuab น้ำปลาร้าอีสานพาสวบ 3ขวด ราคาแค่ 180 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังออกกำลังกายเสร็จเหนื่อยๆ บางวันเคี้ยวอกไก่ไม่ไหวจริงๆ ได้ตัวนี้ดื่มแทนง่ายมาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น นมเปรี้ยว ดัชมิลล์ ขนาด เซต ราคาแค่ 250 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แคบหมูไร้มัน แคปหมูไร้มัน . . ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กาแฟดำเพื่อสุขภาพ ไม่มีน้ำตาล คั่วสด บดละเอีย ราคาแค่ 99 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ทุเรียนจันทบุรีเนื้อพรีเมียม ยอดขายเยอะที่สุด ราคาแค่ 621 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู เคี้ยวเพลินๆรสต้มยำ ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ . ราคาแค่ 3700 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม น้ำปลาร้าปรุงสุก ตราไม ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ แอปเปิ้ลแช่แข็งแห้งกรอบพรีเมี่ยมชิ้นไม่มีสารเ ราคาแค่ 112 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุน ราคาแค่ 155 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3123,16 +3123,141 @@
           <t>https://s.shopee.co.th/AKY2BxEinW</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98u-lnfj2bxeyxioc3.webp</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
           <t>done 2026-06-25 05:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>15</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>[จัดให้ 2 กระปุก]🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปูมัน รสชาติดีแซ่บนัว เผ็ดกำลังดีกินกับอะไรก็อร่อย ราคา 199.00 บาท</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5L9MEmdTGN</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98z-lof5ug62n1lrb6.webp</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>done 2026-06-26 06:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>17</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>พริกกากหมู สูตรโบราณดั้งเดิม ราคา 150.00 บาท</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/LkgHbCNxF</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zte-mgl5dbuy21vu55.webp</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>done 2026-06-26 06:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>15</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส ไม่ใส่สารกันเสีย ขนาด 150 กรัม ราคา 150.00 บาท</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7KuOYNPsuy</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mkc4ypl093wg43.webp</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>done 2026-06-26 06:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>18</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>สเต็กเนื้อโคขุนพริกไทยดำ(140-150กรัม/ชิ้น)(10ชิ้น)มีทั้งแบบหมักและยังไม่หมัก ราคา 650.00 บาท</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5q5alcwc11</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-23020-776z5w1itknved.webp</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>done 2026-06-26 06:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>17</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>🚚โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธรรมชาติ ขนาด 100และ500 กรัม สับปะรด สับปะรดอบแห้ง ราคา 150.00 บาท</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2LVkfLPdSv</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/f07437515d60d68bea2d8cd474eb1eee.webp</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>done 2026-06-26 06:03</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3286,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["A", "H", "G", "E", "H", "D", "A", "D", "B", "H", "G", "H", "E", "A", "D", "F", "E", "A", "D", "E", "A", "C", "E", "F", "E", "A", "A", "E", "A", "B", "H", "B", "H", "F", "E", "D", "B", "F", "F", "E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B"], "last_hooks": ["มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ..."], "last_styles": ["การบอกต่อเฉยๆ", "การเปรียบเทียบ", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)"], "last_roles": ["R6", "R2", "R4", "R1", "R1", "R3", "R3", "R6", "R5", "R4", "R2", "R4", "R5", "R6", "R5", "R4", "R4", "R7", "R6", "R2", "R5", "R8", "R8", "R7", "R4", "R6", "R5", "R7", "R6", "R2", "R8", "R1", "R6", "R8", "R3", "R4", "R2", "R7", "R6", "R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4"], "recent_captions": ["มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง กระปุก แซลมอน ราคาแค่ 1089 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 283 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น *แซลมอนชาคริต* ชิ้น ส่งแช่แข็งฟรี -เนื้อแซลมอ ราคาแค่ 3099 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ก Muek Groob หมึกกรุบ ราคาแค่ 270 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูสามชั้นแดดเดียวไร้หนัง สะอาด ปลอดภัย ไม่ใส ราคาแค่ 152 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ช่วยลดยากินน้ำหวานจุกจิกได้เยอะ แคลคุมง่ายอิ่มท้องนาน แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชุด ขวด นมแดรี่โฮมไฮโปรตีน สูตรแลคโตสฟรี ราคาแค่ 300 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มันหนึบญี่ปุ่น เบนิฮารุกะ หวานธรรมชาติ ไม่ใส่ ราคาแค่ 272 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น 🦐 กุ้งแม่น้ำไซส์จัมโป้ -7ตัวโล กุ้งตัวใหญ่ๆ ราคาแค่ 280 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เมล็ดเจีย Organic มี อย.คัดพิเศษ ราคาแค่ 130 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ถูกที่สุด Bertolli Extra Virgin ราคาแค่ 442 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 529 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ขนมเปี๊ยะไส้ทะลัก ไข่แดงเค็ม ใบ มีให้เลือก ราคาแค่ 139 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 1112 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Teelek Nougat -นูกัตถุงใหญ่ ชิ้น ราคาแค่ 250 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Country Sourdough Bread ขนมปังซาวโดว์โฮมเมด ราคาแค่ 182 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มาใหม่ดูไบคิมบับ ดูไบคุกกี้ชิววี่ เวฟไฟอ่อน10 ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง นมแพะ Smart Goat ลัง ราคาแค่ 2180 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สลิดติดปาก ปลาสลิดแดดเดียว -/โล | ราคาแค่ 469 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซื้อ แถม Matcha Japan ราคาแค่ 351 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกปูม้าเจ๊เล็กน้ำพริกปูม้า,ฮาลาลฟู๊ด,มี6 ราคาแค่ 147 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ICHITAN อิชิตัน น้ำด่าง ผสมวิตามินบีรวม ราคาแค่ 480 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ในไทย Marukyu​ Koyamaen​ ผงมัทฉะ​ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ Kanbayashi Shunsho.มัทฉะ Matcha ZUIHO/ชาเขียว ราคาแค่ 1048 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูเเดดเดียว กรัม เจ๊ติ๋ม ตลาด ราคาแค่ 194 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ตราฉัตร กิโล ข้าวหอมมะลิใหม่ ข้าวหอมมะลิแท้ ราคาแค่ 145 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถม1ขนมโมจิมีนม่วงญี่ปุ่น หอม หวาน มัน ราคาแค่ 98 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Nao Matcha นาโอะ มัทฉะแท้ ราคาแค่ 290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ของกินตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Esan phasuab น้ำปลาร้าอีสานพาสวบ 3ขวด ราคาแค่ 180 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังออกกำลังกายเสร็จเหนื่อยๆ บางวันเคี้ยวอกไก่ไม่ไหวจริงๆ ได้ตัวนี้ดื่มแทนง่ายมาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น นมเปรี้ยว ดัชมิลล์ ขนาด เซต ราคาแค่ 250 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แคบหมูไร้มัน แคปหมูไร้มัน . . ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กาแฟดำเพื่อสุขภาพ ไม่มีน้ำตาล คั่วสด บดละเอีย ราคาแค่ 99 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ทุเรียนจันทบุรีเนื้อพรีเมียม ยอดขายเยอะที่สุด ราคาแค่ 621 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู เคี้ยวเพลินๆรสต้มยำ ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ . ราคาแค่ 3700 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม น้ำปลาร้าปรุงสุก ตราไม ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ แอปเปิ้ลแช่แข็งแห้งกรอบพรีเมี่ยมชิ้นไม่มีสารเ ราคาแค่ 112 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุน ราคาแค่ 155 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇"]}</t>
+          <t>{"last_personas": ["D", "A", "D", "B", "H", "G", "H", "E", "A", "D", "F", "E", "A", "D", "E", "A", "C", "E", "F", "E", "A", "A", "E", "A", "B", "H", "B", "H", "F", "E", "D", "B", "F", "F", "E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ"], "last_styles": ["การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)"], "last_roles": ["R3", "R3", "R6", "R5", "R4", "R2", "R4", "R5", "R6", "R5", "R4", "R4", "R7", "R6", "R2", "R5", "R8", "R8", "R7", "R4", "R6", "R5", "R7", "R6", "R2", "R8", "R1", "R6", "R8", "R3", "R4", "R2", "R7", "R6", "R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1"], "recent_captions": ["แชร์เผื่อมีคนกำลังหาอยู่ ช่วยลดยากินน้ำหวานจุกจิกได้เยอะ แคลคุมง่ายอิ่มท้องนาน แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชุด ขวด นมแดรี่โฮมไฮโปรตีน สูตรแลคโตสฟรี ราคาแค่ 300 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มันหนึบญี่ปุ่น เบนิฮารุกะ หวานธรรมชาติ ไม่ใส่ ราคาแค่ 272 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น 🦐 กุ้งแม่น้ำไซส์จัมโป้ -7ตัวโล กุ้งตัวใหญ่ๆ ราคาแค่ 280 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เมล็ดเจีย Organic มี อย.คัดพิเศษ ราคาแค่ 130 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ถูกที่สุด Bertolli Extra Virgin ราคาแค่ 442 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 529 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ขนมเปี๊ยะไส้ทะลัก ไข่แดงเค็ม ใบ มีให้เลือก ราคาแค่ 139 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 1112 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Teelek Nougat -นูกัตถุงใหญ่ ชิ้น ราคาแค่ 250 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Country Sourdough Bread ขนมปังซาวโดว์โฮมเมด ราคาแค่ 182 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มาใหม่ดูไบคิมบับ ดูไบคุกกี้ชิววี่ เวฟไฟอ่อน10 ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง นมแพะ Smart Goat ลัง ราคาแค่ 2180 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สลิดติดปาก ปลาสลิดแดดเดียว -/โล | ราคาแค่ 469 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซื้อ แถม Matcha Japan ราคาแค่ 351 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกปูม้าเจ๊เล็กน้ำพริกปูม้า,ฮาลาลฟู๊ด,มี6 ราคาแค่ 147 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ICHITAN อิชิตัน น้ำด่าง ผสมวิตามินบีรวม ราคาแค่ 480 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ในไทย Marukyu​ Koyamaen​ ผงมัทฉะ​ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ Kanbayashi Shunsho.มัทฉะ Matcha ZUIHO/ชาเขียว ราคาแค่ 1048 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูเเดดเดียว กรัม เจ๊ติ๋ม ตลาด ราคาแค่ 194 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ตราฉัตร กิโล ข้าวหอมมะลิใหม่ ข้าวหอมมะลิแท้ ราคาแค่ 145 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถม1ขนมโมจิมีนม่วงญี่ปุ่น หอม หวาน มัน ราคาแค่ 98 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Nao Matcha นาโอะ มัทฉะแท้ ราคาแค่ 290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ของกินตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Esan phasuab น้ำปลาร้าอีสานพาสวบ 3ขวด ราคาแค่ 180 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังออกกำลังกายเสร็จเหนื่อยๆ บางวันเคี้ยวอกไก่ไม่ไหวจริงๆ ได้ตัวนี้ดื่มแทนง่ายมาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น นมเปรี้ยว ดัชมิลล์ ขนาด เซต ราคาแค่ 250 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แคบหมูไร้มัน แคปหมูไร้มัน . . ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กาแฟดำเพื่อสุขภาพ ไม่มีน้ำตาล คั่วสด บดละเอีย ราคาแค่ 99 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ทุเรียนจันทบุรีเนื้อพรีเมียม ยอดขายเยอะที่สุด ราคาแค่ 621 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู เคี้ยวเพลินๆรสต้มยำ ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ . ราคาแค่ 3700 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม น้ำปลาร้าปรุงสุก ตราไม ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ แอปเปิ้ลแช่แข็งแห้งกรอบพรีเมี่ยมชิ้นไม่มีสารเ ราคาแค่ 112 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุน ราคาแค่ 155 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3248,16 +3248,141 @@
           <t>https://s.shopee.co.th/2LVkfLPdSv</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/f07437515d60d68bea2d8cd474eb1eee.webp</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
           <t>done 2026-06-26 06:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>9</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>ถั่ว 9 เซียน ธัญพืชรวม อบกรุบกรอบ รสดั้งเดิม ออแกนิค ไม่น้ำมัน ไม่เนย VIP Mixed nuts ราคา 199.00 บาท</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3qKYRjSfM7</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasb-m0pmsf4ero482f.webp</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>done 2026-06-27 05:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>14</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ (ลูกเกดเหลือง, ลูกเกดดำ, แครนเบอร์รี่, สตรอว์เบอร์รี่ ราคา 135.00 บาท</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8Kmxo5EbPm</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasm-m0zk8bm0ldm0ab.webp</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>done 2026-06-27 05:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>2</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ไร้เม็ด ผลไม้อบแห้งเกรดส่งออก สูตรน้ำตาลต่ำ (Dried Orange Low Sugar) ราคา 95.00 บาท</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9zvBn7ZKHf</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m6tjad8k1fxc38.webp</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>done 2026-06-27 05:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>3</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>น้ำพริกน้ำย้อย ตรายาหยี (สูตรเมืองแพร่ดั้งเดิม) 👉 รสหอมกระเทียม BY ทอดไท/หมวยมาลี ราคา 97.00 บาท</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3qKYRqd2O6</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m26a2qtnb0f59d.webp</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>done 2026-06-27 05:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>20</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>[มี อ.ย.‼] ซอสผัดกะเพรา สูตรเข้มข้น ตราใบเพรา ขนาด 500 ml. (ส่งของทุกวัน) ราคา 119.00 บาท</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6AiTE2tGTE</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98x-lv5y3stoku1p7e.webp</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>done 2026-06-27 05:50</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3411,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["D", "A", "D", "B", "H", "G", "H", "E", "A", "D", "F", "E", "A", "D", "E", "A", "C", "E", "F", "E", "A", "A", "E", "A", "B", "H", "B", "H", "F", "E", "D", "B", "F", "F", "E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ"], "last_styles": ["การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)"], "last_roles": ["R3", "R3", "R6", "R5", "R4", "R2", "R4", "R5", "R6", "R5", "R4", "R4", "R7", "R6", "R2", "R5", "R8", "R8", "R7", "R4", "R6", "R5", "R7", "R6", "R2", "R8", "R1", "R6", "R8", "R3", "R4", "R2", "R7", "R6", "R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1"], "recent_captions": ["แชร์เผื่อมีคนกำลังหาอยู่ ช่วยลดยากินน้ำหวานจุกจิกได้เยอะ แคลคุมง่ายอิ่มท้องนาน แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชุด ขวด นมแดรี่โฮมไฮโปรตีน สูตรแลคโตสฟรี ราคาแค่ 300 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ มันหนึบญี่ปุ่น เบนิฮารุกะ หวานธรรมชาติ ไม่ใส่ ราคาแค่ 272 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น 🦐 กุ้งแม่น้ำไซส์จัมโป้ -7ตัวโล กุ้งตัวใหญ่ๆ ราคาแค่ 280 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เมล็ดเจีย Organic มี อย.คัดพิเศษ ราคาแค่ 130 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ถูกที่สุด Bertolli Extra Virgin ราคาแค่ 442 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 529 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ขนมเปี๊ยะไส้ทะลัก ไข่แดงเค็ม ใบ มีให้เลือก ราคาแค่ 139 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 1112 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Teelek Nougat -นูกัตถุงใหญ่ ชิ้น ราคาแค่ 250 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Country Sourdough Bread ขนมปังซาวโดว์โฮมเมด ราคาแค่ 182 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มาใหม่ดูไบคิมบับ ดูไบคุกกี้ชิววี่ เวฟไฟอ่อน10 ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง นมแพะ Smart Goat ลัง ราคาแค่ 2180 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สลิดติดปาก ปลาสลิดแดดเดียว -/โล | ราคาแค่ 469 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซื้อ แถม Matcha Japan ราคาแค่ 351 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกปูม้าเจ๊เล็กน้ำพริกปูม้า,ฮาลาลฟู๊ด,มี6 ราคาแค่ 147 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ICHITAN อิชิตัน น้ำด่าง ผสมวิตามินบีรวม ราคาแค่ 480 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ในไทย Marukyu​ Koyamaen​ ผงมัทฉะ​ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ Kanbayashi Shunsho.มัทฉะ Matcha ZUIHO/ชาเขียว ราคาแค่ 1048 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูเเดดเดียว กรัม เจ๊ติ๋ม ตลาด ราคาแค่ 194 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ตราฉัตร กิโล ข้าวหอมมะลิใหม่ ข้าวหอมมะลิแท้ ราคาแค่ 145 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถม1ขนมโมจิมีนม่วงญี่ปุ่น หอม หวาน มัน ราคาแค่ 98 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Nao Matcha นาโอะ มัทฉะแท้ ราคาแค่ 290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ของกินตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Esan phasuab น้ำปลาร้าอีสานพาสวบ 3ขวด ราคาแค่ 180 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังออกกำลังกายเสร็จเหนื่อยๆ บางวันเคี้ยวอกไก่ไม่ไหวจริงๆ ได้ตัวนี้ดื่มแทนง่ายมาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น นมเปรี้ยว ดัชมิลล์ ขนาด เซต ราคาแค่ 250 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แคบหมูไร้มัน แคปหมูไร้มัน . . ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กาแฟดำเพื่อสุขภาพ ไม่มีน้ำตาล คั่วสด บดละเอีย ราคาแค่ 99 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ทุเรียนจันทบุรีเนื้อพรีเมียม ยอดขายเยอะที่สุด ราคาแค่ 621 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู เคี้ยวเพลินๆรสต้มยำ ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ . ราคาแค่ 3700 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม น้ำปลาร้าปรุงสุก ตราไม ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ แอปเปิ้ลแช่แข็งแห้งกรอบพรีเมี่ยมชิ้นไม่มีสารเ ราคาแค่ 112 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุน ราคาแค่ 155 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇"]}</t>
+          <t>{"last_personas": ["G", "H", "E", "A", "D", "F", "E", "A", "D", "E", "A", "C", "E", "F", "E", "A", "A", "E", "A", "B", "H", "B", "H", "F", "E", "D", "B", "F", "F", "E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C"], "last_hooks": ["มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ..."], "last_styles": ["คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)"], "last_roles": ["R2", "R4", "R5", "R6", "R5", "R4", "R4", "R7", "R6", "R2", "R5", "R8", "R8", "R7", "R4", "R6", "R5", "R7", "R6", "R2", "R8", "R1", "R6", "R8", "R3", "R4", "R2", "R7", "R6", "R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2"], "recent_captions": ["มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 529 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ขนมเปี๊ยะไส้ทะลัก ไข่แดงเค็ม ใบ มีให้เลือก ราคาแค่ 139 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 1112 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Teelek Nougat -นูกัตถุงใหญ่ ชิ้น ราคาแค่ 250 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Country Sourdough Bread ขนมปังซาวโดว์โฮมเมด ราคาแค่ 182 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มาใหม่ดูไบคิมบับ ดูไบคุกกี้ชิววี่ เวฟไฟอ่อน10 ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง นมแพะ Smart Goat ลัง ราคาแค่ 2180 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สลิดติดปาก ปลาสลิดแดดเดียว -/โล | ราคาแค่ 469 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซื้อ แถม Matcha Japan ราคาแค่ 351 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกปูม้าเจ๊เล็กน้ำพริกปูม้า,ฮาลาลฟู๊ด,มี6 ราคาแค่ 147 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ICHITAN อิชิตัน น้ำด่าง ผสมวิตามินบีรวม ราคาแค่ 480 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ในไทย Marukyu​ Koyamaen​ ผงมัทฉะ​ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ Kanbayashi Shunsho.มัทฉะ Matcha ZUIHO/ชาเขียว ราคาแค่ 1048 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูเเดดเดียว กรัม เจ๊ติ๋ม ตลาด ราคาแค่ 194 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ตราฉัตร กิโล ข้าวหอมมะลิใหม่ ข้าวหอมมะลิแท้ ราคาแค่ 145 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถม1ขนมโมจิมีนม่วงญี่ปุ่น หอม หวาน มัน ราคาแค่ 98 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Nao Matcha นาโอะ มัทฉะแท้ ราคาแค่ 290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ของกินตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Esan phasuab น้ำปลาร้าอีสานพาสวบ 3ขวด ราคาแค่ 180 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังออกกำลังกายเสร็จเหนื่อยๆ บางวันเคี้ยวอกไก่ไม่ไหวจริงๆ ได้ตัวนี้ดื่มแทนง่ายมาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น นมเปรี้ยว ดัชมิลล์ ขนาด เซต ราคาแค่ 250 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แคบหมูไร้มัน แคปหมูไร้มัน . . ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กาแฟดำเพื่อสุขภาพ ไม่มีน้ำตาล คั่วสด บดละเอีย ราคาแค่ 99 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ทุเรียนจันทบุรีเนื้อพรีเมียม ยอดขายเยอะที่สุด ราคาแค่ 621 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู เคี้ยวเพลินๆรสต้มยำ ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ . ราคาแค่ 3700 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม น้ำปลาร้าปรุงสุก ตราไม ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ แอปเปิ้ลแช่แข็งแห้งกรอบพรีเมี่ยมชิ้นไม่มีสารเ ราคาแค่ 112 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุน ราคาแค่ 155 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3373,16 +3373,141 @@
           <t>https://s.shopee.co.th/6AiTE2tGTE</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98x-lv5y3stoku1p7e.webp</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
           <t>done 2026-06-27 05:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>11</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน 👉 100/200 ก. ราคา 109.00 บาท</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/60P0xuwNip</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98t-lr10flflo1x932.webp</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>done 2026-06-28 05:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>5</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>มัทฉะ Kanbayashi Shunsho Koicha Zuihou ซุยโหว Uji matcha powder 20g/40g【ส่งตรงจากญี่ปุ่น】 ราคา 1854.00 บาท</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7fXH0ll3wH</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-mj7uce60pq1137.webp</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>done 2026-06-28 05:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>6</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ลูกใหญ่ เนื้อนุ่มหนึบ ไม่แข็ง ราคา 189.00 บาท</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2BCKSwb0pY</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98s-lp8wi9tav0ji70.webp</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>done 2026-06-28 05:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>8</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร้อมส่งด่วนทั่วประเทศ ซีลแป้งถุงสูญญากาศ ราคา 119.00 บาท</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/30lPOOlK3t</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztj-mjebq9kba60z58.webp</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>done 2026-06-28 05:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>1</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด 500 กรัม ราคา 270.00 บาท</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/AUrSO2T1U0</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-ml68c61fho8w10.webp</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>done 2026-06-28 05:44</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3536,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["G", "H", "E", "A", "D", "F", "E", "A", "D", "E", "A", "C", "E", "F", "E", "A", "A", "E", "A", "B", "H", "B", "H", "F", "E", "D", "B", "F", "F", "E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C"], "last_hooks": ["มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ..."], "last_styles": ["คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)"], "last_roles": ["R2", "R4", "R5", "R6", "R5", "R4", "R4", "R7", "R6", "R2", "R5", "R8", "R8", "R7", "R4", "R6", "R5", "R7", "R6", "R2", "R8", "R1", "R6", "R8", "R3", "R4", "R2", "R7", "R6", "R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2"], "recent_captions": ["มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น แพ็ค Muek Groob หมึกกรุบ ราคาแค่ 529 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ขนมเปี๊ยะไส้ทะลัก ไข่แดงเค็ม ใบ มีให้เลือก ราคาแค่ 139 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี กระ ราคาแค่ 1112 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Teelek Nougat -นูกัตถุงใหญ่ ชิ้น ราคาแค่ 250 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Country Sourdough Bread ขนมปังซาวโดว์โฮมเมด ราคาแค่ 182 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มาใหม่ดูไบคิมบับ ดูไบคุกกี้ชิววี่ เวฟไฟอ่อน10 ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง นมแพะ Smart Goat ลัง ราคาแค่ 2180 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สลิดติดปาก ปลาสลิดแดดเดียว -/โล | ราคาแค่ 469 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซื้อ แถม Matcha Japan ราคาแค่ 351 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกปูม้าเจ๊เล็กน้ำพริกปูม้า,ฮาลาลฟู๊ด,มี6 ราคาแค่ 147 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ICHITAN อิชิตัน น้ำด่าง ผสมวิตามินบีรวม ราคาแค่ 480 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ในไทย Marukyu​ Koyamaen​ ผงมัทฉะ​ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ Kanbayashi Shunsho.มัทฉะ Matcha ZUIHO/ชาเขียว ราคาแค่ 1048 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูเเดดเดียว กรัม เจ๊ติ๋ม ตลาด ราคาแค่ 194 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ตราฉัตร กิโล ข้าวหอมมะลิใหม่ ข้าวหอมมะลิแท้ ราคาแค่ 145 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถม1ขนมโมจิมีนม่วงญี่ปุ่น หอม หวาน มัน ราคาแค่ 98 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Nao Matcha นาโอะ มัทฉะแท้ ราคาแค่ 290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ของกินตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Esan phasuab น้ำปลาร้าอีสานพาสวบ 3ขวด ราคาแค่ 180 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังออกกำลังกายเสร็จเหนื่อยๆ บางวันเคี้ยวอกไก่ไม่ไหวจริงๆ ได้ตัวนี้ดื่มแทนง่ายมาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น นมเปรี้ยว ดัชมิลล์ ขนาด เซต ราคาแค่ 250 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แคบหมูไร้มัน แคปหมูไร้มัน . . ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กาแฟดำเพื่อสุขภาพ ไม่มีน้ำตาล คั่วสด บดละเอีย ราคาแค่ 99 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ทุเรียนจันทบุรีเนื้อพรีเมียม ยอดขายเยอะที่สุด ราคาแค่ 621 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู เคี้ยวเพลินๆรสต้มยำ ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ . ราคาแค่ 3700 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม น้ำปลาร้าปรุงสุก ตราไม ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ แอปเปิ้ลแช่แข็งแห้งกรอบพรีเมี่ยมชิ้นไม่มีสารเ ราคาแค่ 112 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุน ราคาแค่ 155 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇"]}</t>
+          <t>{"last_personas": ["F", "E", "A", "D", "E", "A", "C", "E", "F", "E", "A", "A", "E", "A", "B", "H", "B", "H", "F", "E", "D", "B", "F", "F", "E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ"], "last_roles": ["R4", "R4", "R7", "R6", "R2", "R5", "R8", "R8", "R7", "R4", "R6", "R5", "R7", "R6", "R2", "R8", "R1", "R6", "R8", "R3", "R4", "R2", "R7", "R6", "R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6"], "recent_captions": ["แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มาใหม่ดูไบคิมบับ ดูไบคุกกี้ชิววี่ เวฟไฟอ่อน10 ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง นมแพะ Smart Goat ลัง ราคาแค่ 2180 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สลิดติดปาก ปลาสลิดแดดเดียว -/โล | ราคาแค่ 469 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซื้อ แถม Matcha Japan ราคาแค่ 351 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกปูม้าเจ๊เล็กน้ำพริกปูม้า,ฮาลาลฟู๊ด,มี6 ราคาแค่ 147 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ICHITAN อิชิตัน น้ำด่าง ผสมวิตามินบีรวม ราคาแค่ 480 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ในไทย Marukyu​ Koyamaen​ ผงมัทฉะ​ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ Kanbayashi Shunsho.มัทฉะ Matcha ZUIHO/ชาเขียว ราคาแค่ 1048 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูเเดดเดียว กรัม เจ๊ติ๋ม ตลาด ราคาแค่ 194 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ตราฉัตร กิโล ข้าวหอมมะลิใหม่ ข้าวหอมมะลิแท้ ราคาแค่ 145 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถม1ขนมโมจิมีนม่วงญี่ปุ่น หอม หวาน มัน ราคาแค่ 98 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Nao Matcha นาโอะ มัทฉะแท้ ราคาแค่ 290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ของกินตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Esan phasuab น้ำปลาร้าอีสานพาสวบ 3ขวด ราคาแค่ 180 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังออกกำลังกายเสร็จเหนื่อยๆ บางวันเคี้ยวอกไก่ไม่ไหวจริงๆ ได้ตัวนี้ดื่มแทนง่ายมาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น นมเปรี้ยว ดัชมิลล์ ขนาด เซต ราคาแค่ 250 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แคบหมูไร้มัน แคปหมูไร้มัน . . ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กาแฟดำเพื่อสุขภาพ ไม่มีน้ำตาล คั่วสด บดละเอีย ราคาแค่ 99 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ทุเรียนจันทบุรีเนื้อพรีเมียม ยอดขายเยอะที่สุด ราคาแค่ 621 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู เคี้ยวเพลินๆรสต้มยำ ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ . ราคาแค่ 3700 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม น้ำปลาร้าปรุงสุก ตราไม ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ แอปเปิ้ลแช่แข็งแห้งกรอบพรีเมี่ยมชิ้นไม่มีสารเ ราคาแค่ 112 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุน ราคาแค่ 155 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3498,16 +3498,141 @@
           <t>https://s.shopee.co.th/AUrSO2T1U0</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-ml68c61fho8w10.webp</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
           <t>done 2026-06-28 05:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>7</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย เนื้อแน่น หนังกรอบ กรอบนอกนุ่มใน พร้อมน้ำจิ้ม ขนาด 500ก./ 1,000ก. ราคา 290.00 บาท</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2qS1FtJTov</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rask-m76elywra3an63.webp</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>done 2026-06-29 05:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>12</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด 500 กรัม ราคา 270.00 บาท</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3g18FVFWd9</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zte-ml680l0flgxt0f.webp</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>done 2026-06-29 05:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>17</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko 100 กรัม | Premium Grade Nishio Matcha Powder ราคา 600.00 บาท</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3g18FVwHjP</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mk3h45kcwrnpc8.webp</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>done 2026-06-29 05:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>15</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>ส่งด่วน กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื้อละมุน หวานมัน ปีละครั้ง ต้องลอง🍉 ส่งด่วนทุกวัน ทั่วประเทศ ราคา 849.00 บาท</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8ATXbpvKoM</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0n-md1gusdgvf2880.webp</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>done 2026-06-29 05:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>17</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>อุดมสุข นรกแซลมอน 100 กรัม น้ำพริกคลีน น้ำพริกคีโต น้ำพริกเพื่อสุขภาพ อาหารคลีน อาหารคีโต ราคา 159.00 บาท</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/17pspiEJT</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mk5i8ralf11k25.webp</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>done 2026-06-29 05:43</t>
         </is>
       </c>
     </row>
@@ -3536,7 +3661,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["F", "E", "A", "D", "E", "A", "C", "E", "F", "E", "A", "A", "E", "A", "B", "H", "B", "H", "F", "E", "D", "B", "F", "F", "E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ"], "last_roles": ["R4", "R4", "R7", "R6", "R2", "R5", "R8", "R8", "R7", "R4", "R6", "R5", "R7", "R6", "R2", "R8", "R1", "R6", "R8", "R3", "R4", "R2", "R7", "R6", "R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6"], "recent_captions": ["แชร์เผื่อมีคนกำลังหาอยู่ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มาใหม่ดูไบคิมบับ ดูไบคุกกี้ชิววี่ เวฟไฟอ่อน10 ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง นมแพะ Smart Goat ลัง ราคาแค่ 2180 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สลิดติดปาก ปลาสลิดแดดเดียว -/โล | ราคาแค่ 469 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ซื้อ แถม Matcha Japan ราคาแค่ 351 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกปูม้าเจ๊เล็กน้ำพริกปูม้า,ฮาลาลฟู๊ด,มี6 ราคาแค่ 147 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ICHITAN อิชิตัน น้ำด่าง ผสมวิตามินบีรวม ราคาแค่ 480 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ในไทย Marukyu​ Koyamaen​ ผงมัทฉะ​ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ Kanbayashi Shunsho.มัทฉะ Matcha ZUIHO/ชาเขียว ราคาแค่ 1048 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูเเดดเดียว กรัม เจ๊ติ๋ม ตลาด ราคาแค่ 194 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ตราฉัตร กิโล ข้าวหอมมะลิใหม่ ข้าวหอมมะลิแท้ ราคาแค่ 145 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถม1ขนมโมจิมีนม่วงญี่ปุ่น หอม หวาน มัน ราคาแค่ 98 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Nao Matcha นาโอะ มัทฉะแท้ ราคาแค่ 290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ของกินตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Esan phasuab น้ำปลาร้าอีสานพาสวบ 3ขวด ราคาแค่ 180 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังออกกำลังกายเสร็จเหนื่อยๆ บางวันเคี้ยวอกไก่ไม่ไหวจริงๆ ได้ตัวนี้ดื่มแทนง่ายมาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น นมเปรี้ยว ดัชมิลล์ ขนาด เซต ราคาแค่ 250 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แคบหมูไร้มัน แคปหมูไร้มัน . . ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กาแฟดำเพื่อสุขภาพ ไม่มีน้ำตาล คั่วสด บดละเอีย ราคาแค่ 99 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ทุเรียนจันทบุรีเนื้อพรีเมียม ยอดขายเยอะที่สุด ราคาแค่ 621 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู เคี้ยวเพลินๆรสต้มยำ ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ . ราคาแค่ 3700 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม น้ำปลาร้าปรุงสุก ตราไม ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ แอปเปิ้ลแช่แข็งแห้งกรอบพรีเมี่ยมชิ้นไม่มีสารเ ราคาแค่ 112 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุน ราคาแค่ 155 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇"]}</t>
+          <t>{"last_personas": ["A", "C", "E", "F", "E", "A", "A", "E", "A", "B", "H", "B", "H", "F", "E", "D", "B", "F", "F", "E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D"], "last_hooks": ["มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ..."], "last_styles": ["คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก"], "last_roles": ["R5", "R8", "R8", "R7", "R4", "R6", "R5", "R7", "R6", "R2", "R8", "R1", "R6", "R8", "R3", "R4", "R2", "R7", "R6", "R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5"], "recent_captions": ["มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ICHITAN อิชิตัน น้ำด่าง ผสมวิตามินบีรวม ราคาแค่ 480 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ในไทย Marukyu​ Koyamaen​ ผงมัทฉะ​ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ Kanbayashi Shunsho.มัทฉะ Matcha ZUIHO/ชาเขียว ราคาแค่ 1048 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูเเดดเดียว กรัม เจ๊ติ๋ม ตลาด ราคาแค่ 194 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ตราฉัตร กิโล ข้าวหอมมะลิใหม่ ข้าวหอมมะลิแท้ ราคาแค่ 145 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถม1ขนมโมจิมีนม่วงญี่ปุ่น หอม หวาน มัน ราคาแค่ 98 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Nao Matcha นาโอะ มัทฉะแท้ ราคาแค่ 290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ของกินตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Esan phasuab น้ำปลาร้าอีสานพาสวบ 3ขวด ราคาแค่ 180 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังออกกำลังกายเสร็จเหนื่อยๆ บางวันเคี้ยวอกไก่ไม่ไหวจริงๆ ได้ตัวนี้ดื่มแทนง่ายมาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น นมเปรี้ยว ดัชมิลล์ ขนาด เซต ราคาแค่ 250 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แคบหมูไร้มัน แคปหมูไร้มัน . . ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กาแฟดำเพื่อสุขภาพ ไม่มีน้ำตาล คั่วสด บดละเอีย ราคาแค่ 99 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ทุเรียนจันทบุรีเนื้อพรีเมียม ยอดขายเยอะที่สุด ราคาแค่ 621 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู เคี้ยวเพลินๆรสต้มยำ ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ . ราคาแค่ 3700 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม น้ำปลาร้าปรุงสุก ตราไม ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ แอปเปิ้ลแช่แข็งแห้งกรอบพรีเมี่ยมชิ้นไม่มีสารเ ราคาแค่ 112 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุน ราคาแค่ 155 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G123"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3623,16 +3623,141 @@
           <t>https://s.shopee.co.th/17pspiEJT</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mk5i8ralf11k25.webp</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
           <t>done 2026-06-29 05:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>13</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>ชาเขียว 100% เพียวมัทฉะ ชาเขียว พรีเมี่ยม matcha powder from japan 0 สารเติมแต่ง 1 กระป๋อง 300g ราคา 355.00 บาท</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4AxOqM1Q5R</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mhivoyzzzqird0.webp</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>done 2026-06-30 05:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>6</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ไม่หวาน ผลิตวันต่อวัน ไม่ใส่วัตถุกันเสีย ของแท้จากบริษัท ราคา 169.00 บาท</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3LOHqo8diW</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98z-lswcqt8y4gxp59.webp</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>done 2026-06-30 05:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>16</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ตากสดใหม่ รับประกันความอร่อย ราคา 129.00 บาท</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5q5alcgJru</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-22110-pkze82odovjv1f.webp</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>done 2026-06-30 05:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>20</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโต น้ำพริกเพื่อสุขภาพ ไม่ใส่ผงชูรส อาหารคลีน ราคา 169.00 บาท</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5Apw2Yaqds</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mk5i7m83jh1fa8.webp</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>done 2026-06-30 05:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>2</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>มัทฉะ Kanbayashi Shunsho Usucha Aya no Mori อายะ โนะ โมริ 20g/40g Uji matcha【ส่งตรงจากญี่ปุ่น】 ราคา 1451.00 บาท</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2Vp8nSwIA9</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mj8j4x9o8jd27f.webp</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>done 2026-06-30 05:41</t>
         </is>
       </c>
     </row>
@@ -3661,7 +3786,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["A", "C", "E", "F", "E", "A", "A", "E", "A", "B", "H", "B", "H", "F", "E", "D", "B", "F", "F", "E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D"], "last_hooks": ["มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ..."], "last_styles": ["คำถาม", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก"], "last_roles": ["R5", "R8", "R8", "R7", "R4", "R6", "R5", "R7", "R6", "R2", "R8", "R1", "R6", "R8", "R3", "R4", "R2", "R7", "R6", "R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5"], "recent_captions": ["มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ICHITAN อิชิตัน น้ำด่าง ผสมวิตามินบีรวม ราคาแค่ 480 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ในไทย Marukyu​ Koyamaen​ ผงมัทฉะ​ ราคาแค่ 760 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ Kanbayashi Shunsho.มัทฉะ Matcha ZUIHO/ชาเขียว ราคาแค่ 1048 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูเเดดเดียว กรัม เจ๊ติ๋ม ตลาด ราคาแค่ 194 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ตราฉัตร กิโล ข้าวหอมมะลิใหม่ ข้าวหอมมะลิแท้ ราคาแค่ 145 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถม1ขนมโมจิมีนม่วงญี่ปุ่น หอม หวาน มัน ราคาแค่ 98 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Nao Matcha นาโอะ มัทฉะแท้ ราคาแค่ 290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ของกินตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Esan phasuab น้ำปลาร้าอีสานพาสวบ 3ขวด ราคาแค่ 180 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังออกกำลังกายเสร็จเหนื่อยๆ บางวันเคี้ยวอกไก่ไม่ไหวจริงๆ ได้ตัวนี้ดื่มแทนง่ายมาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น นมเปรี้ยว ดัชมิลล์ ขนาด เซต ราคาแค่ 250 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แคบหมูไร้มัน แคปหมูไร้มัน . . ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กาแฟดำเพื่อสุขภาพ ไม่มีน้ำตาล คั่วสด บดละเอีย ราคาแค่ 99 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ทุเรียนจันทบุรีเนื้อพรีเมียม ยอดขายเยอะที่สุด ราคาแค่ 621 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู เคี้ยวเพลินๆรสต้มยำ ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ . ราคาแค่ 3700 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม น้ำปลาร้าปรุงสุก ตราไม ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ แอปเปิ้ลแช่แข็งแห้งกรอบพรีเมี่ยมชิ้นไม่มีสารเ ราคาแค่ 112 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุน ราคาแค่ 155 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇"]}</t>
+          <t>{"last_personas": ["A", "A", "E", "A", "B", "H", "B", "H", "F", "E", "D", "B", "F", "F", "E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ"], "last_styles": ["การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)"], "last_roles": ["R6", "R5", "R7", "R6", "R2", "R8", "R1", "R6", "R8", "R3", "R4", "R2", "R7", "R6", "R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3"], "recent_captions": ["แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถม1ขนมโมจิมีนม่วงญี่ปุ่น หอม หวาน มัน ราคาแค่ 98 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Nao Matcha นาโอะ มัทฉะแท้ ราคาแค่ 290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ของกินตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Esan phasuab น้ำปลาร้าอีสานพาสวบ 3ขวด ราคาแค่ 180 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังออกกำลังกายเสร็จเหนื่อยๆ บางวันเคี้ยวอกไก่ไม่ไหวจริงๆ ได้ตัวนี้ดื่มแทนง่ายมาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น นมเปรี้ยว ดัชมิลล์ ขนาด เซต ราคาแค่ 250 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แคบหมูไร้มัน แคปหมูไร้มัน . . ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กาแฟดำเพื่อสุขภาพ ไม่มีน้ำตาล คั่วสด บดละเอีย ราคาแค่ 99 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ทุเรียนจันทบุรีเนื้อพรีเมียม ยอดขายเยอะที่สุด ราคาแค่ 621 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู เคี้ยวเพลินๆรสต้มยำ ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ . ราคาแค่ 3700 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม น้ำปลาร้าปรุงสุก ตราไม ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ แอปเปิ้ลแช่แข็งแห้งกรอบพรีเมี่ยมชิ้นไม่มีสารเ ราคาแค่ 112 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุน ราคาแค่ 155 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="630" yWindow="615" windowWidth="37095" windowHeight="17310" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Products" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:G144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3748,16 +3748,430 @@
           <t>https://s.shopee.co.th/2Vp8nSwIA9</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mj8j4x9o8jd27f.webp</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
           <t>done 2026-06-30 05:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>21</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช 15 ปี ตัวแป้งทำจากมันเทศ เก็บได้นานเดือน อุ่นเวฟทานได้เรื่อยๆ</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6AiH6i2ekD</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-mokxodhqmebkc8.webp</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>฿225</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>22</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไข่ฝนแรกล็อตสุดท้ายของปีนี้</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1gFrkRMbd1</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rash-m8x3w0uh4ci73e.webp</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>฿1600</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>23</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>🔥 แคบหมูกึ่งสำเร็จรูป (ติดมัน) Pig a Pop แคบหมูแบบทอดเอง แคบหมูป๊อป แคบหมู แคปหมู</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8fPc5JDYYT</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mib2ub5p89og02.webp</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>฿90</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>24</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ตากสดใหม่ รับประกันความอร่อย</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/17dlNuzzw</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-22110-pkze82odovjv1f.webp</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>฿129</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>25</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Chocolate Brownie Bite ช็อกโกแลตบราวนี่ไบท์ บราวนี่หน้าฟิล์ม</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1VwRY8x3aK</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-23030-bggj3q1eovovda.webp</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>฿119</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>26</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>ไข่ไก่เบอร์ 2 สดจากฟาร์ม 🥚 คัดพิเศษ ไข่ใหม่ทุกวัน</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9Uyj4qWrbx</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mnkys1a0ddzcce.webp</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>฿80</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>27</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุนไพร รสน้ำพริกนรก แบบซอง ขนาด 100 กรัม 3 รสชาติ 1 ซอง Zalidpordeekum</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9pbZTSdhtH</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m863k6w28arga0.webp</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>฿160</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>28</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>(แพ็ค 24 ซอง) Muek Groob หมึกกรุบ เส้นบุกปรุงรสหม่าล่า (เลือกรสชาติได้)</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4Va37fQGTa</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0t-mbotiunlm1cj35.webp</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>฿502</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>29</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส ไม่ใส่สารกันเสีย ขนาด 150 กรัม</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/902STwG4qp</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mkc4ypl093wg43.webp</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>฿150</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>30</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>กุ้งขาวตัวใหญ่ๆ ไซส์25-35ตัวโล กุ้งสดๆแล้วนำมาแช่แข็ง ขายแพ็คละ 1กิโลกรัม เป็นกุ้งสดๆและนำไปแช่แข็ง</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5ApjuteugA</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m866iuk5c8e4b8.webp</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>฿300</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>31</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>กาแฟดำเพื่อสุขภาพ ไม่มีน้ำตาล คั่วสด บดละเอียด ผงสกัดกาแฟละลายน้ำร้อนทันที พร้อมดื่ม Healthy Black Coffee | ร้านกาแฟ 89</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/AAEPs5TAKT</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98r-ly99vph2c04pdc.webp</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>฿99</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>32</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>น้ำมันมรกต 1 ลิตร ยกลัง 12 ขวด สินค้าส่งตรงจากโรงงาน (1 คำสั่งซื้อ 1 ลัง) ต้องการมากกว่า 1 ให้แยกคำสั่งซื้อ</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2LVYXh5iWf</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98u-lnfj2bxeyxioc3.webp</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>฿822</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>33</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นใหญ่ เต็มคำ แซ่บ เปรี้ยวเผ็ดสะใจ มี2ขนาด 100g./400g.</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8KmlgitbG8</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mnmij2prwhl2a7.webp</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>฿175</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>34</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ 3.5 กก.</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/902STwyckb</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/f8fb32659a3650ce0dcc468f645e65be.webp</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>฿3700</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>35</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>มัทฉะ Kanbayashi Shunsho Usucha Aya no Mori อายะ โนะ โมริ 20g/40g Uji matcha【ส่งตรงจากญี่ปุ่น】</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/AAEPs672Qs</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mj8j4x9o8jd27f.webp</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>฿1451</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>36</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>ระฆังทองน้ำปลาหวาน องค์พระปฐมเจดีย์</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/gNKYdqLZf</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/03ce1f8bce1154adcaab44a6dce2438a.webp</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>฿150</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="630" yWindow="615" windowWidth="37095" windowHeight="17310" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -3773,7 +3773,6 @@
           <t>https://s.shopee.co.th/6AiH6i2ekD</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-mokxodhqmebkc8.webp</t>
@@ -3782,6 +3781,11 @@
       <c r="F129" t="inlineStr">
         <is>
           <t>฿225</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>done 2026-07-16 22:01</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3803,6 @@
           <t>https://s.shopee.co.th/1gFrkRMbd1</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7rash-m8x3w0uh4ci73e.webp</t>
@@ -3825,7 +3828,6 @@
           <t>https://s.shopee.co.th/8fPc5JDYYT</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mib2ub5p89og02.webp</t>
@@ -3851,7 +3853,6 @@
           <t>https://s.shopee.co.th/17dlNuzzw</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/sg-11134201-22110-pkze82odovjv1f.webp</t>
@@ -3877,7 +3878,6 @@
           <t>https://s.shopee.co.th/1VwRY8x3aK</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-23030-bggj3q1eovovda.webp</t>
@@ -3903,7 +3903,6 @@
           <t>https://s.shopee.co.th/9Uyj4qWrbx</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mnkys1a0ddzcce.webp</t>
@@ -3929,7 +3928,6 @@
           <t>https://s.shopee.co.th/9pbZTSdhtH</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m863k6w28arga0.webp</t>
@@ -3955,7 +3953,6 @@
           <t>https://s.shopee.co.th/4Va37fQGTa</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0t-mbotiunlm1cj35.webp</t>
@@ -3981,7 +3978,6 @@
           <t>https://s.shopee.co.th/902STwG4qp</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mkc4ypl093wg43.webp</t>
@@ -4007,7 +4003,6 @@
           <t>https://s.shopee.co.th/5ApjuteugA</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m866iuk5c8e4b8.webp</t>
@@ -4033,7 +4028,6 @@
           <t>https://s.shopee.co.th/AAEPs5TAKT</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98r-ly99vph2c04pdc.webp</t>
@@ -4059,7 +4053,6 @@
           <t>https://s.shopee.co.th/2LVYXh5iWf</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98u-lnfj2bxeyxioc3.webp</t>
@@ -4085,7 +4078,6 @@
           <t>https://s.shopee.co.th/8KmlgitbG8</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mnmij2prwhl2a7.webp</t>
@@ -4111,7 +4103,6 @@
           <t>https://s.shopee.co.th/902STwyckb</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/f8fb32659a3650ce0dcc468f645e65be.webp</t>
@@ -4137,7 +4128,6 @@
           <t>https://s.shopee.co.th/AAEPs672Qs</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mj8j4x9o8jd27f.webp</t>
@@ -4163,7 +4153,6 @@
           <t>https://s.shopee.co.th/gNKYdqLZf</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/03ce1f8bce1154adcaab44a6dce2438a.webp</t>
@@ -4200,7 +4189,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["A", "A", "E", "A", "B", "H", "B", "H", "F", "E", "D", "B", "F", "F", "E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ"], "last_styles": ["การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)"], "last_roles": ["R6", "R5", "R7", "R6", "R2", "R8", "R1", "R6", "R8", "R3", "R4", "R2", "R7", "R6", "R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3"], "recent_captions": ["แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถม1ขนมโมจิมีนม่วงญี่ปุ่น หอม หวาน มัน ราคาแค่ 98 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Nao Matcha นาโอะ มัทฉะแท้ ราคาแค่ 290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ของกินตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Esan phasuab น้ำปลาร้าอีสานพาสวบ 3ขวด ราคาแค่ 180 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังออกกำลังกายเสร็จเหนื่อยๆ บางวันเคี้ยวอกไก่ไม่ไหวจริงๆ ได้ตัวนี้ดื่มแทนง่ายมาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น นมเปรี้ยว ดัชมิลล์ ขนาด เซต ราคาแค่ 250 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แคบหมูไร้มัน แคปหมูไร้มัน . . ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กาแฟดำเพื่อสุขภาพ ไม่มีน้ำตาล คั่วสด บดละเอีย ราคาแค่ 99 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ทุเรียนจันทบุรีเนื้อพรีเมียม ยอดขายเยอะที่สุด ราคาแค่ 621 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู เคี้ยวเพลินๆรสต้มยำ ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ . ราคาแค่ 3700 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม น้ำปลาร้าปรุงสุก ตราไม ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ แอปเปิ้ลแช่แข็งแห้งกรอบพรีเมี่ยมชิ้นไม่มีสารเ ราคาแค่ 112 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุน ราคาแค่ 155 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇"]}</t>
+          <t>{"last_personas": ["A", "E", "A", "B", "H", "B", "H", "F", "E", "D", "B", "F", "F", "E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C"], "last_hooks": ["เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["มุกตลก", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ"], "last_roles": ["R5", "R7", "R6", "R2", "R8", "R1", "R6", "R8", "R3", "R4", "R2", "R7", "R6", "R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1"], "recent_captions": ["เห็นคนพูดถึงเยอะเลยลอง ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Nao Matcha นาโอะ มัทฉะแท้ ราคาแค่ 290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ของกินตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Esan phasuab น้ำปลาร้าอีสานพาสวบ 3ขวด ราคาแค่ 180 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังออกกำลังกายเสร็จเหนื่อยๆ บางวันเคี้ยวอกไก่ไม่ไหวจริงๆ ได้ตัวนี้ดื่มแทนง่ายมาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น นมเปรี้ยว ดัชมิลล์ ขนาด เซต ราคาแค่ 250 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แคบหมูไร้มัน แคปหมูไร้มัน . . ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กาแฟดำเพื่อสุขภาพ ไม่มีน้ำตาล คั่วสด บดละเอีย ราคาแค่ 99 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ทุเรียนจันทบุรีเนื้อพรีเมียม ยอดขายเยอะที่สุด ราคาแค่ 621 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู เคี้ยวเพลินๆรสต้มยำ ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ . ราคาแค่ 3700 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม น้ำปลาร้าปรุงสุก ตราไม ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ แอปเปิ้ลแช่แข็งแห้งกรอบพรีเมี่ยมชิ้นไม่มีสารเ ราคาแค่ 112 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุน ราคาแค่ 155 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -3813,6 +3813,11 @@
           <t>฿1600</t>
         </is>
       </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>done 2026-07-17 08:23</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -4189,7 +4194,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["A", "E", "A", "B", "H", "B", "H", "F", "E", "D", "B", "F", "F", "E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C"], "last_hooks": ["เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["มุกตลก", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ"], "last_roles": ["R5", "R7", "R6", "R2", "R8", "R1", "R6", "R8", "R3", "R4", "R2", "R7", "R6", "R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1"], "recent_captions": ["เห็นคนพูดถึงเยอะเลยลอง ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Nao Matcha นาโอะ มัทฉะแท้ ราคาแค่ 290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ของกินตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Esan phasuab น้ำปลาร้าอีสานพาสวบ 3ขวด ราคาแค่ 180 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังออกกำลังกายเสร็จเหนื่อยๆ บางวันเคี้ยวอกไก่ไม่ไหวจริงๆ ได้ตัวนี้ดื่มแทนง่ายมาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น นมเปรี้ยว ดัชมิลล์ ขนาด เซต ราคาแค่ 250 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แคบหมูไร้มัน แคปหมูไร้มัน . . ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กาแฟดำเพื่อสุขภาพ ไม่มีน้ำตาล คั่วสด บดละเอีย ราคาแค่ 99 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ทุเรียนจันทบุรีเนื้อพรีเมียม ยอดขายเยอะที่สุด ราคาแค่ 621 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู เคี้ยวเพลินๆรสต้มยำ ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ . ราคาแค่ 3700 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม น้ำปลาร้าปรุงสุก ตราไม ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ แอปเปิ้ลแช่แข็งแห้งกรอบพรีเมี่ยมชิ้นไม่มีสารเ ราคาแค่ 112 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุน ราคาแค่ 155 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225"]}</t>
+          <t>{"last_personas": ["E", "A", "B", "H", "B", "H", "F", "E", "D", "B", "F", "F", "E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B"], "last_hooks": ["ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง"], "last_styles": ["มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก"], "last_roles": ["R7", "R6", "R2", "R8", "R1", "R6", "R8", "R3", "R4", "R2", "R7", "R6", "R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3"], "recent_captions": ["ไม่คิดว่าจะ... ของกินตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Esan phasuab น้ำปลาร้าอีสานพาสวบ 3ขวด ราคาแค่ 180 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังออกกำลังกายเสร็จเหนื่อยๆ บางวันเคี้ยวอกไก่ไม่ไหวจริงๆ ได้ตัวนี้ดื่มแทนง่ายมาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น นมเปรี้ยว ดัชมิลล์ ขนาด เซต ราคาแค่ 250 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แคบหมูไร้มัน แคปหมูไร้มัน . . ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กาแฟดำเพื่อสุขภาพ ไม่มีน้ำตาล คั่วสด บดละเอีย ราคาแค่ 99 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ทุเรียนจันทบุรีเนื้อพรีเมียม ยอดขายเยอะที่สุด ราคาแค่ 621 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู เคี้ยวเพลินๆรสต้มยำ ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ . ราคาแค่ 3700 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม น้ำปลาร้าปรุงสุก ตราไม ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ แอปเปิ้ลแช่แข็งแห้งกรอบพรีเมี่ยมชิ้นไม่มีสารเ ราคาแค่ 112 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุน ราคาแค่ 155 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -3843,6 +3843,11 @@
           <t>฿90</t>
         </is>
       </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>done 2026-07-17 19:39</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -4194,7 +4199,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["E", "A", "B", "H", "B", "H", "F", "E", "D", "B", "F", "F", "E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B"], "last_hooks": ["ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง"], "last_styles": ["มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก"], "last_roles": ["R7", "R6", "R2", "R8", "R1", "R6", "R8", "R3", "R4", "R2", "R7", "R6", "R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3"], "recent_captions": ["ไม่คิดว่าจะ... ของกินตัวนี้เลยค่ะ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Esan phasuab น้ำปลาร้าอีสานพาสวบ 3ขวด ราคาแค่ 180 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังออกกำลังกายเสร็จเหนื่อยๆ บางวันเคี้ยวอกไก่ไม่ไหวจริงๆ ได้ตัวนี้ดื่มแทนง่ายมาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น นมเปรี้ยว ดัชมิลล์ ขนาด เซต ราคาแค่ 250 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แคบหมูไร้มัน แคปหมูไร้มัน . . ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กาแฟดำเพื่อสุขภาพ ไม่มีน้ำตาล คั่วสด บดละเอีย ราคาแค่ 99 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ทุเรียนจันทบุรีเนื้อพรีเมียม ยอดขายเยอะที่สุด ราคาแค่ 621 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู เคี้ยวเพลินๆรสต้มยำ ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ . ราคาแค่ 3700 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม น้ำปลาร้าปรุงสุก ตราไม ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ แอปเปิ้ลแช่แข็งแห้งกรอบพรีเมี่ยมชิ้นไม่มีสารเ ราคาแค่ 112 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุน ราคาแค่ 155 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600"]}</t>
+          <t>{"last_personas": ["A", "B", "H", "B", "H", "F", "E", "D", "B", "F", "F", "E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C"], "last_hooks": ["ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ..."], "last_styles": ["คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม"], "last_roles": ["R6", "R2", "R8", "R1", "R6", "R8", "R3", "R4", "R2", "R7", "R6", "R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4"], "recent_captions": ["ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังออกกำลังกายเสร็จเหนื่อยๆ บางวันเคี้ยวอกไก่ไม่ไหวจริงๆ ได้ตัวนี้ดื่มแทนง่ายมาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น นมเปรี้ยว ดัชมิลล์ ขนาด เซต ราคาแค่ 250 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แคบหมูไร้มัน แคปหมูไร้มัน . . ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กาแฟดำเพื่อสุขภาพ ไม่มีน้ำตาล คั่วสด บดละเอีย ราคาแค่ 99 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ทุเรียนจันทบุรีเนื้อพรีเมียม ยอดขายเยอะที่สุด ราคาแค่ 621 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู เคี้ยวเพลินๆรสต้มยำ ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ . ราคาแค่ 3700 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม น้ำปลาร้าปรุงสุก ตราไม ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ แอปเปิ้ลแช่แข็งแห้งกรอบพรีเมี่ยมชิ้นไม่มีสารเ ราคาแค่ 112 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุน ราคาแค่ 155 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="630" yWindow="615" windowWidth="37095" windowHeight="17310" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Products" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G144"/>
+  <dimension ref="A1:G143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -522,41 +522,10 @@
       </c>
     </row>
     <row r="2" ht="39.95" customHeight="1">
-      <c r="A2" s="2" t="n">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>วางรายละเอียดสินค้าจาก Shopee ทั้งหมดที่นี่</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>https://s.shopee.co.th/xxx</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>https://s.lazada.co.th/xxx</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>https://down-th.img.susercontent.com/xxx.jpg</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>ลด 20%</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n"/>
-    </row>
-    <row r="3" ht="345" customHeight="1">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>RAY-BAN JUSTIN- RB4165F 601/71
 Ray-Ban เรแบนเป็นผู้นำด้านการผลิตแว่นกันแดด และแว่นสายตา ที่ได้ความนิยมมากที่สุดทั่วโลก มีให้เลือกหลากหลายสไตล์ เหมาะกับทุกคน และใส่ได้ทั้งผู้หญิงและผู้ชาย
@@ -570,23 +539,23 @@
 Lens Material: Polycarbonate Standard</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>https://s.shopee.co.th/AUqz80oxUd</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>https://s.lazada.co.th/s.Z6PzJE?c=b&amp;t=p-ijr1Q-svKWG</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>https://down-th.img.susercontent.com/file/th-11134201-7r990-lscec08f21gm73.webp
 https://down-th.img.susercontent.com/file/th-11134201-7r98y-lscec0amysmu78.webp</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">฿5,130
 final price indicator icon
@@ -598,17 +567,17 @@
 </t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>done 2026-05-21 13:15</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="409.5" customHeight="1">
-      <c r="A4" t="n">
+    <row r="3" ht="345" customHeight="1">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Sony BRAVIA 3 ทีวี 55 นิ้ว รุ่น K-55S30 4K Ultra HD Smart TV (Google TV) | 4K HDR Processor X1
 รายละเอียดสินค้า
@@ -628,22 +597,22 @@
 เรียกดูภาพยนตร์และรายการทีวีมากกว่า 400,000 ตอนจากบริการสตรีมมิ่งของคุณทั้งหมดในที่เดียว โดยจัดเป็นหัวข้อและแนวเนื้อหาไว้ตามสิ่งที่คุณสนใจ</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>https://s.shopee.co.th/10zvLKc6Ji</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>https://s.lazada.co.th/s.Z6mEyG?c=a&amp;t=p-i0-s0&amp;sub_id1=W1</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>https://down-th.img.susercontent.com/file/th-11134207-7r98v-lvsn9yh5vql9c5.webp</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">฿20,500
 final price indicator icon
@@ -653,129 +622,154 @@
 </t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>done 2026-05-31 16:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="409.5" customHeight="1">
+      <c r="A4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่นกรึบ หวานน้อย สูตรน้ำตาลต่ำ (Dried Coconut) ราคา 189.00 บาท</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3qKMKSQPB2</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mg3ydny6nkzwa4.webp</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>done 2026-05-31 16:19</t>
+          <t>done 2026-06-05 11:44</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่นกรึบ หวานน้อย สูตรน้ำตาลต่ำ (Dried Coconut) ราคา 189.00 บาท</t>
+          <t>เก๊กฮวยผงสำเร็จรูป HighlandHerb ขนาด 600 กรัม ราคา 249.00 บาท</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3qKMKSQPB2</t>
+          <t>https://s.shopee.co.th/3VhVvoUPHl</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mg3ydny6nkzwa4.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98v-lp4vdgeuw77id2.webp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>done 2026-06-05 11:44</t>
+          <t>done 2026-06-05 11:57</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>เก๊กฮวยผงสำเร็จรูป HighlandHerb ขนาด 600 กรัม ราคา 249.00 บาท</t>
+          <t>❤️ส่งด่วน1วัน รีวิวเยอะสุด 🙏เกรดพรีเมี่ยม ทุเรียนหมอนทองจันทบุรี แกะเนื้อล้วน พร้อมทาน 🚚ส่งรถเย็น ราคา 469.00 บาท</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3VhVvoUPHl</t>
+          <t>https://s.shopee.co.th/1gFrkSHnnm</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98v-lp4vdgeuw77id2.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0o-mcoacmrgvbz293.webp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>done 2026-06-05 11:57</t>
+          <t>done 2026-06-05 22:49</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>❤️ส่งด่วน1วัน รีวิวเยอะสุด 🙏เกรดพรีเมี่ยม ทุเรียนหมอนทองจันทบุรี แกะเนื้อล้วน พร้อมทาน 🚚ส่งรถเย็น ราคา 469.00 บาท</t>
+          <t>ชาเขียว 100% เพียวมัทฉะ ชาเขียว พรีเมี่ยม matcha powder from japan 0 สารเติมแต่ง 1 กระป๋อง 300g ราคา 374.00 บาท</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1gFrkSHnnm</t>
+          <t>https://s.shopee.co.th/1qZHwlPy1j</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0o-mcoacmrgvbz293.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mhivoyzzzqird0.webp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>done 2026-06-05 22:49</t>
+          <t>done 2026-06-06 09:30</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ชาเขียว 100% เพียวมัทฉะ ชาเขียว พรีเมี่ยม matcha powder from japan 0 สารเติมแต่ง 1 กระป๋อง 300g ราคา 374.00 บาท</t>
+          <t>ไส้อั่วโฮมเมดสูตรเชียงใหม่ หอมสมุนไพร เครื่องแกงเราทำเอง ชุด2แพ็ค รวมน้ำหนัก 1กิโลกรัม ราคา 337.00 บาท</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1qZHwlPy1j</t>
+          <t>https://s.shopee.co.th/2qS1GCKbXS</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mhivoyzzzqird0.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/0b788de026956cdf22390697e7a0306c.webp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>done 2026-06-06 09:30</t>
+          <t>done 2026-06-08 05:46</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ไส้อั่วโฮมเมดสูตรเชียงใหม่ หอมสมุนไพร เครื่องแกงเราทำเอง ชุด2แพ็ค รวมน้ำหนัก 1กิโลกรัม ราคา 337.00 บาท</t>
+          <t>ทุเรียนจันทบุรีเนื้อพรีเมียม ยอดขายเยอะที่สุดทุเรียนหมอนทอง คัดเนื้อเทพไม่เน้นทรง เนื้อเหลือง เนื้อตลาดที่คนไทยกิน ราคา 621.00 บาท</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2qS1GCKbXS</t>
+          <t>https://s.shopee.co.th/5fmCd5ZUob</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/0b788de026956cdf22390697e7a0306c.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rask-mabmx8hshx6278.webp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -786,21 +780,21 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ทุเรียนจันทบุรีเนื้อพรีเมียม ยอดขายเยอะที่สุดทุเรียนหมอนทอง คัดเนื้อเทพไม่เน้นทรง เนื้อเหลือง เนื้อตลาดที่คนไทยกิน ราคา 621.00 บาท</t>
+          <t>หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย เนื้อแน่น หนังกรอบ กรอบนอกนุ่มใน พร้อมน้ำจิ้ม ขนาด 500ก./ 1,000ก. ราคา 290.00 บาท</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5fmCd5ZUob</t>
+          <t>https://s.shopee.co.th/7pqf9H2jLU</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rask-mabmx8hshx6278.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rask-m76elywra3an63.webp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -811,21 +805,21 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย เนื้อแน่น หนังกรอบ กรอบนอกนุ่มใน พร้อมน้ำจิ้ม ขนาด 500ก./ 1,000ก. ราคา 290.00 บาท</t>
+          <t>กุ้งจ่อมโคราชแท้ 100% ขนาด 500 กรัม (ส่งตรงจากบ้านปลาจ่อม อำเภอปักธงชัย จังหวัดนครราชสีมา) ราคา 90.00 บาท</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7pqf9H2jLU</t>
+          <t>https://s.shopee.co.th/6VLJcuyatD</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rask-m76elywra3an63.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/0952cbb174eccbe472d21bbfd74f6b1e.webp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -836,21 +830,21 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>กุ้งจ่อมโคราชแท้ 100% ขนาด 500 กรัม (ส่งตรงจากบ้านปลาจ่อม อำเภอปักธงชัย จังหวัดนครราชสีมา) ราคา 90.00 บาท</t>
+          <t>[แพ็คเกจลุ้นรางวัล][แพ็ค 6] Tulip Cocoa Powder Dark Brown Colour 440 g. ทิวลิปผงโกโก้สีเข้ม 440 กรัม ราคา 1335.00 บาท</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6VLJcuyatD</t>
+          <t>https://s.shopee.co.th/BRG53bISA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/0952cbb174eccbe472d21bbfd74f6b1e.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-823pw-mowwmk8cx5vmdc.webp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -861,46 +855,46 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[แพ็คเกจลุ้นรางวัล][แพ็ค 6] Tulip Cocoa Powder Dark Brown Colour 440 g. ทิวลิปผงโกโก้สีเข้ม 440 กรัม ราคา 1335.00 บาท</t>
+          <t>ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ไร้เม็ด ผลไม้อบแห้งเกรดส่งออก สูตรน้ำตาลต่ำ (Dried Orange Low Sugar) ราคา 95.00 บาท</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/BRG53bISA</t>
+          <t>https://s.shopee.co.th/6fehl9kz4K</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/sg-11134201-823pw-mowwmk8cx5vmdc.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m6tjad8k1fxc38.webp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>done 2026-06-08 05:46</t>
+          <t>done 2026-06-08 07:40</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ไร้เม็ด ผลไม้อบแห้งเกรดส่งออก สูตรน้ำตาลต่ำ (Dried Orange Low Sugar) ราคา 95.00 บาท</t>
+          <t>ขนมเปี๊ยะลาวาไส้ฝอยทองนูเทลล่า (350g) Noeyleeshop ราคา 94.00 บาท</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6fehl9kz4K</t>
+          <t>https://s.shopee.co.th/8fPoCgrCHw</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m6tjad8k1fxc38.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasb-mb1xybwmbxc1d2.webp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -911,46 +905,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ขนมเปี๊ยะลาวาไส้ฝอยทองนูเทลล่า (350g) Noeyleeshop ราคา 94.00 บาท</t>
+          <t>หมูหวานซีอิ๊วงา ทอดไท (นุ่ม-ไม่แข็ง 150 ก) 👉 ไม่ใส่พริกไทย เด็กทานได้ ราคา 114.00 บาท</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8fPoCgrCHw</t>
+          <t>https://s.shopee.co.th/110N4eA1qB</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasb-mb1xybwmbxc1d2.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98y-lr10flflzagt5a.webp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>done 2026-06-08 07:40</t>
+          <t>done 2026-06-08 07:41</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>หมูหวานซีอิ๊วงา ทอดไท (นุ่ม-ไม่แข็ง 150 ก) 👉 ไม่ใส่พริกไทย เด็กทานได้ ราคา 114.00 บาท</t>
+          <t>นมกล่อง (ยกลัง) นมยูเอชที นมไฮคิวสูตร3 1พลัส ซูเปอร์โกลด์ รสจืด180 มล (27 กล่อง) นม UHT HiQ Super Gold UHT ราคา 669.00 บาท</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/110N4eA1qB</t>
+          <t>https://s.shopee.co.th/2qS1FunWwa</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98y-lr10flflzagt5a.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasg-m7hrtewsksjj0d.webp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -961,21 +955,21 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>นมกล่อง (ยกลัง) นมยูเอชที นมไฮคิวสูตร3 1พลัส ซูเปอร์โกลด์ รสจืด180 มล (27 กล่อง) นม UHT HiQ Super Gold UHT ราคา 669.00 บาท</t>
+          <t>น้ำมันปาล์ม ตรา หยก ขนาด1ลิตร แพ็ค 3 ขวด ราคา 210.00 บาท</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2qS1FunWwa</t>
+          <t>https://s.shopee.co.th/70HaDgeSt4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasg-m7hrtewsksjj0d.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-823rr-mp0ouarhqkn61b.webp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -986,46 +980,46 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>น้ำมันปาล์ม ตรา หยก ขนาด1ลิตร แพ็ค 3 ขวด ราคา 210.00 บาท</t>
+          <t>ขนมอัลมอนด์ดาร์กช็อค ไม่ใส่เนย ไม่ใส่แป้ง Ketoทานได้ สูตรคลีนเพื่อสุขภาพ Almond DarkChoc Kanomdeedee (ขนมดีดี) ราคา 193.00 บาท</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/70HaDgeSt4</t>
+          <t>https://s.shopee.co.th/8pjEP3FPCX</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/sg-11134201-823rr-mp0ouarhqkn61b.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztc-mjlfxs2zdmva1c.webp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>done 2026-06-08 07:41</t>
+          <t>done 2026-06-09 06:03</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ขนมอัลมอนด์ดาร์กช็อค ไม่ใส่เนย ไม่ใส่แป้ง Ketoทานได้ สูตรคลีนเพื่อสุขภาพ Almond DarkChoc Kanomdeedee (ขนมดีดี) ราคา 193.00 บาท</t>
+          <t>[ของแท้ ต้นตำรับ] หยิบเป็นชิ้นทานง่าย หมี่กรอบเตาถ่าน กรอบนุ่มไม่แข็ง หอมผิวส้มซ่า (1กล่อง 60 ชิ้น) ราคา 251.00 บาท</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8pjEP3FPCX</t>
+          <t>https://s.shopee.co.th/4qD5devtq4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztc-mjlfxs2zdmva1c.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztn-mlth9szef6df1f.webp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1036,21 +1030,21 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[ของแท้ ต้นตำรับ] หยิบเป็นชิ้นทานง่าย หมี่กรอบเตาถ่าน กรอบนุ่มไม่แข็ง หอมผิวส้มซ่า (1กล่อง 60 ชิ้น) ราคา 251.00 บาท</t>
+          <t>น้ำพริกกากหมู ขนาด 150 กรัม แบบกระปุก แซ่บปะล้ำปะเหลือ ราคา 158.00 บาท</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4qD5devtq4</t>
+          <t>https://s.shopee.co.th/17psx9vPd</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztn-mlth9szef6df1f.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7qul6-lig9ntju66lk6e.webp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1061,46 +1055,46 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>น้ำพริกกากหมู ขนาด 150 กรัม แบบกระปุก แซ่บปะล้ำปะเหลือ ราคา 158.00 บาท</t>
+          <t>ค่าส่งถูกที่สุดร้านช่วยจ่าย ยอดขายเยอะที่สุดทุเรียนหมอนทอง คัดเนื้อเทพไม่เน้นทรง เนื้อเหลือง เนื้อตลาดที่คนไทยกิน ราคา 621.00 บาท</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/17psx9vPd</t>
+          <t>https://s.shopee.co.th/4ftfRK3fOI</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7qul6-lig9ntju66lk6e.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r992-lx9x2ueokgxcc9.webp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>done 2026-06-09 06:03</t>
+          <t>done 2026-06-09 06:04</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ค่าส่งถูกที่สุดร้านช่วยจ่าย ยอดขายเยอะที่สุดทุเรียนหมอนทอง คัดเนื้อเทพไม่เน้นทรง เนื้อเหลือง เนื้อตลาดที่คนไทยกิน ราคา 621.00 บาท</t>
+          <t>น้ำพริกกากหมู ยาหยี (200 ก) 🌶 อร่อย 🔥มีเนื้อ - มีหนัง ราคา 99.00 บาท</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4ftfRK3fOI</t>
+          <t>https://s.shopee.co.th/4ftfRbjCEv</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r992-lx9x2ueokgxcc9.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98q-lr8le588wcsd92.webp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1111,46 +1105,46 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>น้ำพริกกากหมู ยาหยี (200 ก) 🌶 อร่อย 🔥มีเนื้อ - มีหนัง ราคา 99.00 บาท</t>
+          <t>เมล็ดกาแฟคั่ว เขาทะลุ ชุมพร💥คัดเกรดขนาด 500 กรัม กาแฟโรบัสต้า จากขุนเขาชุมพร สู่กาแฟพรีเมียมไทย | Khao Thalu Coffee ราคา 180.00 บาท</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4ftfRbjCEv</t>
+          <t>https://s.shopee.co.th/6VLJciC5w7</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98q-lr8le588wcsd92.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztn-mjh2qiig3y83e1.webp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>done 2026-06-09 06:04</t>
+          <t>done 2026-06-10 06:04</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>เมล็ดกาแฟคั่ว เขาทะลุ ชุมพร💥คัดเกรดขนาด 500 กรัม กาแฟโรบัสต้า จากขุนเขาชุมพร สู่กาแฟพรีเมียมไทย | Khao Thalu Coffee ราคา 180.00 บาท</t>
+          <t>ปลาหมึกไข่แดดเดียวทอดพร้อมทาน -(ไข่ทุกตัว) ไซร์ 5-9 ตัวต่อแพค น้ำหนักก่อนทอด300กรัมและ 500 กรัม ราคา 325.00 บาท</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6VLJciC5w7</t>
+          <t>https://s.shopee.co.th/6fehlA2J9M</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztn-mjh2qiig3y83e1.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/23e49a44f577b0531100e55e0851f11f.webp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1161,21 +1155,21 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ปลาหมึกไข่แดดเดียวทอดพร้อมทาน -(ไข่ทุกตัว) ไซร์ 5-9 ตัวต่อแพค น้ำหนักก่อนทอด300กรัมและ 500 กรัม ราคา 325.00 บาท</t>
+          <t>[โปร 3 กระปุก] น้ำพริกแจ่วบอง ไร่จิตภักดี แบบผัดสุก รสชาติเผ็ดนัวแซ่บถึงใจ ขนาด150กรัม ราคา 219.00 บาท</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6fehlA2J9M</t>
+          <t>https://s.shopee.co.th/LkgHbeZU4</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/23e49a44f577b0531100e55e0851f11f.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasc-m8x35mczvx0ude.webp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1186,46 +1180,46 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[โปร 3 กระปุก] น้ำพริกแจ่วบอง ไร่จิตภักดี แบบผัดสุก รสชาติเผ็ดนัวแซ่บถึงใจ ขนาด150กรัม ราคา 219.00 บาท</t>
+          <t>น้ำพริกปลาแซลมอน น้ำพริกรสแซ่บ น้ำพริกแห้ง ขนาด 80 กรัม แม่ทองคำรสแซ่บ แซลมอน Salmon Chilli Paste ราคา 55.00 บาท</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/LkgHbeZU4</t>
+          <t>https://s.shopee.co.th/9AM4ncO9EF</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasc-m8x35mczvx0ude.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98p-lrzz1m8bd41pfb.webp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>done 2026-06-10 06:04</t>
+          <t>done 2026-06-10 06:05</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>น้ำพริกปลาแซลมอน น้ำพริกรสแซ่บ น้ำพริกแห้ง ขนาด 80 กรัม แม่ทองคำรสแซ่บ แซลมอน Salmon Chilli Paste ราคา 55.00 บาท</t>
+          <t>ปังเปี๊ยะโมจินมสดฮอกไกโด250g แถมดริปนูเทลล่า 40g ราคา 79.00 บาท</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9AM4ncO9EF</t>
+          <t>https://s.shopee.co.th/9UyvCR64vP</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98p-lrzz1m8bd41pfb.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0g-mcltjs8w1rlsba.webp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1236,46 +1230,46 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ปังเปี๊ยะโมจินมสดฮอกไกโด250g แถมดริปนูเทลล่า 40g ราคา 79.00 บาท</t>
+          <t>Chocolate Brownie Bite ช็อกโกแลตบราวนี่ไบท์ บราวนี่หน้าฟิล์ม ราคา 119.00 บาท</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9UyvCR64vP</t>
+          <t>https://s.shopee.co.th/4AxMmYCMnR</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0g-mcltjs8w1rlsba.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-23030-bggj3q1eovovda.webp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>done 2026-06-10 06:05</t>
+          <t>done 2026-06-10 11:15</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chocolate Brownie Bite ช็อกโกแลตบราวนี่ไบท์ บราวนี่หน้าฟิล์ม ราคา 119.00 บาท</t>
+          <t>ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ตากสดใหม่ รับประกันความอร่อย ราคา 129.00 บาท</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4AxMmYCMnR</t>
+          <t>https://s.shopee.co.th/6pyA1F9Gqv</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-23030-bggj3q1eovovda.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-22110-pkze82odovjv1f.webp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1286,21 +1280,21 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ตากสดใหม่ รับประกันความอร่อย ราคา 129.00 บาท</t>
+          <t>Cheesy Jujube - พุทรานมชีส 250 กรัม ขนม อร่อย โฮมเมด นูกัตตี๋เล็ก พุทรา นม ชีส ของฝาก ขนมทานเล่น by teeleknougat ราคา 189.00 บาท</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6pyA1F9Gqv</t>
+          <t>https://s.shopee.co.th/8fPoCsmUHB</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/sg-11134201-22110-pkze82odovjv1f.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zte-mgdl0qn5u70q1e.webp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1311,46 +1305,46 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cheesy Jujube - พุทรานมชีส 250 กรัม ขนม อร่อย โฮมเมด นูกัตตี๋เล็ก พุทรา นม ชีส ของฝาก ขนมทานเล่น by teeleknougat ราคา 189.00 บาท</t>
+          <t>KETO ไส้อั่วหมูสมุนไพรคีโต ย่างหอมๆจากเมืองเหนือ คีโต-โลว์คาร์บทานได้ ราคา 109.00 บาท</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8fPoCsmUHB</t>
+          <t>https://s.shopee.co.th/17psy0rKS</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zte-mgdl0qn5u70q1e.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98r-ltgbf2j90fi721.webp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>done 2026-06-10 11:15</t>
+          <t>done 2026-06-10 11:16</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>KETO ไส้อั่วหมูสมุนไพรคีโต ย่างหอมๆจากเมืองเหนือ คีโต-โลว์คาร์บทานได้ ราคา 109.00 บาท</t>
+          <t>(แบบไม่มีน้ำจิ้ม) หมูกรอบ อบ ไม่มีไขมันทรานส์ เนื้อนุ่ม หนังกรอบ by หมูกรอบ SNOOK ราคา 172.00 บาท</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/17psy0rKS</t>
+          <t>https://s.shopee.co.th/W46TxsKWN</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98r-ltgbf2j90fi721.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/cc8c958732c4728a5538bdd8ae6475f8.webp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1361,71 +1355,71 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>(แบบไม่มีน้ำจิ้ม) หมูกรอบ อบ ไม่มีไขมันทรานส์ เนื้อนุ่ม หนังกรอบ by หมูกรอบ SNOOK ราคา 172.00 บาท</t>
+          <t>หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ไร้แมลง เนื้อนุ่ม ฉ่ำ ทอดง่าย ราคา 149.00 บาท</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/W46TxsKWN</t>
+          <t>https://s.shopee.co.th/30lRSKFxR4</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/cc8c958732c4728a5538bdd8ae6475f8.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mm8rnpzzshs429.webp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>done 2026-06-10 11:16</t>
+          <t>done 2026-06-11 06:14</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ไร้แมลง เนื้อนุ่ม ฉ่ำ ทอดง่าย ราคา 149.00 บาท</t>
+          <t>ผงชาเขียวอาโอโมริ"AOMORI Matcha"ผงชาเขียวมัทฉะ 100% สูตรพรีเมี่ยม 100g. ราคา 119.00 บาท</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/30lRSKFxR4</t>
+          <t>https://s.shopee.co.th/1LdDTGYsoS</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mm8rnpzzshs429.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasj-m5sqf6g4v4c668.webp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>done 2026-06-11 06:14</t>
+          <t>done 2026-06-11 06:15</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ผงชาเขียวอาโอโมริ"AOMORI Matcha"ผงชาเขียวมัทฉะ 100% สูตรพรีเมี่ยม 100g. ราคา 119.00 บาท</t>
+          <t>น้ำพริกหนังไก่ ยาหยี (100/150/200 ก) 🌶 เผ็ด จัดจ้าน ราคา 75.00 บาท</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1LdDTGYsoS</t>
+          <t>https://s.shopee.co.th/50WTm4WhFs</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasj-m5sqf6g4v4c668.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r991-lr10flflv2rh60.webp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1436,21 +1430,21 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>น้ำพริกหนังไก่ ยาหยี (100/150/200 ก) 🌶 เผ็ด จัดจ้าน ราคา 75.00 บาท</t>
+          <t>เบนิฟิตต์ ไฮโปรตีน ขนาด350 มล.( หมดอายุ เดือน 9-10/2026)จัดส่งภายใน2-3วัน(สั่ง1ลังต่อคำสั่งซื้อ) ราคา 399.00 บาท</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/50WTm4WhFs</t>
+          <t>https://s.shopee.co.th/3LOHr6tssA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r991-lr10flflv2rh60.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztj-mlh91o6kf95bed.webp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1461,21 +1455,21 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>เบนิฟิตต์ ไฮโปรตีน ขนาด350 มล.( หมดอายุ เดือน 9-10/2026)จัดส่งภายใน2-3วัน(สั่ง1ลังต่อคำสั่งซื้อ) ราคา 399.00 บาท</t>
+          <t>เม็ดมะม่วงหิมพานต์อบ 500 กรัม เกรด A เต็มเม็ด หอม กรอบ ไม่ทอด | Khunja Shop ราคา 155.00 บาท</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3LOHr6tssA</t>
+          <t>https://s.shopee.co.th/9AM4nb7QzA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztj-mlh91o6kf95bed.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zti-miibfjkeai2q55.webp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1486,26 +1480,26 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>เม็ดมะม่วงหิมพานต์อบ 500 กรัม เกรด A เต็มเม็ด หอม กรอบ ไม่ทอด | Khunja Shop ราคา 155.00 บาท</t>
+          <t>ตราฉัตร 5 กิโล ข้าวหอมมะลิใหม่ ข้าวหอมมะลิแท้ ตราฉัตร 5kg. (หอม นุ่ม ตลอดปี) ข้าวหอมผสม ข้าวขาว หุงอร่อย หุงขึ้นหม้อ ราคา 134.00 บาท</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9AM4nb7QzA</t>
+          <t>https://s.shopee.co.th/2qRzC7LIj7</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zti-miibfjkeai2q55.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-8260m-mkdsz738rxtu0a.webp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>done 2026-06-11 06:15</t>
+          <t>done 2026-06-12 06:11</t>
         </is>
       </c>
     </row>
@@ -1515,17 +1509,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ตราฉัตร 5 กิโล ข้าวหอมมะลิใหม่ ข้าวหอมมะลิแท้ ตราฉัตร 5kg. (หอม นุ่ม ตลอดปี) ข้าวหอมผสม ข้าวขาว หุงอร่อย หุงขึ้นหม้อ ราคา 134.00 บาท</t>
+          <t>ผลไม้ดอง 1kg บรรจุขวดโหล ชั่งเฉพาะเนื้อ แถมฟรีพริกเกลือรสเด็ด ราคา 100.00 บาท</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2qRzC7LIj7</t>
+          <t>https://s.shopee.co.th/7fXH0vfIv3</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/sg-11134201-8260m-mkdsz738rxtu0a.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98x-ll6odn47bqr032.webp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1536,21 +1530,21 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ผลไม้ดอง 1kg บรรจุขวดโหล ชั่งเฉพาะเนื้อ แถมฟรีพริกเกลือรสเด็ด ราคา 100.00 บาท</t>
+          <t>น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นใหญ่ เต็มคำ แซ่บ เปรี้ยวเผ็ดสะใจ มี2ขนาด 100g./400g. ราคา 177.00 บาท</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7fXH0vfIv3</t>
+          <t>https://s.shopee.co.th/8pjCL6ho1X</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98x-ll6odn47bqr032.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mnmij2prwhl2a7.webp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1561,21 +1555,21 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นใหญ่ เต็มคำ แซ่บ เปรี้ยวเผ็ดสะใจ มี2ขนาด 100g./400g. ราคา 177.00 บาท</t>
+          <t>ผงมัทฉะ ออร์แกนิค 100% กลิ่นหอมละมุน ชงง่ายในทุกเมนู - RAIWAN ขนาด 100 กรัม ราคา 340.00 บาท</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8pjCL6ho1X</t>
+          <t>https://s.shopee.co.th/30lPOOyjCD</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mnmij2prwhl2a7.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0s-md4csnzellfp52.webp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1586,21 +1580,21 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ผงมัทฉะ ออร์แกนิค 100% กลิ่นหอมละมุน ชงง่ายในทุกเมนู - RAIWAN ขนาด 100 กรัม ราคา 340.00 บาท</t>
+          <t>น้ำพริกปูม้า แบรนด์ บังฟิส มันปู/ไข่ปู/เนื้อปู ราคา 169.00 บาท</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/30lPOOyjCD</t>
+          <t>https://s.shopee.co.th/4AxOqi9zhi</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0s-md4csnzellfp52.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98v-lzsvhmsql75t87.webp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1611,46 +1605,46 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>น้ำพริกปูม้า แบรนด์ บังฟิส มันปู/ไข่ปู/เนื้อปู ราคา 169.00 บาท</t>
+          <t>ปุยแสบปาก พริกผัดน้ำมันมะกอก Vegen ราคา 263.00 บาท</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4AxOqi9zhi</t>
+          <t>https://s.shopee.co.th/AKY2C1mROs</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98v-lzsvhmsql75t87.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mnu2gil3c16u83.webp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>done 2026-06-12 06:11</t>
+          <t>done 2026-06-13 06:03</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ปุยแสบปาก พริกผัดน้ำมันมะกอก Vegen ราคา 263.00 บาท</t>
+          <t>ส่งด่วนกรุงเทพ/ตจว.❤️ทุเรียนหมอนทองระยอง-จัน แท้💯พรีเมี่ยม แกะเนื้อ รับประกันไม่ตรงปกเปลี่ยนใหม่ให้100%💋 ส่งทุกวัน ราคา 415.00 บาท</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/AKY2C1mROs</t>
+          <t>https://s.shopee.co.th/9fILOaKtZ4</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mnu2gil3c16u83.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-mkjkqzprk3ye45.webp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1661,21 +1655,21 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ส่งด่วนกรุงเทพ/ตจว.❤️ทุเรียนหมอนทองระยอง-จัน แท้💯พรีเมี่ยม แกะเนื้อ รับประกันไม่ตรงปกเปลี่ยนใหม่ให้100%💋 ส่งทุกวัน ราคา 415.00 บาท</t>
+          <t>[เซ็ตคู่] น้ำพริกไข่ปูม้า + น้ำพริกเนื้อปูม้า น้ำพริก ปูม้ามีเลขฮาลาลทุกสูตร . ราคา 304.00 บาท</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9fILOaKtZ4</t>
+          <t>https://s.shopee.co.th/5Apw2WWZJu</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-mkjkqzprk3ye45.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasi-m5phpwu6gkvqac.webp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1686,46 +1680,46 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>[เซ็ตคู่] น้ำพริกไข่ปูม้า + น้ำพริกเนื้อปูม้า น้ำพริก ปูม้ามีเลขฮาลาลทุกสูตร . ราคา 304.00 บาท</t>
+          <t>[Official] 🔥 [KETO] Wholesweet น้ำเชื่อมหญ้าหวาน ไซรัปหญ้าหวาน สูตรคีโต 320 มล. ราคา 151.00 บาท</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5Apw2WWZJu</t>
+          <t>https://s.shopee.co.th/1BJnH6JRHT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasi-m5phpwu6gkvqac.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/a59d309f9d3e34b88669ec977426484d.webp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>done 2026-06-13 06:03</t>
+          <t>done 2026-06-13 06:04</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>[Official] 🔥 [KETO] Wholesweet น้ำเชื่อมหญ้าหวาน ไซรัปหญ้าหวาน สูตรคีโต 320 มล. ราคา 151.00 บาท</t>
+          <t>หมูแดดเดียว หมูเบทาโกรเกรดA ไม่ใส่สารกันบูด ไม่เหนียว ไม่แข็ง สีธรรมชาติ วัตถุดิบเครื่องปรุงคุณภาพสูง อร่อย สะอาด มี อย. ราคา 92.00 บาท</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1BJnH6JRHT</t>
+          <t>https://s.shopee.co.th/5Apw2XRyH1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/a59d309f9d3e34b88669ec977426484d.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98x-lxflamy6285r9b.webp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -1736,26 +1730,26 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>หมูแดดเดียว หมูเบทาโกรเกรดA ไม่ใส่สารกันบูด ไม่เหนียว ไม่แข็ง สีธรรมชาติ วัตถุดิบเครื่องปรุงคุณภาพสูง อร่อย สะอาด มี อย. ราคา 92.00 บาท</t>
+          <t>(แพ็ค 24 ซอง) Muek Groob หมึกกรุบ เส้นบุกปรุงรสหม่าล่า (เลือกรสชาติได้) ราคา 532.00 บาท</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5Apw2XRyH1</t>
+          <t>https://s.shopee.co.th/1gG3rjy0Kb</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98x-lxflamy6285r9b.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mp4md3z4eyvi66.webp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>done 2026-06-13 06:04</t>
+          <t>done 2026-06-14 05:45</t>
         </is>
       </c>
     </row>
@@ -1765,42 +1759,42 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>(แพ็ค 24 ซอง) Muek Groob หมึกกรุบ เส้นบุกปรุงรสหม่าล่า (เลือกรสชาติได้) ราคา 532.00 บาท</t>
+          <t>ขายดีมาก ปลาสลิดไข่ 4-5 ตัว 500 กรัม📌(ซื้อ2แพคคุ้มกว่าจ้า) เค็มน้อย อร่อยมาก มีไข่จุกๆทุกตัว ราคา 200.00 บาท</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1gG3rjy0Kb</t>
+          <t>https://s.shopee.co.th/7pqhDM2ExP</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mp4md3z4eyvi66.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-mg3tpwy77v2m4b.webp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>done 2026-06-14 05:45</t>
+          <t>done 2026-06-14 05:46</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ขายดีมาก ปลาสลิดไข่ 4-5 ตัว 500 กรัม📌(ซื้อ2แพคคุ้มกว่าจ้า) เค็มน้อย อร่อยมาก มีไข่จุกๆทุกตัว ราคา 200.00 บาท</t>
+          <t>Llamito ผงมัทฉะ ออร์แกนิค (Matcha Powder) ขนาด 250g ราคา 449.00 บาท</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7pqhDM2ExP</t>
+          <t>https://s.shopee.co.th/qgwsYVoHw</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-mg3tpwy77v2m4b.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mih9x5ddqn0n95.webp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -1815,17 +1809,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Llamito ผงมัทฉะ ออร์แกนิค (Matcha Powder) ขนาด 250g ราคา 449.00 บาท</t>
+          <t>อุดมสุข น้ำพริกอกไก่คลีน น้ำพริกอกไก่ น้ำพริกคลีน น้ำพริกคีโต อาหารเพื่อสุขภาพ อาหารคลีน อาหารคีโต ราคา 109.00 บาท</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/qgwsYVoHw</t>
+          <t>https://s.shopee.co.th/5VSmQmR3XO</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mih9x5ddqn0n95.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mgdp5aurnthl96.webp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -1836,21 +1830,21 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>อุดมสุข น้ำพริกอกไก่คลีน น้ำพริกอกไก่ น้ำพริกคลีน น้ำพริกคีโต อาหารเพื่อสุขภาพ อาหารคลีน อาหารคีโต ราคา 109.00 บาท</t>
+          <t>เต้าหู้เฮียแว่น เต้าหู้เนื้อครีมคัสตาร์ด กรอบนอก ครีมฉ่ำ นิ่มละมุน | แพ็ค 5 ชิ้น 1 กิโล | โปรตีน 55 กรัม | แช่เย็น 7 วัน ราคา 175.00 บาท</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5VSmQmR3XO</t>
+          <t>https://s.shopee.co.th/1BJnGwvqq6</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mgdp5aurnthl96.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-ml3bpvzk2l8ic2.webp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -1861,46 +1855,46 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>เต้าหู้เฮียแว่น เต้าหู้เนื้อครีมคัสตาร์ด กรอบนอก ครีมฉ่ำ นิ่มละมุน | แพ็ค 5 ชิ้น 1 กิโล | โปรตีน 55 กรัม | แช่เย็น 7 วัน ราคา 175.00 บาท</t>
+          <t>(6.6) koreadong โคเรียดอง 4 กระปุก แซลมอน 2 กุ้ง 2 ฟรี!! น้ำจิ้ม 2 สูตร ราคา 1089.00 บาท</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1BJnGwvqq6</t>
+          <t>https://s.shopee.co.th/6VLJcekMgd</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-ml3bpvzk2l8ic2.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztn-mp3lp4rqcflt1c.webp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>done 2026-06-14 05:46</t>
+          <t>done 2026-06-15 05:50</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>(6.6) koreadong โคเรียดอง 4 กระปุก แซลมอน 2 กุ้ง 2 ฟรี!! น้ำจิ้ม 2 สูตร ราคา 1089.00 บาท</t>
+          <t>koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี 1 กระปุก ขนาด 500 กรัม ราคา 283.00 บาท</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6VLJcekMgd</t>
+          <t>https://s.shopee.co.th/30lRSHhZGU</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztn-mp3lp4rqcflt1c.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98o-lvaiypl9rum22b.webp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -1911,46 +1905,46 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี 1 กระปุก ขนาด 500 กรัม ราคา 283.00 บาท</t>
+          <t>PRO2 *แซลมอนชาคริต* 20 ชิ้น ส่งแช่แข็งฟรี -เนื้อแซลมอน นอร์เวย์ ไร้ก้าง ทานดิบได้- ร้านของคริต ชาคริต แย้มนาม ร้านชาคริต ราคา 3099.00 บาท</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/30lRSHhZGU</t>
+          <t>https://s.shopee.co.th/5q5cpPcaAJ</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98o-lvaiypl9rum22b.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztj-ml5rl1atqqyq13.webp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>done 2026-06-15 05:50</t>
+          <t>done 2026-06-15 05:51</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PRO2 *แซลมอนชาคริต* 20 ชิ้น ส่งแช่แข็งฟรี -เนื้อแซลมอน นอร์เวย์ ไร้ก้าง ทานดิบได้- ร้านของคริต ชาคริต แย้มนาม ร้านชาคริต ราคา 3099.00 บาท</t>
+          <t>(แพ็ก 12) Muek Groob หมึกกรุบ เส้นบุกปรุงรสหม่าล่า สูตรดั้งเดิม หมึกกรุบซันซุ sunsu ราคา 270.00 บาท</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5q5cpPcaAJ</t>
+          <t>https://s.shopee.co.th/7fXH0qnVjj</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztj-ml5rl1atqqyq13.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-823qs-mp3qgnwmeept30.webp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -1961,21 +1955,21 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>(แพ็ก 12) Muek Groob หมึกกรุบ เส้นบุกปรุงรสหม่าล่า สูตรดั้งเดิม หมึกกรุบซันซุ sunsu ราคา 270.00 บาท</t>
+          <t>หมูสามชั้นแดดเดียวไร้หนัง สะอาด ปลอดภัย ไม่ใส่สารกันเสีย ไม่ใส่สีผสมอาหาร ทำสดใหม่ทุกวัน ราคา 152.00 บาท</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7fXH0qnVjj</t>
+          <t>https://s.shopee.co.th/1qZU4Lgl3I</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/sg-11134201-823qs-mp3qgnwmeept30.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mhshbqn5vy848f.webp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -1986,46 +1980,46 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>หมูสามชั้นแดดเดียวไร้หนัง สะอาด ปลอดภัย ไม่ใส่สารกันเสีย ไม่ใส่สีผสมอาหาร ทำสดใหม่ทุกวัน ราคา 152.00 บาท</t>
+          <t>ชุด 4 ขวด นมแดรี่โฮมไฮโปรตีน สูตรแลคโตสฟรี ขนาด 300 มล. **จัดส่งเฉพาะในกรุงเทพ** (ไม่มีแถมลังโฟม) ราคา 300.00 บาท</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1qZU4Lgl3I</t>
+          <t>https://s.shopee.co.th/8Kmxo93MVt</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mhshbqn5vy848f.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztn-mogz3i52c64t0b.webp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>done 2026-06-15 05:51</t>
+          <t>done 2026-06-16 06:24</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ชุด 4 ขวด นมแดรี่โฮมไฮโปรตีน สูตรแลคโตสฟรี ขนาด 300 มล. **จัดส่งเฉพาะในกรุงเทพ** (ไม่มีแถมลังโฟม) ราคา 300.00 บาท</t>
+          <t>มันหนึบญี่ปุ่น เบนิฮารุกะ หวานธรรมชาติ ไม่ใส่น้ำตาล ร้านมาซาริ ราคา 272.00 บาท</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8Kmxo93MVt</t>
+          <t>https://s.shopee.co.th/8fPoCyWB2R</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztn-mogz3i52c64t0b.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ras9-m70vmyupwyzzda.webp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2036,21 +2030,21 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>มันหนึบญี่ปุ่น เบนิฮารุกะ หวานธรรมชาติ ไม่ใส่น้ำตาล ร้านมาซาริ ราคา 272.00 บาท</t>
+          <t>🦐 กุ้งแม่น้ำไซส์จัมโป้ 4-7ตัวโล กุ้งตัวใหญ่ๆ 1แพ็คมี3-5ตัว น้ำหนัก1กิโลกรัมน้ำหนักอาจหายนะครับกุ้งสดๆและนำไปแช็ง ราคา 280.00 บาท</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8fPoCyWB2R</t>
+          <t>https://s.shopee.co.th/5Apw2WO73q</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ras9-m70vmyupwyzzda.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztj-mlpbfq1962o574.webp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2061,21 +2055,21 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>🦐 กุ้งแม่น้ำไซส์จัมโป้ 4-7ตัวโล กุ้งตัวใหญ่ๆ 1แพ็คมี3-5ตัว น้ำหนัก1กิโลกรัมน้ำหนักอาจหายนะครับกุ้งสดๆและนำไปแช็ง ราคา 280.00 บาท</t>
+          <t>เมล็ดเจีย Organic มี อย.คัดพิเศษ เกรดพรีเมี่ยม แบรนด์ไร่พระจันทร์ chia seed 200 400กรัม ราคา 130.00 บาท</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5Apw2WO73q</t>
+          <t>https://s.shopee.co.th/20suGeAdc0</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztj-mlpbfq1962o574.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztn-mkv374joghds15.webp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2086,21 +2080,21 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>เมล็ดเจีย Organic มี อย.คัดพิเศษ เกรดพรีเมี่ยม แบรนด์ไร่พระจันทร์ chia seed 200 400กรัม ราคา 130.00 บาท</t>
+          <t>ถูกที่สุด Bertolli Extra Virgin Olive Oil เบอร์ทอลลีน้ำมันมะกอกเอ็กซ์ตร้าเวอร์จิ้น ราคา 442.00 บาท</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/20suGeAdc0</t>
+          <t>https://s.shopee.co.th/7fXH0u6NAg</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztn-mkv374joghds15.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-7rbn7-m5xznx46gpavb2.webp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2111,46 +2105,46 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ถูกที่สุด Bertolli Extra Virgin Olive Oil เบอร์ทอลลีน้ำมันมะกอกเอ็กซ์ตร้าเวอร์จิ้น ราคา 442.00 บาท</t>
+          <t>(แพ็ค 24 ซอง) Muek Groob หมึกกรุบ เส้นบุกปรุงรสหม่าล่า (เลือกรสชาติได้) ราคา 529.00 บาท</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7fXH0u6NAg</t>
+          <t>https://s.shopee.co.th/20ssCZUVx7</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/sg-11134201-7rbn7-m5xznx46gpavb2.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mp4md3z4eyvi66.webp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>done 2026-06-16 06:24</t>
+          <t>done 2026-06-17 06:09</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>(แพ็ค 24 ซอง) Muek Groob หมึกกรุบ เส้นบุกปรุงรสหม่าล่า (เลือกรสชาติได้) ราคา 529.00 บาท</t>
+          <t>ขนมเปี๊ยะไส้ทะลัก ไข่แดงเค็ม 3 ใบ มีให้เลือก 4 รสชาติ ขนาด 450 กรัม WANWANACH ราคา 139.00 บาท</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/20ssCZUVx7</t>
+          <t>https://s.shopee.co.th/8V6O0gAxW4</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mp4md3z4eyvi66.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mmprjgiy639d92.webp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2161,46 +2155,46 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ขนมเปี๊ยะไส้ทะลัก ไข่แดงเค็ม 3 ใบ มีให้เลือก 4 รสชาติ ขนาด 450 กรัม WANWANACH ราคา 139.00 บาท</t>
+          <t>(6.6) koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี 4 กระปุก สุดฮิต แถมฟรีน้ำจิ้ม ราคา 1112.00 บาท</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8V6O0gAxW4</t>
+          <t>https://s.shopee.co.th/9AM4nY110F</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mmprjgiy639d92.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zte-mp3lys3nslqk0b.webp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>done 2026-06-17 06:09</t>
+          <t>done 2026-06-17 06:10</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>(6.6) koreadong โคเรียดอง แซลมอนดองซีอิ๊วเกาหลี 4 กระปุก สุดฮิต แถมฟรีน้ำจิ้ม ราคา 1112.00 บาท</t>
+          <t>Teelek Nougat -นูกัตถุงใหญ่ 18 ชิ้น ราคา 250.00 บาท</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9AM4nY110F</t>
+          <t>https://s.shopee.co.th/4ftfRb84dJ</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zte-mp3lys3nslqk0b.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0i-mbrwl55927v730.webp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2211,21 +2205,21 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Teelek Nougat -นูกัตถุงใหญ่ 18 ชิ้น ราคา 250.00 บาท</t>
+          <t>Country Sourdough Bread ขนมปังซาวโดว์โฮมเมด 100% | SOURDOUGH BREAD | ราคา 182.00 บาท</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4ftfRb84dJ</t>
+          <t>https://s.shopee.co.th/9AM2jit34K</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0i-mbrwl55927v730.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0h-mcpd1y74lysm7e.webp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2236,46 +2230,46 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Country Sourdough Bread ขนมปังซาวโดว์โฮมเมด 100% | SOURDOUGH BREAD | ราคา 182.00 บาท</t>
+          <t>(มาใหม่)ดูไบคิมบับ ดูไบคุกกี้ชิววี่ เวฟไฟอ่อน10-15วิ ก่อนทาน เพิ่มความฉ่ำ ความยืด ยิ่งอร่อยยิ่งฟิน ตุ๊กกี้ตัวแสบ ราคา 129.00 บาท</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9AM2jit34K</t>
+          <t>https://s.shopee.co.th/W46TihThK</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0h-mcpd1y74lysm7e.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mm00dhdvnqbpce.webp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>done 2026-06-17 06:10</t>
+          <t>done 2026-06-19 06:24</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>(มาใหม่)ดูไบคิมบับ ดูไบคุกกี้ชิววี่ เวฟไฟอ่อน10-15วิ ก่อนทาน เพิ่มความฉ่ำ ความยืด ยิ่งอร่อยยิ่งฟิน ตุ๊กกี้ตัวแสบ ราคา 129.00 บาท</t>
+          <t>นมแพะ Smart Goat 3 ลัง - นมเเพะ ขับถ่ายดี สารอาหารสูง สูตร มัลติวิตามิน &amp; Omega ราคา 2180.00 บาท</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/W46TihThK</t>
+          <t>https://s.shopee.co.th/8ATXc38AC9</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mm00dhdvnqbpce.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasl-maayycy88cayfa.webp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2286,21 +2280,21 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>นมแพะ Smart Goat 3 ลัง - นมเเพะ ขับถ่ายดี สารอาหารสูง สูตร มัลติวิตามิน &amp; Omega ราคา 2180.00 บาท</t>
+          <t>สลิดติดปาก ปลาสลิดแดดเดียว 5-6 ตัว/โล | ปลาสลิดไข่บางบ่อ ตัวโต สด สะอาด เนื้อแน่นหอมมัน ราคา 469.00 บาท</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8ATXc38AC9</t>
+          <t>https://s.shopee.co.th/4ftfRc0nMj</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasl-maayycy88cayfa.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mgvmi6civ40e0a.webp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2311,21 +2305,21 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>สลิดติดปาก ปลาสลิดแดดเดียว 5-6 ตัว/โล | ปลาสลิดไข่บางบ่อ ตัวโต สด สะอาด เนื้อแน่นหอมมัน ราคา 469.00 บาท</t>
+          <t>(ซื้อ 1 แถม 2)Matcha Japan ผงมัทฉะ ออร์แกนิค (Organic Matcha Powder) ขนาด 300g ขนาด ไม่ผสมแป้ง ไม่ผสมน้ำตาล ทานง่ายไม่ขม ราคา 351.00 บาท</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4ftfRc0nMj</t>
+          <t>https://s.shopee.co.th/1BJnGu1X1D</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mgvmi6civ40e0a.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-7ren5-mdu2gpkdaiop19.webp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2336,21 +2330,21 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>(ซื้อ 1 แถม 2)Matcha Japan ผงมัทฉะ ออร์แกนิค (Organic Matcha Powder) ขนาด 300g ขนาด ไม่ผสมแป้ง ไม่ผสมน้ำตาล ทานง่ายไม่ขม ราคา 351.00 บาท</t>
+          <t>น้ำพริกปูม้า(เจ๊เล็กน้ำพริกปูม้า),ฮาลาลฟู๊ด,มี6สูตร มันปูม้า/ไข่ปูม้า/เนื้อปูม้า/สไปซี่/ไข่เผ็ดน้อย ราคา 147.00 บาท</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1BJnGu1X1D</t>
+          <t>https://s.shopee.co.th/80A7PfAPBU</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/sg-11134201-7ren5-mdu2gpkdaiop19.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasl-m5phtrsv3qy25c.webp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2361,46 +2355,46 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>น้ำพริกปูม้า(เจ๊เล็กน้ำพริกปูม้า),ฮาลาลฟู๊ด,มี6สูตร มันปูม้า/ไข่ปูม้า/เนื้อปูม้า/สไปซี่/ไข่เผ็ดน้อย ราคา 147.00 บาท</t>
+          <t>ICHITAN อิชิตัน น้ำด่าง ผสมวิตามินบีรวม ขนาดใหญ่ 550 ml. 1 ลัง (24 ขวด) รวมจัดส่ง ราคา 480.00 บาท</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/80A7PfAPBU</t>
+          <t>https://s.shopee.co.th/9AM4ngSAXx</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasl-m5phtrsv3qy25c.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ras9-m3byqpp14oa0c1.webp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>done 2026-06-19 06:24</t>
+          <t>done 2026-06-20 05:37</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ICHITAN อิชิตัน น้ำด่าง ผสมวิตามินบีรวม ขนาดใหญ่ 550 ml. 1 ลัง (24 ขวด) รวมจัดส่ง ราคา 480.00 บาท</t>
+          <t>พร้อมส่งในไทย Marukyu​ Koyamaen​ ผงมัทฉะ​ มารุคิวของแท้จากญี่ปุ่น​ Matcha​ มัทฉะยี่ห้อดังจากอูจิ ราคา 760.00 บาท</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9AM4ngSAXx</t>
+          <t>https://s.shopee.co.th/6VLJclpvLq</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ras9-m3byqpp14oa0c1.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mn5j25gwgmx2ed.webp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -2411,46 +2405,46 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>พร้อมส่งในไทย Marukyu​ Koyamaen​ ผงมัทฉะ​ มารุคิวของแท้จากญี่ปุ่น​ Matcha​ มัทฉะยี่ห้อดังจากอูจิ ราคา 760.00 บาท</t>
+          <t>Kanbayashi Shunsho.มัทฉะ Matcha ZUIHO/ชาเขียว/ชาเขียวมัทฉะ/ผงมัทฉะ/ลูกร่อนผงมัทฉะ/มัทฉะโทนถั่ว ราคา 1048.00 บาท</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6VLJclpvLq</t>
+          <t>https://s.shopee.co.th/4qD5dYKnKI</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mn5j25gwgmx2ed.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasi-m76lcjji3bcfb4.webp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>done 2026-06-20 05:37</t>
+          <t>done 2026-06-20 05:38</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Kanbayashi Shunsho.มัทฉะ Matcha ZUIHO/ชาเขียว/ชาเขียวมัทฉะ/ผงมัทฉะ/ลูกร่อนผงมัทฉะ/มัทฉะโทนถั่ว ราคา 1048.00 บาท</t>
+          <t>หมูเเดดเดียว 500 กรัม เจ๊ติ๋ม ตลาด อ.ต.ก.เจ้าเก่า (30ปี) "สูตรอร่อยไม่มีใครเหมือน" ราคา 194.00 บาท</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4qD5dYKnKI</t>
+          <t>https://s.shopee.co.th/8fPoCzE2Lb</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasi-m76lcjji3bcfb4.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/3f7c3f4a61b0bef5b99b1041e212dfe4.webp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2461,21 +2455,21 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>หมูเเดดเดียว 500 กรัม เจ๊ติ๋ม ตลาด อ.ต.ก.เจ้าเก่า (30ปี) "สูตรอร่อยไม่มีใครเหมือน" ราคา 194.00 บาท</t>
+          <t>ตราฉัตร 5 กิโล ข้าวหอมมะลิใหม่ ข้าวหอมมะลิแท้ ตราฉัตร 5kg. (หอม นุ่ม ตลอดปี) ข้าวหอมผสม ข้าวขาว หุงอร่อย หุงขึ้นหม้อ ราคา 145.00 บาท</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8fPoCzE2Lb</t>
+          <t>https://s.shopee.co.th/4AxOqdHAb1</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/3f7c3f4a61b0bef5b99b1041e212dfe4.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-8260m-mkdsz738rxtu0a.webp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2486,46 +2480,46 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ตราฉัตร 5 กิโล ข้าวหอมมะลิใหม่ ข้าวหอมมะลิแท้ ตราฉัตร 5kg. (หอม นุ่ม ตลอดปี) ข้าวหอมผสม ข้าวขาว หุงอร่อย หุงขึ้นหม้อ ราคา 145.00 บาท</t>
+          <t>1แถม1ขนมโมจิมีนม่วงญี่ปุ่น หอม หวาน มัน ราคา 98.00 บาท</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4AxOqdHAb1</t>
+          <t>https://s.shopee.co.th/7KuQcRjWpZ</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/sg-11134201-8260m-mkdsz738rxtu0a.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mfun2mvlmk25c6.webp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>done 2026-06-20 05:38</t>
+          <t>done 2026-06-21 05:49</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1แถม1ขนมโมจิมีนม่วงญี่ปุ่น หอม หวาน มัน ราคา 98.00 บาท</t>
+          <t>Nao Matcha นาโอะ มัทฉะแท้ 100% เกรดพรีเมียมจากนิชิโอะ ญี่ปุ่น หอมนัว Nutty ไม่ขม ไม่ฝาด ขนาด 40g ราคา 290.00 บาท</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7KuQcRjWpZ</t>
+          <t>https://s.shopee.co.th/5VSmQuoqES</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mfun2mvlmk25c6.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztj-mn9qqsw8mtqab0.webp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2536,21 +2530,21 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Nao Matcha นาโอะ มัทฉะแท้ 100% เกรดพรีเมียมจากนิชิโอะ ญี่ปุ่น หอมนัว Nutty ไม่ขม ไม่ฝาด ขนาด 40g ราคา 290.00 บาท</t>
+          <t>Esan phasuab น้ำปลาร้าอีสานพาสวบ 3ขวด (ขวดละ350มล) หอมกลิ่นปลาร้าแท้ สูตรแซบนัว สำหรับส้มตำและอาหาร ราคา 180.00 บาท</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5VSmQuoqES</t>
+          <t>https://s.shopee.co.th/3g18FWNAGN</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztj-mn9qqsw8mtqab0.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7qukz-lhj88jai5qmrb3.webp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -2561,21 +2555,21 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Esan phasuab น้ำปลาร้าอีสานพาสวบ 3ขวด (ขวดละ350มล) หอมกลิ่นปลาร้าแท้ สูตรแซบนัว สำหรับส้มตำและอาหาร ราคา 180.00 บาท</t>
+          <t>นมเปรี้ยว ดัชมิลล์ ขนาด 180 ml เซต 5 แพ็ค มี 5 รสชาติ คละรสให้อย่างละ 1แพ็ค (4 กล่อง/แพ็ค) ราคา 250.00 บาท</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3g18FWNAGN</t>
+          <t>https://s.shopee.co.th/902ebaZJA4</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7qukz-lhj88jai5qmrb3.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasj-m0hc9m3k5g3e37.webp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -2586,21 +2580,21 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>นมเปรี้ยว ดัชมิลล์ ขนาด 180 ml เซต 5 แพ็ค มี 5 รสชาติ คละรสให้อย่างละ 1แพ็ค (4 กล่อง/แพ็ค) ราคา 250.00 บาท</t>
+          <t>แคบหมูไร้มัน แคปหมูไร้มัน 1kg. 500g. ราคา 219.00 บาท</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/902ebaZJA4</t>
+          <t>https://s.shopee.co.th/30lRSLg5c1</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasj-m0hc9m3k5g3e37.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-macyz9o9j8fof8.webp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -2611,71 +2605,71 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>แคบหมูไร้มัน แคปหมูไร้มัน 1kg. 500g. ราคา 219.00 บาท</t>
+          <t>กาแฟดำเพื่อสุขภาพ ไม่มีน้ำตาล คั่วสด บดละเอียด ผงสกัดกาแฟละลายน้ำร้อนทันที พร้อมดื่ม Healthy Black Coffee | ร้านกาแฟ 89 ราคา 99.00 บาท</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/30lRSLg5c1</t>
+          <t>https://s.shopee.co.th/6VLHYpGKZE</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-macyz9o9j8fof8.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98r-ly99vph2c04pdc.webp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>done 2026-06-21 05:49</t>
+          <t>done 2026-06-22 05:48</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>กาแฟดำเพื่อสุขภาพ ไม่มีน้ำตาล คั่วสด บดละเอียด ผงสกัดกาแฟละลายน้ำร้อนทันที พร้อมดื่ม Healthy Black Coffee | ร้านกาแฟ 89 ราคา 99.00 บาท</t>
+          <t>ทุเรียนจันทบุรีเนื้อพรีเมียม ยอดขายเยอะที่สุดทุเรียนหมอนทอง คัดเนื้อเทพไม่เน้นทรง เนื้อเหลือง เนื้อตลาดที่คนไทยกิน ราคา 621.00 บาท</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6VLHYpGKZE</t>
+          <t>https://s.shopee.co.th/2LVibAwjEv</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98r-ly99vph2c04pdc.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rask-mabmx8hshx6278.webp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>done 2026-06-22 05:48</t>
+          <t>done 2026-06-22 05:49</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ทุเรียนจันทบุรีเนื้อพรีเมียม ยอดขายเยอะที่สุดทุเรียนหมอนทอง คัดเนื้อเทพไม่เน้นทรง เนื้อเหลือง เนื้อตลาดที่คนไทยกิน ราคา 621.00 บาท</t>
+          <t>พริกกากหมู เคี้ยวเพลินๆ(รสต้มยำ) ราคา 150.00 บาท</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2LVibAwjEv</t>
+          <t>https://s.shopee.co.th/5Apw2C68Zb</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rask-mabmx8hshx6278.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mgl58k2i07ii90.webp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -2686,21 +2680,21 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>พริกกากหมู เคี้ยวเพลินๆ(รสต้มยำ) ราคา 150.00 บาท</t>
+          <t>ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ 3.5 กก. ราคา 3700.00 บาท</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5Apw2C68Zb</t>
+          <t>https://s.shopee.co.th/8pjEP0uUQS</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mgl58k2i07ii90.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/f8fb32659a3650ce0dcc468f645e65be.webp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -2711,21 +2705,21 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ 3.5 กก. ราคา 3700.00 บาท</t>
+          <t>[✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม] น้ำปลาร้าปรุงสุก ตราไมค์ 6 ขวด ขนาด 350 ml. (แซ่บไมค์) น้ำปลาร้า ปรุงสุก สูตรแซ่บทุกเมนู ราคา 245.00 บาท</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8pjEP0uUQS</t>
+          <t>https://s.shopee.co.th/60P31jKZ0f</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/f8fb32659a3650ce0dcc468f645e65be.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasj-mab0imamdy4f32.webp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -2736,71 +2730,71 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>[✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม] น้ำปลาร้าปรุงสุก ตราไมค์ 6 ขวด ขนาด 350 ml. (แซ่บไมค์) น้ำปลาร้า ปรุงสุก สูตรแซ่บทุกเมนู ราคา 245.00 บาท</t>
+          <t>แอปเปิ้ลแช่แข็งแห้งกรอบพรีเมี่ยมชิ้นไม่มีสารเติมแต่งขนมขบเคี้ยวผลไม้แห้งสําหรับผู้ใหญ่ของว่างเพื่อสุขภาพแบบสบาย ๆ ราคา 112.00 บาท</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/60P31jKZ0f</t>
+          <t>https://s.shopee.co.th/6AiTE9uySD</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasj-mab0imamdy4f32.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/cn-11134207-820l4-mn06agdyktfl55.webp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>done 2026-06-22 05:49</t>
+          <t>done 2026-06-23 06:05</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>แอปเปิ้ลแช่แข็งแห้งกรอบพรีเมี่ยมชิ้นไม่มีสารเติมแต่งขนมขบเคี้ยวผลไม้แห้งสําหรับผู้ใหญ่ของว่างเพื่อสุขภาพแบบสบาย ๆ ราคา 112.00 บาท</t>
+          <t>น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุนไพร รสน้ำพริกนรก แบบซอง ขนาด 100 กรัม 3 รสชาติ 1 ซอง Zalidpordeekum ราคา 155.00 บาท</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6AiTE9uySD</t>
+          <t>https://s.shopee.co.th/7VDqoXVW0v</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/cn-11134207-820l4-mn06agdyktfl55.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m863k6w28arga0.webp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>done 2026-06-23 06:05</t>
+          <t>done 2026-06-23 06:06</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุนไพร รสน้ำพริกนรก แบบซอง ขนาด 100 กรัม 3 รสชาติ 1 ซอง Zalidpordeekum ราคา 155.00 บาท</t>
+          <t>กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวมากที่สุด ทุเรียนหมอนทองจันทบุรีแกะเนื้อ ราคา 542.00 บาท</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7VDqoXVW0v</t>
+          <t>https://s.shopee.co.th/9fILOohMBk</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m863k6w28arga0.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/4fb7d47caa67d61241a2af680a4ad3a6.webp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -2811,21 +2805,21 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวมากที่สุด ทุเรียนหมอนทองจันทบุรีแกะเนื้อ ราคา 542.00 บาท</t>
+          <t>เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา 173.00 บาท</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9fILOohMBk</t>
+          <t>https://s.shopee.co.th/6VLJckD4gB</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/4fb7d47caa67d61241a2af680a4ad3a6.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztk-mjrwzih0tts540.webp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -2836,21 +2830,21 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา 173.00 บาท</t>
+          <t>เนยถั่วรวม Chocolate Nuts Butter รสช็อคโกแลต ขนาด 220 g. | Paweenee’s ราคา 175.00 บาท</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6VLJckD4gB</t>
+          <t>https://s.shopee.co.th/20suGfEdLr</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztk-mjrwzih0tts540.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0j-mdoxiej3ykficb.webp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -2861,46 +2855,46 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>เนยถั่วรวม Chocolate Nuts Butter รสช็อคโกแลต ขนาด 220 g. | Paweenee’s ราคา 175.00 บาท</t>
+          <t>อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไข่ฝนแรกล็อตสุดท้ายของปีนี้ ราคา 850.00 บาท</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/20suGfEdLr</t>
+          <t>https://s.shopee.co.th/1VwdfVn8Ft</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0j-mdoxiej3ykficb.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rash-m8x3w0uh4ci73e.webp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>done 2026-06-23 06:06</t>
+          <t>done 2026-06-24 05:51</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไข่ฝนแรกล็อตสุดท้ายของปีนี้ ราคา 850.00 บาท</t>
+          <t>หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ไร้แมลง เนื้อนุ่ม ฉ่ำ ทอดง่าย ราคา 149.00 บาท</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1VwdfVn8Ft</t>
+          <t>https://s.shopee.co.th/2g8YznZTBU</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rash-m8x3w0uh4ci73e.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mm8rnpzzshs429.webp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -2911,21 +2905,21 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ไร้แมลง เนื้อนุ่ม ฉ่ำ ทอดง่าย ราคา 149.00 บาท</t>
+          <t>ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ พร้อมส่ง📌 ราคา 80.00 บาท</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2g8YznZTBU</t>
+          <t>https://s.shopee.co.th/9zvBnPVuA0</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mm8rnpzzshs429.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rash-m3hccjp1scl7d9.webp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -2936,21 +2930,21 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ พร้อมส่ง📌 ราคา 80.00 บาท</t>
+          <t>[พร้อมส่งในไทย]Marukyu Koyamaen Matcha มัทฉะมารุคิวโคยามะเอ็น สาหร่ายผู้ดี อูมามิ เกรดพิธีการญี่ปุ่น ราคา 1118.00 บาท</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9zvBnPVuA0</t>
+          <t>https://s.shopee.co.th/902ebFHsE7</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rash-m3hccjp1scl7d9.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasj-m91el64l52bt32.webp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -2961,71 +2955,71 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>[พร้อมส่งในไทย]Marukyu Koyamaen Matcha มัทฉะมารุคิวโคยามะเอ็น สาหร่ายผู้ดี อูมามิ เกรดพิธีการญี่ปุ่น ราคา 1118.00 บาท</t>
+          <t>น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นใหญ่ เต็มคำ แซ่บ เปรี้ยวเผ็ดสะใจ มี2ขนาด 100g./400g. ราคา 365.00 บาท</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/902ebFHsE7</t>
+          <t>https://s.shopee.co.th/20suGMieQS</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasj-m91el64l52bt32.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mnmij2prwhl2a7.webp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>done 2026-06-24 05:51</t>
+          <t>done 2026-06-24 05:52</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นใหญ่ เต็มคำ แซ่บ เปรี้ยวเผ็ดสะใจ มี2ขนาด 100g./400g. ราคา 365.00 บาท</t>
+          <t>น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี** กระทะร้อน อร่อยมาก ถึงเครื่อง เข้มข้น ครบรส ราคา 89.00 บาท</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/20suGMieQS</t>
+          <t>https://s.shopee.co.th/9fILOSX406</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mnmij2prwhl2a7.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mp66zmbl7xtt82.webp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>done 2026-06-24 05:52</t>
+          <t>done 2026-06-25 05:51</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี** กระทะร้อน อร่อยมาก ถึงเครื่อง เข้มข้น ครบรส ราคา 89.00 บาท</t>
+          <t>น้ำมันปาล์ม เกสร ราคาพิเศษ 3 ขวด ราคา 220.00 บาท</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9fILOSX406</t>
+          <t>https://s.shopee.co.th/3LOHqsGZzL</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mp66zmbl7xtt82.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztc-mmtjwuvjtxxf59.webp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3036,21 +3030,21 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>น้ำมันปาล์ม เกสร ราคาพิเศษ 3 ขวด ราคา 220.00 บาท</t>
+          <t>คุกกี้ไส้ทะลัก แบบ 6 ชิ้น 10 ชิ้น กระปุกเดี่ยว (เลือกได้ 3 ไส้ ช็อกโกแลต, ไวท์ช็อก, มัทฉะ) ราคา 120.00 บาท</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3LOHqsGZzL</t>
+          <t>https://s.shopee.co.th/60P324DO3F</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztc-mmtjwuvjtxxf59.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztk-mf0sw2zx81sdb8.webp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -3061,46 +3055,46 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>คุกกี้ไส้ทะลัก แบบ 6 ชิ้น 10 ชิ้น กระปุกเดี่ยว (เลือกได้ 3 ไส้ ช็อกโกแลต, ไวท์ช็อก, มัทฉะ) ราคา 120.00 บาท</t>
+          <t>Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่นกรึบ หวานน้อย สูตรน้ำตาลต่ำ (Dried Coconut) ราคา 195.00 บาท</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/60P324DO3F</t>
+          <t>https://s.shopee.co.th/8fPm8nVF0k</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztk-mf0sw2zx81sdb8.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mg3ydny6nkzwa4.webp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>done 2026-06-25 05:51</t>
+          <t>done 2026-06-25 05:52</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่นกรึบ หวานน้อย สูตรน้ำตาลต่ำ (Dried Coconut) ราคา 195.00 บาท</t>
+          <t>น้ำมันมรกต 1 ลิตร ยกลัง 12 ขวด สินค้าส่งตรงจากโรงงาน (1 คำสั่งซื้อ 1 ลัง) ต้องการมากกว่า 1 ให้แยกคำสั่งซื้อ ราคา 822.00 บาท</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8fPm8nVF0k</t>
+          <t>https://s.shopee.co.th/AKY2BxEinW</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mg3ydny6nkzwa4.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98u-lnfj2bxeyxioc3.webp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -3111,46 +3105,46 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>น้ำมันมรกต 1 ลิตร ยกลัง 12 ขวด สินค้าส่งตรงจากโรงงาน (1 คำสั่งซื้อ 1 ลัง) ต้องการมากกว่า 1 ให้แยกคำสั่งซื้อ ราคา 822.00 บาท</t>
+          <t>[จัดให้ 2 กระปุก]🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปูมัน รสชาติดีแซ่บนัว เผ็ดกำลังดีกินกับอะไรก็อร่อย ราคา 199.00 บาท</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/AKY2BxEinW</t>
+          <t>https://s.shopee.co.th/5L9MEmdTGN</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98u-lnfj2bxeyxioc3.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98z-lof5ug62n1lrb6.webp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>done 2026-06-25 05:52</t>
+          <t>done 2026-06-26 06:02</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>[จัดให้ 2 กระปุก]🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปูมัน รสชาติดีแซ่บนัว เผ็ดกำลังดีกินกับอะไรก็อร่อย ราคา 199.00 บาท</t>
+          <t>พริกกากหมู สูตรโบราณดั้งเดิม ราคา 150.00 บาท</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5L9MEmdTGN</t>
+          <t>https://s.shopee.co.th/LkgHbCNxF</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98z-lof5ug62n1lrb6.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zte-mgl5dbuy21vu55.webp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -3161,21 +3155,21 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>พริกกากหมู สูตรโบราณดั้งเดิม ราคา 150.00 บาท</t>
+          <t>น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส ไม่ใส่สารกันเสีย ขนาด 150 กรัม ราคา 150.00 บาท</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/LkgHbCNxF</t>
+          <t>https://s.shopee.co.th/7KuOYNPsuy</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zte-mgl5dbuy21vu55.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mkc4ypl093wg43.webp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -3186,46 +3180,46 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส ไม่ใส่สารกันเสีย ขนาด 150 กรัม ราคา 150.00 บาท</t>
+          <t>สเต็กเนื้อโคขุนพริกไทยดำ(140-150กรัม/ชิ้น)(10ชิ้น)มีทั้งแบบหมักและยังไม่หมัก ราคา 650.00 บาท</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7KuOYNPsuy</t>
+          <t>https://s.shopee.co.th/5q5alcwc11</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mkc4ypl093wg43.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-23020-776z5w1itknved.webp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>done 2026-06-26 06:02</t>
+          <t>done 2026-06-26 06:03</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>สเต็กเนื้อโคขุนพริกไทยดำ(140-150กรัม/ชิ้น)(10ชิ้น)มีทั้งแบบหมักและยังไม่หมัก ราคา 650.00 บาท</t>
+          <t>🚚โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธรรมชาติ ขนาด 100และ500 กรัม สับปะรด สับปะรดอบแห้ง ราคา 150.00 บาท</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5q5alcwc11</t>
+          <t>https://s.shopee.co.th/2LVkfLPdSv</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-23020-776z5w1itknved.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/f07437515d60d68bea2d8cd474eb1eee.webp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -3236,46 +3230,46 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>🚚โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธรรมชาติ ขนาด 100และ500 กรัม สับปะรด สับปะรดอบแห้ง ราคา 150.00 บาท</t>
+          <t>ถั่ว 9 เซียน ธัญพืชรวม อบกรุบกรอบ รสดั้งเดิม ออแกนิค ไม่น้ำมัน ไม่เนย VIP Mixed nuts ราคา 199.00 บาท</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2LVkfLPdSv</t>
+          <t>https://s.shopee.co.th/3qKYRjSfM7</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/f07437515d60d68bea2d8cd474eb1eee.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasb-m0pmsf4ero482f.webp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>done 2026-06-26 06:03</t>
+          <t>done 2026-06-27 05:49</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ถั่ว 9 เซียน ธัญพืชรวม อบกรุบกรอบ รสดั้งเดิม ออแกนิค ไม่น้ำมัน ไม่เนย VIP Mixed nuts ราคา 199.00 บาท</t>
+          <t>ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ (ลูกเกดเหลือง, ลูกเกดดำ, แครนเบอร์รี่, สตรอว์เบอร์รี่ ราคา 135.00 บาท</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3qKYRjSfM7</t>
+          <t>https://s.shopee.co.th/8Kmxo5EbPm</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasb-m0pmsf4ero482f.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasm-m0zk8bm0ldm0ab.webp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -3286,21 +3280,21 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ (ลูกเกดเหลือง, ลูกเกดดำ, แครนเบอร์รี่, สตรอว์เบอร์รี่ ราคา 135.00 บาท</t>
+          <t>ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ไร้เม็ด ผลไม้อบแห้งเกรดส่งออก สูตรน้ำตาลต่ำ (Dried Orange Low Sugar) ราคา 95.00 บาท</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8Kmxo5EbPm</t>
+          <t>https://s.shopee.co.th/9zvBn7ZKHf</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasm-m0zk8bm0ldm0ab.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m6tjad8k1fxc38.webp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -3311,46 +3305,46 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ไร้เม็ด ผลไม้อบแห้งเกรดส่งออก สูตรน้ำตาลต่ำ (Dried Orange Low Sugar) ราคา 95.00 บาท</t>
+          <t>น้ำพริกน้ำย้อย ตรายาหยี (สูตรเมืองแพร่ดั้งเดิม) 👉 รสหอมกระเทียม BY ทอดไท/หมวยมาลี ราคา 97.00 บาท</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9zvBn7ZKHf</t>
+          <t>https://s.shopee.co.th/3qKYRqd2O6</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m6tjad8k1fxc38.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m26a2qtnb0f59d.webp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>done 2026-06-27 05:49</t>
+          <t>done 2026-06-27 05:50</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>น้ำพริกน้ำย้อย ตรายาหยี (สูตรเมืองแพร่ดั้งเดิม) 👉 รสหอมกระเทียม BY ทอดไท/หมวยมาลี ราคา 97.00 บาท</t>
+          <t>[มี อ.ย.‼] ซอสผัดกะเพรา สูตรเข้มข้น ตราใบเพรา ขนาด 500 ml. (ส่งของทุกวัน) ราคา 119.00 บาท</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3qKYRqd2O6</t>
+          <t>https://s.shopee.co.th/6AiTE2tGTE</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m26a2qtnb0f59d.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98x-lv5y3stoku1p7e.webp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -3361,46 +3355,46 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>[มี อ.ย.‼] ซอสผัดกะเพรา สูตรเข้มข้น ตราใบเพรา ขนาด 500 ml. (ส่งของทุกวัน) ราคา 119.00 บาท</t>
+          <t>หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน 👉 100/200 ก. ราคา 109.00 บาท</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6AiTE2tGTE</t>
+          <t>https://s.shopee.co.th/60P0xuwNip</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98x-lv5y3stoku1p7e.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98t-lr10flflo1x932.webp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>done 2026-06-27 05:50</t>
+          <t>done 2026-06-28 05:43</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน 👉 100/200 ก. ราคา 109.00 บาท</t>
+          <t>มัทฉะ Kanbayashi Shunsho Koicha Zuihou ซุยโหว Uji matcha powder 20g/40g【ส่งตรงจากญี่ปุ่น】 ราคา 1854.00 บาท</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/60P0xuwNip</t>
+          <t>https://s.shopee.co.th/7fXH0ll3wH</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98t-lr10flflo1x932.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-mj7uce60pq1137.webp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -3411,21 +3405,21 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>มัทฉะ Kanbayashi Shunsho Koicha Zuihou ซุยโหว Uji matcha powder 20g/40g【ส่งตรงจากญี่ปุ่น】 ราคา 1854.00 บาท</t>
+          <t>สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ลูกใหญ่ เนื้อนุ่มหนึบ ไม่แข็ง ราคา 189.00 บาท</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7fXH0ll3wH</t>
+          <t>https://s.shopee.co.th/2BCKSwb0pY</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-mj7uce60pq1137.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98s-lp8wi9tav0ji70.webp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -3436,21 +3430,21 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ลูกใหญ่ เนื้อนุ่มหนึบ ไม่แข็ง ราคา 189.00 บาท</t>
+          <t>โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร้อมส่งด่วนทั่วประเทศ ซีลแป้งถุงสูญญากาศ ราคา 119.00 บาท</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2BCKSwb0pY</t>
+          <t>https://s.shopee.co.th/30lPOOlK3t</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98s-lp8wi9tav0ji70.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztj-mjebq9kba60z58.webp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -3461,71 +3455,71 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร้อมส่งด่วนทั่วประเทศ ซีลแป้งถุงสูญญากาศ ราคา 119.00 บาท</t>
+          <t>แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด 500 กรัม ราคา 270.00 บาท</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/30lPOOlK3t</t>
+          <t>https://s.shopee.co.th/AUrSO2T1U0</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztj-mjebq9kba60z58.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-ml68c61fho8w10.webp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>done 2026-06-28 05:43</t>
+          <t>done 2026-06-28 05:44</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด 500 กรัม ราคา 270.00 บาท</t>
+          <t>หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย เนื้อแน่น หนังกรอบ กรอบนอกนุ่มใน พร้อมน้ำจิ้ม ขนาด 500ก./ 1,000ก. ราคา 290.00 บาท</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/AUrSO2T1U0</t>
+          <t>https://s.shopee.co.th/2qS1FtJTov</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-ml68c61fho8w10.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rask-m76elywra3an63.webp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>done 2026-06-28 05:44</t>
+          <t>done 2026-06-29 05:43</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย เนื้อแน่น หนังกรอบ กรอบนอกนุ่มใน พร้อมน้ำจิ้ม ขนาด 500ก./ 1,000ก. ราคา 290.00 บาท</t>
+          <t>แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด 500 กรัม ราคา 270.00 บาท</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2qS1FtJTov</t>
+          <t>https://s.shopee.co.th/3g18FVFWd9</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rask-m76elywra3an63.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zte-ml680l0flgxt0f.webp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -3536,21 +3530,21 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด 500 กรัม ราคา 270.00 บาท</t>
+          <t>ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko 100 กรัม | Premium Grade Nishio Matcha Powder ราคา 600.00 บาท</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3g18FVFWd9</t>
+          <t>https://s.shopee.co.th/3g18FVwHjP</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zte-ml680l0flgxt0f.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mk3h45kcwrnpc8.webp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -3561,21 +3555,21 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko 100 กรัม | Premium Grade Nishio Matcha Powder ราคา 600.00 บาท</t>
+          <t>ส่งด่วน กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื้อละมุน หวานมัน ปีละครั้ง ต้องลอง🍉 ส่งด่วนทุกวัน ทั่วประเทศ ราคา 849.00 บาท</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3g18FVwHjP</t>
+          <t>https://s.shopee.co.th/8ATXbpvKoM</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mk3h45kcwrnpc8.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0n-md1gusdgvf2880.webp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -3586,21 +3580,21 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ส่งด่วน กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื้อละมุน หวานมัน ปีละครั้ง ต้องลอง🍉 ส่งด่วนทุกวัน ทั่วประเทศ ราคา 849.00 บาท</t>
+          <t>อุดมสุข นรกแซลมอน 100 กรัม น้ำพริกคลีน น้ำพริกคีโต น้ำพริกเพื่อสุขภาพ อาหารคลีน อาหารคีโต ราคา 159.00 บาท</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8ATXbpvKoM</t>
+          <t>https://s.shopee.co.th/17pspiEJT</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0n-md1gusdgvf2880.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mk5i8ralf11k25.webp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -3611,71 +3605,71 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>อุดมสุข นรกแซลมอน 100 กรัม น้ำพริกคลีน น้ำพริกคีโต น้ำพริกเพื่อสุขภาพ อาหารคลีน อาหารคีโต ราคา 159.00 บาท</t>
+          <t>ชาเขียว 100% เพียวมัทฉะ ชาเขียว พรีเมี่ยม matcha powder from japan 0 สารเติมแต่ง 1 กระป๋อง 300g ราคา 355.00 บาท</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/17pspiEJT</t>
+          <t>https://s.shopee.co.th/4AxOqM1Q5R</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mk5i8ralf11k25.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mhivoyzzzqird0.webp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>done 2026-06-29 05:43</t>
+          <t>done 2026-06-30 05:40</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>ชาเขียว 100% เพียวมัทฉะ ชาเขียว พรีเมี่ยม matcha powder from japan 0 สารเติมแต่ง 1 กระป๋อง 300g ราคา 355.00 บาท</t>
+          <t>น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ไม่หวาน ผลิตวันต่อวัน ไม่ใส่วัตถุกันเสีย ของแท้จากบริษัท ราคา 169.00 บาท</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4AxOqM1Q5R</t>
+          <t>https://s.shopee.co.th/3LOHqo8diW</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mhivoyzzzqird0.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98z-lswcqt8y4gxp59.webp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>done 2026-06-30 05:40</t>
+          <t>done 2026-06-30 05:41</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ไม่หวาน ผลิตวันต่อวัน ไม่ใส่วัตถุกันเสีย ของแท้จากบริษัท ราคา 169.00 บาท</t>
+          <t>ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ตากสดใหม่ รับประกันความอร่อย ราคา 129.00 บาท</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3LOHqo8diW</t>
+          <t>https://s.shopee.co.th/5q5alcgJru</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98z-lswcqt8y4gxp59.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-22110-pkze82odovjv1f.webp</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -3686,21 +3680,21 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ตากสดใหม่ รับประกันความอร่อย ราคา 129.00 บาท</t>
+          <t>อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโต น้ำพริกเพื่อสุขภาพ ไม่ใส่ผงชูรส อาหารคลีน ราคา 169.00 บาท</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5q5alcgJru</t>
+          <t>https://s.shopee.co.th/5Apw2Yaqds</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/sg-11134201-22110-pkze82odovjv1f.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mk5i7m83jh1fa8.webp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -3711,21 +3705,21 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโต น้ำพริกเพื่อสุขภาพ ไม่ใส่ผงชูรส อาหารคลีน ราคา 169.00 บาท</t>
+          <t>มัทฉะ Kanbayashi Shunsho Usucha Aya no Mori อายะ โนะ โมริ 20g/40g Uji matcha【ส่งตรงจากญี่ปุ่น】 ราคา 1451.00 บาท</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5Apw2Yaqds</t>
+          <t>https://s.shopee.co.th/2Vp8nSwIA9</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mk5i7m83jh1fa8.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mj8j4x9o8jd27f.webp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -3736,439 +3730,414 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>มัทฉะ Kanbayashi Shunsho Usucha Aya no Mori อายะ โนะ โมริ 20g/40g Uji matcha【ส่งตรงจากญี่ปุ่น】 ราคา 1451.00 บาท</t>
+          <t>ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช 15 ปี ตัวแป้งทำจากมันเทศ เก็บได้นานเดือน อุ่นเวฟทานได้เรื่อยๆ</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2Vp8nSwIA9</t>
+          <t>https://s.shopee.co.th/6AiH6i2ekD</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mj8j4x9o8jd27f.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-mokxodhqmebkc8.webp</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>฿225</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>done 2026-06-30 05:41</t>
+          <t>done 2026-07-16 22:01</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช 15 ปี ตัวแป้งทำจากมันเทศ เก็บได้นานเดือน อุ่นเวฟทานได้เรื่อยๆ</t>
+          <t>อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไข่ฝนแรกล็อตสุดท้ายของปีนี้</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6AiH6i2ekD</t>
+          <t>https://s.shopee.co.th/1gFrkRMbd1</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-mokxodhqmebkc8.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rash-m8x3w0uh4ci73e.webp</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>฿225</t>
+          <t>฿1600</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>done 2026-07-16 22:01</t>
+          <t>done 2026-07-17 08:23</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไข่ฝนแรกล็อตสุดท้ายของปีนี้</t>
+          <t>🔥 แคบหมูกึ่งสำเร็จรูป (ติดมัน) Pig a Pop แคบหมูแบบทอดเอง แคบหมูป๊อป แคบหมู แคปหมู</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1gFrkRMbd1</t>
+          <t>https://s.shopee.co.th/8fPc5JDYYT</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rash-m8x3w0uh4ci73e.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mib2ub5p89og02.webp</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>฿1600</t>
+          <t>฿90</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>done 2026-07-17 08:23</t>
+          <t>done 2026-07-17 19:39</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>🔥 แคบหมูกึ่งสำเร็จรูป (ติดมัน) Pig a Pop แคบหมูแบบทอดเอง แคบหมูป๊อป แคบหมู แคปหมู</t>
+          <t>ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ตากสดใหม่ รับประกันความอร่อย</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8fPc5JDYYT</t>
+          <t>https://s.shopee.co.th/17dlNuzzw</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mib2ub5p89og02.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-22110-pkze82odovjv1f.webp</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>฿90</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>done 2026-07-17 19:39</t>
+          <t>฿129</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ตากสดใหม่ รับประกันความอร่อย</t>
+          <t>Chocolate Brownie Bite ช็อกโกแลตบราวนี่ไบท์ บราวนี่หน้าฟิล์ม</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/17dlNuzzw</t>
+          <t>https://s.shopee.co.th/1VwRY8x3aK</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/sg-11134201-22110-pkze82odovjv1f.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-23030-bggj3q1eovovda.webp</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>฿129</t>
+          <t>฿119</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Chocolate Brownie Bite ช็อกโกแลตบราวนี่ไบท์ บราวนี่หน้าฟิล์ม</t>
+          <t>ไข่ไก่เบอร์ 2 สดจากฟาร์ม 🥚 คัดพิเศษ ไข่ใหม่ทุกวัน</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1VwRY8x3aK</t>
+          <t>https://s.shopee.co.th/9Uyj4qWrbx</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-23030-bggj3q1eovovda.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mnkys1a0ddzcce.webp</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>฿119</t>
+          <t>฿80</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>ไข่ไก่เบอร์ 2 สดจากฟาร์ม 🥚 คัดพิเศษ ไข่ใหม่ทุกวัน</t>
+          <t>น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุนไพร รสน้ำพริกนรก แบบซอง ขนาด 100 กรัม 3 รสชาติ 1 ซอง Zalidpordeekum</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9Uyj4qWrbx</t>
+          <t>https://s.shopee.co.th/9pbZTSdhtH</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mnkys1a0ddzcce.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m863k6w28arga0.webp</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>฿80</t>
+          <t>฿160</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุนไพร รสน้ำพริกนรก แบบซอง ขนาด 100 กรัม 3 รสชาติ 1 ซอง Zalidpordeekum</t>
+          <t>(แพ็ค 24 ซอง) Muek Groob หมึกกรุบ เส้นบุกปรุงรสหม่าล่า (เลือกรสชาติได้)</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9pbZTSdhtH</t>
+          <t>https://s.shopee.co.th/4Va37fQGTa</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m863k6w28arga0.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0t-mbotiunlm1cj35.webp</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>฿160</t>
+          <t>฿502</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>(แพ็ค 24 ซอง) Muek Groob หมึกกรุบ เส้นบุกปรุงรสหม่าล่า (เลือกรสชาติได้)</t>
+          <t>น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส ไม่ใส่สารกันเสีย ขนาด 150 กรัม</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4Va37fQGTa</t>
+          <t>https://s.shopee.co.th/902STwG4qp</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0t-mbotiunlm1cj35.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mkc4ypl093wg43.webp</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>฿502</t>
+          <t>฿150</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส ไม่ใส่สารกันเสีย ขนาด 150 กรัม</t>
+          <t>กุ้งขาวตัวใหญ่ๆ ไซส์25-35ตัวโล กุ้งสดๆแล้วนำมาแช่แข็ง ขายแพ็คละ 1กิโลกรัม เป็นกุ้งสดๆและนำไปแช่แข็ง</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/902STwG4qp</t>
+          <t>https://s.shopee.co.th/5ApjuteugA</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mkc4ypl093wg43.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m866iuk5c8e4b8.webp</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>฿150</t>
+          <t>฿300</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>กุ้งขาวตัวใหญ่ๆ ไซส์25-35ตัวโล กุ้งสดๆแล้วนำมาแช่แข็ง ขายแพ็คละ 1กิโลกรัม เป็นกุ้งสดๆและนำไปแช่แข็ง</t>
+          <t>กาแฟดำเพื่อสุขภาพ ไม่มีน้ำตาล คั่วสด บดละเอียด ผงสกัดกาแฟละลายน้ำร้อนทันที พร้อมดื่ม Healthy Black Coffee | ร้านกาแฟ 89</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5ApjuteugA</t>
+          <t>https://s.shopee.co.th/AAEPs5TAKT</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m866iuk5c8e4b8.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98r-ly99vph2c04pdc.webp</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>฿300</t>
+          <t>฿99</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>กาแฟดำเพื่อสุขภาพ ไม่มีน้ำตาล คั่วสด บดละเอียด ผงสกัดกาแฟละลายน้ำร้อนทันที พร้อมดื่ม Healthy Black Coffee | ร้านกาแฟ 89</t>
+          <t>น้ำมันมรกต 1 ลิตร ยกลัง 12 ขวด สินค้าส่งตรงจากโรงงาน (1 คำสั่งซื้อ 1 ลัง) ต้องการมากกว่า 1 ให้แยกคำสั่งซื้อ</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/AAEPs5TAKT</t>
+          <t>https://s.shopee.co.th/2LVYXh5iWf</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98r-ly99vph2c04pdc.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98u-lnfj2bxeyxioc3.webp</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>฿99</t>
+          <t>฿822</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>น้ำมันมรกต 1 ลิตร ยกลัง 12 ขวด สินค้าส่งตรงจากโรงงาน (1 คำสั่งซื้อ 1 ลัง) ต้องการมากกว่า 1 ให้แยกคำสั่งซื้อ</t>
+          <t>น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นใหญ่ เต็มคำ แซ่บ เปรี้ยวเผ็ดสะใจ มี2ขนาด 100g./400g.</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2LVYXh5iWf</t>
+          <t>https://s.shopee.co.th/8KmlgitbG8</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98u-lnfj2bxeyxioc3.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mnmij2prwhl2a7.webp</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>฿822</t>
+          <t>฿175</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นใหญ่ เต็มคำ แซ่บ เปรี้ยวเผ็ดสะใจ มี2ขนาด 100g./400g.</t>
+          <t>ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ 3.5 กก.</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8KmlgitbG8</t>
+          <t>https://s.shopee.co.th/902STwyckb</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mnmij2prwhl2a7.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/f8fb32659a3650ce0dcc468f645e65be.webp</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>฿175</t>
+          <t>฿3700</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ 3.5 กก.</t>
+          <t>มัทฉะ Kanbayashi Shunsho Usucha Aya no Mori อายะ โนะ โมริ 20g/40g Uji matcha【ส่งตรงจากญี่ปุ่น】</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/902STwyckb</t>
+          <t>https://s.shopee.co.th/AAEPs672Qs</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/f8fb32659a3650ce0dcc468f645e65be.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mj8j4x9o8jd27f.webp</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>฿3700</t>
+          <t>฿1451</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>มัทฉะ Kanbayashi Shunsho Usucha Aya no Mori อายะ โนะ โมริ 20g/40g Uji matcha【ส่งตรงจากญี่ปุ่น】</t>
+          <t>ระฆังทองน้ำปลาหวาน องค์พระปฐมเจดีย์</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/AAEPs672Qs</t>
+          <t>https://s.shopee.co.th/gNKYdqLZf</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mj8j4x9o8jd27f.webp</t>
+          <t>https://down-bs-th.img.susercontent.com/03ce1f8bce1154adcaab44a6dce2438a.webp</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
-        <is>
-          <t>฿1451</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="n">
-        <v>36</v>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>ระฆังทองน้ำปลาหวาน องค์พระปฐมเจดีย์</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>https://s.shopee.co.th/gNKYdqLZf</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>https://down-bs-th.img.susercontent.com/03ce1f8bce1154adcaab44a6dce2438a.webp</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
         <is>
           <t>฿150</t>
         </is>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="630" yWindow="615" windowWidth="37095" windowHeight="17310" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -642,6 +642,11 @@
           <t>https://s.shopee.co.th/3qKMKSQPB2</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://s.lazada.co.th/s.Z6mEyG?c=a&amp;t=p-i0-s0&amp;sub_id1=W1</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mg3ydny6nkzwa4.webp</t>
@@ -3840,6 +3845,11 @@
       <c r="F131" t="inlineStr">
         <is>
           <t>฿129</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>done 2026-07-18 13:02</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4178,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["A", "B", "H", "B", "H", "F", "E", "D", "B", "F", "F", "E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C"], "last_hooks": ["ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ..."], "last_styles": ["คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม"], "last_roles": ["R6", "R2", "R8", "R1", "R6", "R8", "R3", "R4", "R2", "R7", "R6", "R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4"], "recent_captions": ["ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังออกกำลังกายเสร็จเหนื่อยๆ บางวันเคี้ยวอกไก่ไม่ไหวจริงๆ ได้ตัวนี้ดื่มแทนง่ายมาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น นมเปรี้ยว ดัชมิลล์ ขนาด เซต ราคาแค่ 250 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แคบหมูไร้มัน แคปหมูไร้มัน . . ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กาแฟดำเพื่อสุขภาพ ไม่มีน้ำตาล คั่วสด บดละเอีย ราคาแค่ 99 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ทุเรียนจันทบุรีเนื้อพรีเมียม ยอดขายเยอะที่สุด ราคาแค่ 621 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู เคี้ยวเพลินๆรสต้มยำ ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ . ราคาแค่ 3700 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม น้ำปลาร้าปรุงสุก ตราไม ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ แอปเปิ้ลแช่แข็งแห้งกรอบพรีเมี่ยมชิ้นไม่มีสารเ ราคาแค่ 112 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุน ราคาแค่ 155 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90"]}</t>
+          <t>{"last_personas": ["B", "H", "B", "H", "F", "E", "D", "B", "F", "F", "E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D"], "last_hooks": ["เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี"], "last_styles": ["การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)"], "last_roles": ["R2", "R8", "R1", "R6", "R8", "R3", "R4", "R2", "R7", "R6", "R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2"], "recent_captions": ["เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แคบหมูไร้มัน แคปหมูไร้มัน . . ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กาแฟดำเพื่อสุขภาพ ไม่มีน้ำตาล คั่วสด บดละเอีย ราคาแค่ 99 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ทุเรียนจันทบุรีเนื้อพรีเมียม ยอดขายเยอะที่สุด ราคาแค่ 621 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู เคี้ยวเพลินๆรสต้มยำ ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ . ราคาแค่ 3700 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม น้ำปลาร้าปรุงสุก ตราไม ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ แอปเปิ้ลแช่แข็งแห้งกรอบพรีเมี่ยมชิ้นไม่มีสารเ ราคาแค่ 112 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุน ราคาแค่ 155 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -3877,6 +3877,11 @@
           <t>฿119</t>
         </is>
       </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>done 2026-07-18 13:12</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -4178,7 +4183,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["B", "H", "B", "H", "F", "E", "D", "B", "F", "F", "E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D"], "last_hooks": ["เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี"], "last_styles": ["การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)"], "last_roles": ["R2", "R8", "R1", "R6", "R8", "R3", "R4", "R2", "R7", "R6", "R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2"], "recent_captions": ["เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แคบหมูไร้มัน แคปหมูไร้มัน . . ราคาแค่ 219 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กาแฟดำเพื่อสุขภาพ ไม่มีน้ำตาล คั่วสด บดละเอีย ราคาแค่ 99 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ทุเรียนจันทบุรีเนื้อพรีเมียม ยอดขายเยอะที่สุด ราคาแค่ 621 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู เคี้ยวเพลินๆรสต้มยำ ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ . ราคาแค่ 3700 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม น้ำปลาร้าปรุงสุก ตราไม ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ แอปเปิ้ลแช่แข็งแห้งกรอบพรีเมี่ยมชิ้นไม่มีสารเ ราคาแค่ 112 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุน ราคาแค่ 155 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129"]}</t>
+          <t>{"last_personas": ["H", "B", "H", "F", "E", "D", "B", "F", "F", "E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F"], "last_hooks": ["มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ..."], "last_styles": ["การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ"], "last_roles": ["R8", "R1", "R6", "R8", "R3", "R4", "R2", "R7", "R6", "R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5"], "recent_captions": ["มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กาแฟดำเพื่อสุขภาพ ไม่มีน้ำตาล คั่วสด บดละเอีย ราคาแค่ 99 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ทุเรียนจันทบุรีเนื้อพรีเมียม ยอดขายเยอะที่สุด ราคาแค่ 621 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู เคี้ยวเพลินๆรสต้มยำ ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ . ราคาแค่ 3700 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม น้ำปลาร้าปรุงสุก ตราไม ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ แอปเปิ้ลแช่แข็งแห้งกรอบพรีเมี่ยมชิ้นไม่มีสารเ ราคาแค่ 112 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุน ราคาแค่ 155 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -3907,6 +3907,11 @@
           <t>฿80</t>
         </is>
       </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>done 2026-07-18 19:09</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -4183,7 +4188,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["H", "B", "H", "F", "E", "D", "B", "F", "F", "E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F"], "last_hooks": ["มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ..."], "last_styles": ["การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ"], "last_roles": ["R8", "R1", "R6", "R8", "R3", "R4", "R2", "R7", "R6", "R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5"], "recent_captions": ["มีใครเป็นเหมือนผมไหม สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กาแฟดำเพื่อสุขภาพ ไม่มีน้ำตาล คั่วสด บดละเอีย ราคาแค่ 99 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ทุเรียนจันทบุรีเนื้อพรีเมียม ยอดขายเยอะที่สุด ราคาแค่ 621 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู เคี้ยวเพลินๆรสต้มยำ ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ . ราคาแค่ 3700 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม น้ำปลาร้าปรุงสุก ตราไม ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ แอปเปิ้ลแช่แข็งแห้งกรอบพรีเมี่ยมชิ้นไม่มีสารเ ราคาแค่ 112 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุน ราคาแค่ 155 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119"]}</t>
+          <t>{"last_personas": ["B", "H", "F", "E", "D", "B", "F", "F", "E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F"], "last_hooks": ["ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม"], "last_styles": ["การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ"], "last_roles": ["R1", "R6", "R8", "R3", "R4", "R2", "R7", "R6", "R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8"], "recent_captions": ["ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ทุเรียนจันทบุรีเนื้อพรีเมียม ยอดขายเยอะที่สุด ราคาแค่ 621 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู เคี้ยวเพลินๆรสต้มยำ ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ . ราคาแค่ 3700 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม น้ำปลาร้าปรุงสุก ตราไม ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ แอปเปิ้ลแช่แข็งแห้งกรอบพรีเมี่ยมชิ้นไม่มีสารเ ราคาแค่ 112 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุน ราคาแค่ 155 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -3937,6 +3937,11 @@
           <t>฿160</t>
         </is>
       </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>done 2026-07-20 20:23</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -4188,7 +4193,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["B", "H", "F", "E", "D", "B", "F", "F", "E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F"], "last_hooks": ["ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม"], "last_styles": ["การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ"], "last_roles": ["R1", "R6", "R8", "R3", "R4", "R2", "R7", "R6", "R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8"], "recent_captions": ["ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ทุเรียนจันทบุรีเนื้อพรีเมียม ยอดขายเยอะที่สุด ราคาแค่ 621 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู เคี้ยวเพลินๆรสต้มยำ ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ . ราคาแค่ 3700 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม น้ำปลาร้าปรุงสุก ตราไม ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ แอปเปิ้ลแช่แข็งแห้งกรอบพรีเมี่ยมชิ้นไม่มีสารเ ราคาแค่ 112 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุน ราคาแค่ 155 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80"]}</t>
+          <t>{"last_personas": ["H", "F", "E", "D", "B", "F", "F", "E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C"], "last_hooks": ["โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ"], "last_styles": ["การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)"], "last_roles": ["R6", "R8", "R3", "R4", "R2", "R7", "R6", "R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8"], "recent_captions": ["โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู เคี้ยวเพลินๆรสต้มยำ ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ . ราคาแค่ 3700 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม น้ำปลาร้าปรุงสุก ตราไม ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ แอปเปิ้ลแช่แข็งแห้งกรอบพรีเมี่ยมชิ้นไม่มีสารเ ราคาแค่ 112 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุน ราคาแค่ 155 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -3967,6 +3967,11 @@
           <t>฿502</t>
         </is>
       </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>done 2026-07-21 19:49</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -4193,7 +4198,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["H", "F", "E", "D", "B", "F", "F", "E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C"], "last_hooks": ["โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ"], "last_styles": ["การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)"], "last_roles": ["R6", "R8", "R3", "R4", "R2", "R7", "R6", "R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8"], "recent_captions": ["โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู เคี้ยวเพลินๆรสต้มยำ ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ . ราคาแค่ 3700 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม น้ำปลาร้าปรุงสุก ตราไม ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ แอปเปิ้ลแช่แข็งแห้งกรอบพรีเมี่ยมชิ้นไม่มีสารเ ราคาแค่ 112 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุน ราคาแค่ 155 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160"]}</t>
+          <t>{"last_personas": ["F", "E", "D", "B", "F", "F", "E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม"], "last_roles": ["R8", "R3", "R4", "R2", "R7", "R6", "R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ . ราคาแค่ 3700 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม น้ำปลาร้าปรุงสุก ตราไม ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ แอปเปิ้ลแช่แข็งแห้งกรอบพรีเมี่ยมชิ้นไม่มีสารเ ราคาแค่ 112 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุน ราคาแค่ 155 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -3997,6 +3997,11 @@
           <t>฿150</t>
         </is>
       </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>done 2026-07-22 19:50</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -4198,7 +4203,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["F", "E", "D", "B", "F", "F", "E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม"], "last_roles": ["R8", "R3", "R4", "R2", "R7", "R6", "R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ทุเรียนหมอนทอง คัดพิเศษ กล่องใหญ่ . ราคาแค่ 3700 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม น้ำปลาร้าปรุงสุก ตราไม ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ แอปเปิ้ลแช่แข็งแห้งกรอบพรีเมี่ยมชิ้นไม่มีสารเ ราคาแค่ 112 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุน ราคาแค่ 155 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502"]}</t>
+          <t>{"last_personas": ["E", "D", "B", "F", "F", "E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G"], "last_hooks": ["อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี"], "last_styles": ["การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก"], "last_roles": ["R3", "R4", "R2", "R7", "R6", "R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4"], "recent_captions": ["อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม น้ำปลาร้าปรุงสุก ตราไม ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ แอปเปิ้ลแช่แข็งแห้งกรอบพรีเมี่ยมชิ้นไม่มีสารเ ราคาแค่ 112 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุน ราคาแค่ 155 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -4027,6 +4027,11 @@
           <t>฿300</t>
         </is>
       </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>done 2026-07-23 19:53</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -4203,7 +4208,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["E", "D", "B", "F", "F", "E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G"], "last_hooks": ["อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี"], "last_styles": ["การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก"], "last_roles": ["R3", "R4", "R2", "R7", "R6", "R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4"], "recent_captions": ["อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ✅โค้ดส่งฟรี+🎫โค้ดคุุ้ม น้ำปลาร้าปรุงสุก ตราไม ราคาแค่ 245 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ แอปเปิ้ลแช่แข็งแห้งกรอบพรีเมี่ยมชิ้นไม่มีสารเ ราคาแค่ 112 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุน ราคาแค่ 155 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150"]}</t>
+          <t>{"last_personas": ["D", "B", "F", "F", "E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ"], "last_styles": ["มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)"], "last_roles": ["R4", "R2", "R7", "R6", "R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6"], "recent_captions": ["แชร์เผื่อมีคนกำลังหาอยู่ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ แอปเปิ้ลแช่แข็งแห้งกรอบพรีเมี่ยมชิ้นไม่มีสารเ ราคาแค่ 112 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุน ราคาแค่ 155 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -4057,6 +4057,11 @@
           <t>฿99</t>
         </is>
       </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>done 2026-07-24 19:50</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -4208,7 +4213,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["D", "B", "F", "F", "E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ"], "last_styles": ["มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)"], "last_roles": ["R4", "R2", "R7", "R6", "R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6"], "recent_captions": ["แชร์เผื่อมีคนกำลังหาอยู่ ของกินตัวนี้เลยค่ะ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ แอปเปิ้ลแช่แข็งแห้งกรอบพรีเมี่ยมชิ้นไม่มีสารเ ราคาแค่ 112 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุน ราคาแค่ 155 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300"]}</t>
+          <t>{"last_personas": ["B", "F", "F", "E", "E", "B", "F", "H", "A", "F", "E", "G", "F", "B", "G", "E", "H", "E", "D", "C", "F", "B", "C", "C", "A", "H", "A", "H", "G", "C", "F", "C", "F", "D", "H", "E", "A", "D", "D", "C", "B", "C", "D", "F", "F", "C", "E", "G", "G", "H"], "last_hooks": ["เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่", "เห็นคนพูดถึงเยอะเลยลอง", "ไม่คิดว่าจะ...", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เมื่อวานเพิ่งเจอ...", "มีใครเป็นเหมือนผมไหม", "ตอนแรกไม่ได้จะซื้อ", "โดนป้ายยามาอีกที", "กำลังหาของแบบนี้อยู่พอดี", "อันนี้เกินคาดจริงๆ", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "มุกตลก", "มุกตลก", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "คำถาม", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ"], "last_roles": ["R2", "R7", "R6", "R7", "R4", "R4", "R6", "R7", "R3", "R2", "R8", "R3", "R8", "R4", "R6", "R2", "R3", "R5", "R1", "R8", "R7", "R8", "R7", "R2", "R1", "R3", "R3", "R4", "R6", "R6", "R5", "R7", "R4", "R5", "R2", "R1", "R2", "R6", "R3", "R1", "R3", "R4", "R2", "R5", "R8", "R8", "R1", "R4", "R6", "R2"], "recent_captions": ["เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกแห้งปลาสลิดโรยข้าว รสผัดพริกขิง รสสมุน ราคาแค่ 155 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ กรุงเทพปริมณฑลมีส่งด่วนยอดขายมากที่สุด รีวิวม ราคาแค่ 542 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนสกาแฟ​ nescafe กาแฟ​สำเร็จ​รูป ราคา ราคาแค่ 173 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เนยถั่วรวม Chocolate Nuts Butter ราคาแค่ 175 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง อึ่งไข่ฝนแรก ❗️พร้อมส่ง อึ่งไข่แช่แข็ง 📍อึ่งไ ราคาแค่ 850 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ หมูแดดเดียวพรีเมียม อบลมร้อน สะอาด ไร้ฝุ่น ราคาแค่ 149 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ชามะระขี้นก ตราทองหลวง ☘️❇️ ของเเท้ ราคาแค่ 80 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ในไทยMarukyu Koyamaen Matcha มัทฉะมารุคิวโคยา ราคาแค่ 1118 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ของกินตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำพริกหมูกระจกมะเดี่ยว วับวาว รสต้มยำ ชิ้นให ราคาแค่ 365 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ น้ำจิ้มปิ้งย่าง สูตรพี่ฟร้องซ์ **ไม่ใส่ผักชี* ราคาแค่ 89 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำมันปาล์ม เกสร ราคาพิเศษ ขวด ราคาแค่ 220 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น คุกกี้ไส้ทะลัก แบบ ชิ้น ชิ้น ราคาแค่ 120 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Benefruit มะพร้าวอบแห้ง🥥 มะพร้าวกรอบ เนื้อแน่ ราคาแค่ 195 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ลองซื้อ นมโปรตีน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำมันมรกต ลิตร ยกลัง ขวด ราคาแค่ 822 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ จัดให้ กระปุก🌶️น้ำพริกไข่มันกุ้ง+น้ำพริกไข่ปู ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ พริกกากหมู สูตรโบราณดั้งเดิม ราคา . ราคาแค่ 150 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง น้ำพริกแซลมอนไข่เค็มคลีน ไม่มัน ไม่ใส่ผงชูรส  ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ นมโปรตีน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ สเต็กเนื้อโคขุนพริกไทยดำ-150กรัม/ชิ้น10ชิ้นมี ราคาแค่ 650 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรงงาน🚚สับปะรดภูแลอบแห้งมินิมอล 齋·حلال สูตรธร ราคาแค่ 150 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยค่ะ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ถั่ว เซียน ธัญพืชรวม อบกรุบกรอบ ราคาแค่ 199 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ผลไม้อบแห้งพรีเมียม: ลูกเกดและเบอร์รี่ ลูกเกด ราคาแค่ 135 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ขายดี🔥 Benefruit ส้มอบแห้ง🍊ส้มหนึบ กลีบส้ม ราคาแค่ 95 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกน้ำย้อย ตรายาหยี สูตรเมืองแพร่ดั้งเดิม ราคาแค่ 97 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น มี อ.ย.‼ ซอสผัดกะเพรา สูตรเข้มข้น ราคาแค่ 119 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น หมูสามชั้นทอดน้ำปลา ตรา ทอดไท 🔥พร้อมทาน ราคาแค่ 109 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ มัทฉะ Kanbayashi Shunsho Koicha ราคาแค่ 1854 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น สตรอว์เบอร์รี่ คลุกพริกเกลือ จี๊ดจ๊าดชื่นใจ ล ราคาแค่ 189 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง โรตีสายไหมทุเรียนแม่ระย้า โรตีสายไหมอยุธยา พร ราคาแค่ 119 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ น้ำพริกหมูกระจก รสต้มยำ ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น หมูกรอบ เงินล้าน เนื้อเยอะ มันน้อย ราคาแค่ 290 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เห็นคนพูดถึงเยอะเลยลอง คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ แพ็คเกจใหม่ รวม น้ำพริกหมูกระจก ขนาด ราคาแค่ 270 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ผงมัทฉะนิชิโอะ เกรดพรีเมี่ยม Noko กรัม ราคาแค่ 600 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี นมโปรตีนตัวนี้เลยค่ะ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ กรุงเทพ/ตจว.❤️ทุเรียนป่าละอู 1โลเนื้อล้วน🧡เนื ราคาแค่ 849 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "เมื่อวานเพิ่งเจอ... ของกินตัวนี้เลยค่ะ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข นรกแซลมอน กรัม น้ำพริกคลีน ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ ของกิน ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ชาเขียว % เพียวมัทฉะ ชาเขียว ราคาแค่ 355 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น น้ำพริกผัดหมูสับ ดมข้าว เผ็ด เค็ม ราคาแค่ 169 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "โดนป้ายยามาอีกที สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "กำลังหาของแบบนี้อยู่พอดี ของกินตัวนี้เลยค่ะ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อุดมสุข น้ำพริกปลากะพง น้ำพริกคลีน น้ำพริกคีโ ราคาแค่ 169 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ ของกิน ตัวนี้มาใช้ได้สักพักแล้วค่ะ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง มัทฉะ Kanbayashi Shunsho Usucha ราคาแค่ 1451 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆค่ะ ตัวนี้มีจุดเด่นคือ ใหม่!เซาปิ่งเปี๊ยะนุ่มลาวา สูตรเยาวราช ปี ตัว ราคาแค่ 225 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿225", "เห็นคนพูดถึงเยอะเลยลอง อึ่งไข่แช่แข็งตัวนี้เลยค่ะ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ อึ่งไข่ฝนแรก ล็อตสุดท้ายของปี ราคาแค่ 1600 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿1600", "ไม่คิดว่าจะ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง แคบหมูกึ่งสำเร็จรูป ตัวนี้รึยังค่ะ ส่วนตัวประทับใจจุดเด่น ทอดเองสดใหม่ ราคาแค่ 90 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿90", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลาหมึกแห้ง ปลาหมึกแพไข่ ไซส์กลาง ไม่เค็มมาก ราคาแค่ 129 บาท ดีกว่าเห็นๆ เลยค่ะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿129", "เมื่อวานเพิ่งเจอ...บราวนี่ รสช็อกโกแลต แบบหน้าฟิล์ม พอดีคำ ราคา 119 บาท ที่ทำให้หนูค้นพบว่าคำว่ากินแค่ชิ้นเดียวไม่มีอยู่จริงค่ะ ตอนแรกกะจะกินเล่นๆ สรุปหมดกล่องเกลี้ยงเลย สภาพเหมือนพายุเข้าพุงตัวเองมาก 555 ใครที่ชอบทาน บราวนี่หน้าฟิล์ม ไซส์น่ารักแบบนี้ เซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนไปลองกันได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿119", "มีใครเป็นเหมือนผมไหม เจียวไข่ทีไรนึกว่าทำสงคราม ล่าสุดเราเลยไปซื้อ ไข่ไก่ ขนาดเบอร์ 2 ที่คัดพิเศษแบบสดใหม่มาในราคา 80 บาทค่ะ สรุปต้องเอามาต้มกินแทนเพื่อความปลอดภัยของใบหน้า ใครที่ทอดไข่ทีไรน้ำมันกระเด็นใส่ตลอดแชร์ต่อให้เพื่อนที่เจอปัญหานี้ด่วนๆ เลยนะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿80", "ตอนแรกไม่ได้จะซื้อ แต่ช่วงก่อนหน้านี้หนูเบื่ออาหารมาก ทานอะไรก็จืดชืดไม่มีรสชาติเลยค่ะ พอได้ลองโรยน้ำพริกโรยข้าวสูตรปลาสลิดแท้ลงบนข้าวสวยร้อนๆ มื้ออาหารก็กลับมามีชีวิตชีวา ทานข้าวหมดจานได้ง่ายๆ เลยค่ะ ตัวนี้เขามี 3 รสชาติ ทั้งผัดพริกขิง สมุนไพร และนรก ขนาด 100g บังเอิญไปเจอช่วงจัดราคาพิเศษ 160 บาทพอดี ใครที่เจอปัญหาเดียวกันเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿160", "โดนป้ายยามาอีกที มีใครเคยเจอปัญหาง่วงนอนตอนบ่ายจนไม่มีสมาธิทำงานเหมือนกันบ้างไหมคะ? ล่าสุดเราได้ แพ็ค Muek Groob หมึกกรุบ มาเคี้ยวเล่นแก้ง่วงระหว่างวัน ช่วยชีวิตในออฟฟิศไว้ได้เยอะเลยค่ะ ใครที่กำลังมองหาของกินเล่นยามบ่าย แชร์ต่อให้เพื่อนที่เจอปัญหานี้แล้วลองไปกดสั่งในราคา 502 บาทมาตุนกันไว้นะคะ\n\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿502", "กำลังหาของแบบนี้อยู่พอดี ตอนแรกหนูแอบสงสัยว่าน้ำพริกรสแซลมอนไข่เค็มมันจะคลีนได้ยังไง จะไม่มันแผลบเหมือนหน้าหนูตอนบ่ายแน่นะ เลยยอมจ่าย 150 บาท ซื้อขนาด 150g มาลองให้รู้แล้วรู้รอดค่ะ ปรากฏว่าเนื้อน้ำพริกคลีนจริง ไม่มัน แถมไร้สารกันเสียตามที่บอกไว้เป๊ะ ใครที่ค้นหาน้ำพริกอร่อยๆ อยู่ กดเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยนะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿150", "อันนี้เกินคาดจริงๆ เมื่อก่อนเราเคยลังเลไม่กล้าซื้อกุ้งแช่แข็งมาทำอาหาร เพราะกลัวว่าจะเจอกุ้งไม่สดหรือเนื้อเละค่ะ แต่พอลองตัดสินใจซื้อกุ้งขาวแช่แข็งไซส์ใหญ่ขนาด 25-35 ตัว/กก. ถุงใหญ่ 1 กก. ในราคา 300 บาทมาลองทำกินเอง ตัวนี้เขาใช้กุ้งสดนำมาแช่แข็งได้คุณภาพมาก ทำให้การทำเมนูกุ้งของหนูสะดวกสบายขึ้นเยอะโดยไม่ต้องเสียเวลาไปเดินหาซื้อกุ้งสดเองเลยค่ะ เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนสายเข้าครัวได้เลยนะคะ ดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿300", "แชร์เผื่อมีคนกำลังหาอยู่ พอดีเราเพิ่งซื้อกาแฟดำมาให้คนที่บ้านชงดื่มค่ะ ตัวนี้ไม่มีน้ำตาล แถมชงแล้วละลายทันที สะดวกมาก ในราคา 99 บาท เซฟโพสต์ไว้หรือแชร์ต่อให้คนในครอบครัวดูได้นะคะ\nดูลิ้งในคอมเมนต์แรกเลยนะคะ 👇\n🔥 โปรโมชั่น: ฿99"]}</t>
         </is>
       </c>
     </row>
